--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 4,154 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (210) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (198) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3746) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 4,155 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (210) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (198) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3747) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>3,746</t>
+          <t>3,747</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="K10" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L10" s="22" t="n">
         <v>3</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="K18" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L18" s="22" t="n">
         <v>3</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="K22" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L22" s="22" t="n">
         <v>3</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="K23" s="22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" s="22" t="n">
         <v>3</v>
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="K32" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L32" s="22" t="n">
         <v>3</v>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="K33" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L33" s="22" t="n">
         <v>3</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="K46" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L46" s="22" t="n">
         <v>6</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="K47" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L47" s="22" t="n">
         <v>3</v>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="K50" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L50" s="22" t="n">
         <v>3</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="K60" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L60" s="22" t="n">
         <v>3</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="K62" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L62" s="22" t="n">
         <v>3</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="K65" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L65" s="22" t="n">
         <v>3</v>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="K69" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L69" s="22" t="n">
         <v>3</v>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="K71" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L71" s="22" t="n">
         <v>3</v>
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="K81" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L81" s="22" t="n">
         <v>5</v>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="K94" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L94" s="22" t="n">
         <v>3</v>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="K129" s="22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L129" s="22" t="n">
         <v>3</v>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="K163" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L163" s="22" t="n">
         <v>4</v>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="K173" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L173" s="22" t="n">
         <v>4</v>
@@ -11280,7 +11280,7 @@
         </is>
       </c>
       <c r="K175" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L175" s="22" t="n">
         <v>3</v>
@@ -11696,7 +11696,7 @@
         </is>
       </c>
       <c r="K182" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L182" s="22" t="n">
         <v>5</v>
@@ -12292,7 +12292,7 @@
         </is>
       </c>
       <c r="K192" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L192" s="22" t="n">
         <v>3</v>
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="K38" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L38" s="22" t="n">
         <v>3</v>
@@ -16743,7 +16743,7 @@
         </is>
       </c>
       <c r="K54" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L54" s="22" t="n">
         <v>3</v>
@@ -18063,7 +18063,7 @@
         </is>
       </c>
       <c r="K76" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L76" s="22" t="n">
         <v>3</v>
@@ -21239,7 +21239,7 @@
         </is>
       </c>
       <c r="K129" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L129" s="22" t="n">
         <v>5</v>
@@ -26158,7 +26158,7 @@
         </is>
       </c>
       <c r="K11" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L11" s="22" t="n">
         <v>0</v>
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="K19" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L19" s="22" t="n">
         <v>2</v>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="K37" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L37" s="22" t="n">
         <v>2</v>
@@ -27942,7 +27942,7 @@
         </is>
       </c>
       <c r="K41" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L41" s="22" t="n">
         <v>2</v>
@@ -28302,7 +28302,7 @@
         </is>
       </c>
       <c r="K47" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L47" s="22" t="n">
         <v>2</v>
@@ -28422,7 +28422,7 @@
         </is>
       </c>
       <c r="K49" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L49" s="22" t="n">
         <v>2</v>
@@ -28658,7 +28658,7 @@
         </is>
       </c>
       <c r="K53" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L53" s="22" t="n">
         <v>2</v>
@@ -29434,7 +29434,7 @@
         </is>
       </c>
       <c r="K66" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L66" s="22" t="n">
         <v>2</v>
@@ -29554,7 +29554,7 @@
         </is>
       </c>
       <c r="K68" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L68" s="22" t="n">
         <v>2</v>
@@ -29614,7 +29614,7 @@
         </is>
       </c>
       <c r="K69" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L69" s="22" t="n">
         <v>2</v>
@@ -31166,7 +31166,7 @@
         </is>
       </c>
       <c r="K95" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L95" s="22" t="n">
         <v>2</v>
@@ -31814,7 +31814,7 @@
         </is>
       </c>
       <c r="K106" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L106" s="22" t="n">
         <v>2</v>
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="K115" s="22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L115" s="22" t="n">
         <v>2</v>
@@ -32410,7 +32410,7 @@
         </is>
       </c>
       <c r="K116" s="22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L116" s="22" t="n">
         <v>2</v>
@@ -32586,7 +32586,7 @@
         </is>
       </c>
       <c r="K119" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L119" s="22" t="n">
         <v>1</v>
@@ -32946,7 +32946,7 @@
         </is>
       </c>
       <c r="K125" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L125" s="22" t="n">
         <v>0</v>
@@ -33366,7 +33366,7 @@
         </is>
       </c>
       <c r="K132" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L132" s="22" t="n">
         <v>2</v>
@@ -34202,7 +34202,7 @@
         </is>
       </c>
       <c r="K146" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L146" s="22" t="n">
         <v>2</v>
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="K164" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L164" s="22" t="n">
         <v>2</v>
@@ -35878,7 +35878,7 @@
         </is>
       </c>
       <c r="K174" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L174" s="22" t="n">
         <v>2</v>
@@ -36474,7 +36474,7 @@
         </is>
       </c>
       <c r="K184" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L184" s="22" t="n">
         <v>2</v>
@@ -37614,7 +37614,7 @@
         </is>
       </c>
       <c r="K203" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L203" s="22" t="n">
         <v>1</v>
@@ -38034,7 +38034,7 @@
         </is>
       </c>
       <c r="K210" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L210" s="22" t="n">
         <v>2</v>
@@ -38154,7 +38154,7 @@
         </is>
       </c>
       <c r="K212" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L212" s="22" t="n">
         <v>1</v>
@@ -38334,7 +38334,7 @@
         </is>
       </c>
       <c r="K215" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L215" s="22" t="n">
         <v>1</v>
@@ -39114,7 +39114,7 @@
         </is>
       </c>
       <c r="K228" s="22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L228" s="22" t="n">
         <v>0</v>
@@ -39830,7 +39830,7 @@
         </is>
       </c>
       <c r="K240" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L240" s="22" t="n">
         <v>1</v>
@@ -40310,7 +40310,7 @@
         </is>
       </c>
       <c r="K248" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L248" s="22" t="n">
         <v>2</v>
@@ -42406,7 +42406,7 @@
         </is>
       </c>
       <c r="K283" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L283" s="22" t="n">
         <v>2</v>
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="K294" s="22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L294" s="22" t="n">
         <v>0</v>
@@ -43182,7 +43182,7 @@
         </is>
       </c>
       <c r="K296" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L296" s="22" t="n">
         <v>0</v>
@@ -43418,14 +43418,14 @@
         </is>
       </c>
       <c r="K300" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L300" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M300" s="21" t="inlineStr">
         <is>
-          <t>NetCashReturner, StrongCoverage, LynchPEGY</t>
+          <t>NetCashReturner, StrongCoverage, LynchPEGY, Greenblatt-MagicFormula</t>
         </is>
       </c>
       <c r="N300" s="24" t="n">
@@ -43598,7 +43598,7 @@
         </is>
       </c>
       <c r="K303" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L303" s="22" t="n">
         <v>1</v>
@@ -44078,7 +44078,7 @@
         </is>
       </c>
       <c r="K311" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L311" s="22" t="n">
         <v>2</v>
@@ -45454,7 +45454,7 @@
         </is>
       </c>
       <c r="K334" s="22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L334" s="22" t="n">
         <v>1</v>
@@ -46114,7 +46114,7 @@
         </is>
       </c>
       <c r="K345" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L345" s="22" t="n">
         <v>1</v>
@@ -46946,7 +46946,7 @@
         </is>
       </c>
       <c r="K359" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L359" s="22" t="n">
         <v>1</v>
@@ -47426,7 +47426,7 @@
         </is>
       </c>
       <c r="K367" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L367" s="22" t="n">
         <v>0</v>
@@ -49106,7 +49106,7 @@
         </is>
       </c>
       <c r="K395" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L395" s="22" t="n">
         <v>1</v>
@@ -50546,7 +50546,7 @@
         </is>
       </c>
       <c r="K419" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L419" s="22" t="n">
         <v>0</v>
@@ -50722,7 +50722,7 @@
         </is>
       </c>
       <c r="K422" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L422" s="22" t="n">
         <v>2</v>
@@ -51442,7 +51442,7 @@
         </is>
       </c>
       <c r="K434" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L434" s="22" t="n">
         <v>1</v>
@@ -51562,7 +51562,7 @@
         </is>
       </c>
       <c r="K436" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L436" s="22" t="n">
         <v>1</v>
@@ -52762,7 +52762,7 @@
         </is>
       </c>
       <c r="K456" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L456" s="22" t="n">
         <v>2</v>
@@ -52882,7 +52882,7 @@
         </is>
       </c>
       <c r="K458" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L458" s="22" t="n">
         <v>2</v>
@@ -52942,14 +52942,14 @@
         </is>
       </c>
       <c r="K459" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L459" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M459" s="21" t="inlineStr">
         <is>
-          <t>MidCapGARP, Bottleneck-Chokepoint, Flyover-QuietQuality</t>
+          <t>MidCapGARP, Bottleneck-Chokepoint, Flyover-QuietQuality, Greenblatt-Ma</t>
         </is>
       </c>
       <c r="N459" s="24" t="n">
@@ -54922,7 +54922,7 @@
         </is>
       </c>
       <c r="K492" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L492" s="22" t="n">
         <v>1</v>

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'STRICT'!$B$3:$O$221</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'STRONG'!$B$3:$O$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'STRONG'!$B$3:$O$197</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CANDIDATE_Top500'!$B$3:$O$503</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 4,326 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (218) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (195) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3913) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 4,326 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (218) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (194) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3914) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>194</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>3,913</t>
+          <t>3,914</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="K34" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L34" s="22" t="n">
         <v>3</v>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="K54" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L54" s="22" t="n">
         <v>4</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="K65" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L65" s="22" t="n">
         <v>6</v>
@@ -13192,14 +13192,14 @@
         </is>
       </c>
       <c r="K207" s="22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L207" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M207" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ROICInflect, BuybackCompounder, Weinstein-Stage2, Kullam</t>
+          <t>KPIThreshold, ROICInflect, BuybackCompounder, Weinstein-Stage2, LowSBC</t>
         </is>
       </c>
       <c r="N207" s="24" t="n">
@@ -14065,7 +14065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O198"/>
+  <dimension ref="A1:O197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -14089,7 +14089,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG — watchlist — 195 names</t>
+          <t xml:space="preserve">  STRONG — watchlist — 194 names</t>
         </is>
       </c>
       <c r="B1" s="11" t="n"/>
@@ -21179,7 +21179,7 @@
         </is>
       </c>
       <c r="K120" s="22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L120" s="22" t="n">
         <v>3</v>
@@ -21193,7 +21193,7 @@
         <v>0.3857195054755893</v>
       </c>
       <c r="O120" s="24" t="n">
-        <v>0.40062322</v>
+        <v>0.3994231152</v>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
@@ -25035,22 +25035,22 @@
       </c>
       <c r="D185" s="18" t="inlineStr">
         <is>
-          <t>ARWR</t>
+          <t>TKA.F</t>
         </is>
       </c>
       <c r="E185" s="19" t="inlineStr">
         <is>
-          <t>Arrowhead Pharmaceuticals, Inc.</t>
+          <t>thyssenkrupp AG</t>
         </is>
       </c>
       <c r="F185" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G185" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H185" s="16" t="inlineStr">
@@ -25059,7 +25059,7 @@
         </is>
       </c>
       <c r="I185" s="22" t="n">
-        <v>11702932480</v>
+        <v>11091495472.63037</v>
       </c>
       <c r="J185" s="23" t="inlineStr">
         <is>
@@ -25067,21 +25067,21 @@
         </is>
       </c>
       <c r="K185" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L185" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M185" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, Kullamagi-Breakout, ReratingConfirmed-52wHigh</t>
+          <t>KPIThreshold, Weinstein-Stage2, Kullamagi-Breakout, StrongCoverage, Ly</t>
         </is>
       </c>
       <c r="N185" s="24" t="n">
-        <v>0.4186436598281458</v>
+        <v>0.3574683544443799</v>
       </c>
       <c r="O185" s="24" t="n">
-        <v>0.3149720464</v>
+        <v>0.309572802</v>
       </c>
     </row>
     <row r="186" ht="16" customHeight="1">
@@ -25095,31 +25095,31 @@
       </c>
       <c r="D186" s="18" t="inlineStr">
         <is>
-          <t>TKA.F</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="E186" s="19" t="inlineStr">
         <is>
-          <t>thyssenkrupp AG</t>
+          <t>Viasat, Inc.</t>
         </is>
       </c>
       <c r="F186" s="26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G186" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H186" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I186" s="22" t="n">
-        <v>11091495472.63037</v>
+        <v>10236634112</v>
       </c>
       <c r="J186" s="23" t="inlineStr">
         <is>
@@ -25130,18 +25130,18 @@
         <v>6</v>
       </c>
       <c r="L186" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M186" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Weinstein-Stage2, Kullamagi-Breakout, StrongCoverage, Ly</t>
+          <t>KPIThreshold, LindyGrowth, MidCapGARP, ConcentratedSegments, LynchEV-G</t>
         </is>
       </c>
       <c r="N186" s="24" t="n">
-        <v>0.3574683544443799</v>
+        <v>0.3514893022857726</v>
       </c>
       <c r="O186" s="24" t="n">
-        <v>0.309572802</v>
+        <v>0.308496948</v>
       </c>
     </row>
     <row r="187" ht="16" customHeight="1">
@@ -25155,22 +25155,22 @@
       </c>
       <c r="D187" s="18" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>NESTE.HE</t>
         </is>
       </c>
       <c r="E187" s="19" t="inlineStr">
         <is>
-          <t>Viasat, Inc.</t>
+          <t>Neste Oyj</t>
         </is>
       </c>
       <c r="F187" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G187" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H187" s="16" t="inlineStr">
@@ -25179,7 +25179,7 @@
         </is>
       </c>
       <c r="I187" s="22" t="n">
-        <v>10236634112</v>
+        <v>29158572284.50196</v>
       </c>
       <c r="J187" s="23" t="inlineStr">
         <is>
@@ -25187,21 +25187,21 @@
         </is>
       </c>
       <c r="K187" s="22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L187" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M187" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LindyGrowth, MidCapGARP, ConcentratedSegments, LynchEV-G</t>
+          <t>KPIThreshold, Weinstein-Stage2, LynchEV-GY, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="N187" s="24" t="n">
-        <v>0.3514893022857726</v>
+        <v>0.3570336702455048</v>
       </c>
       <c r="O187" s="24" t="n">
-        <v>0.308496948</v>
+        <v>0.3070607272</v>
       </c>
     </row>
     <row r="188" ht="16" customHeight="1">
@@ -25215,31 +25215,31 @@
       </c>
       <c r="D188" s="18" t="inlineStr">
         <is>
-          <t>NESTE.HE</t>
+          <t>300136.SZ</t>
         </is>
       </c>
       <c r="E188" s="19" t="inlineStr">
         <is>
-          <t>Neste Oyj</t>
+          <t>Shenzhen Sunway Communication Co., Ltd.</t>
         </is>
       </c>
       <c r="F188" s="26" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G188" s="21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H188" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I188" s="22" t="n">
-        <v>29158572284.50196</v>
+        <v>8127548046.317627</v>
       </c>
       <c r="J188" s="23" t="inlineStr">
         <is>
@@ -25247,21 +25247,21 @@
         </is>
       </c>
       <c r="K188" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L188" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="L188" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="M188" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Weinstein-Stage2, LynchEV-GY, AsleepAtWheel-Beats</t>
+          <t>KPIThreshold, BAB-Becoming, LigerLaggingInflect</t>
         </is>
       </c>
       <c r="N188" s="24" t="n">
-        <v>0.3570336702455048</v>
+        <v>0.3536686037881107</v>
       </c>
       <c r="O188" s="24" t="n">
-        <v>0.3070607272</v>
+        <v>0.3065685716</v>
       </c>
     </row>
     <row r="189" ht="16" customHeight="1">
@@ -25275,17 +25275,17 @@
       </c>
       <c r="D189" s="18" t="inlineStr">
         <is>
-          <t>300136.SZ</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="E189" s="19" t="inlineStr">
         <is>
-          <t>Shenzhen Sunway Communication Co., Ltd.</t>
+          <t>Stmicroelectronics N.V.</t>
         </is>
       </c>
       <c r="F189" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G189" s="21" t="inlineStr">
@@ -25295,11 +25295,11 @@
       </c>
       <c r="H189" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I189" s="22" t="n">
-        <v>8127548046.317627</v>
+        <v>45943218176</v>
       </c>
       <c r="J189" s="23" t="inlineStr">
         <is>
@@ -25310,18 +25310,18 @@
         <v>3</v>
       </c>
       <c r="L189" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M189" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, BAB-Becoming, LigerLaggingInflect</t>
+          <t>LindyMargin, StrongCoverage, DiversifiedSegments</t>
         </is>
       </c>
       <c r="N189" s="24" t="n">
-        <v>0.3536686037881107</v>
+        <v>0.3581033513950115</v>
       </c>
       <c r="O189" s="24" t="n">
-        <v>0.3065685716</v>
+        <v>0.2755918934</v>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1">
@@ -25335,22 +25335,22 @@
       </c>
       <c r="D190" s="18" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>605289.SS</t>
         </is>
       </c>
       <c r="E190" s="19" t="inlineStr">
         <is>
-          <t>Stmicroelectronics N.V.</t>
+          <t>Shanghai Luoman Lighting Technologies Inc.</t>
         </is>
       </c>
       <c r="F190" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G190" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H190" s="16" t="inlineStr">
@@ -25359,7 +25359,7 @@
         </is>
       </c>
       <c r="I190" s="22" t="n">
-        <v>45943218176</v>
+        <v>2203383810.571838</v>
       </c>
       <c r="J190" s="23" t="inlineStr">
         <is>
@@ -25367,21 +25367,21 @@
         </is>
       </c>
       <c r="K190" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L190" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M190" s="21" t="inlineStr">
         <is>
-          <t>LindyMargin, StrongCoverage, DiversifiedSegments</t>
+          <t>RegimeCyclical, KPIThreshold, OwnerOperator, TenBaggerPath, TenBaggerP</t>
         </is>
       </c>
       <c r="N190" s="24" t="n">
-        <v>0.3581033513950115</v>
+        <v>0.3608547301929121</v>
       </c>
       <c r="O190" s="24" t="n">
-        <v>0.2755918934</v>
+        <v>0.273952194</v>
       </c>
     </row>
     <row r="191" ht="16" customHeight="1">
@@ -25395,22 +25395,22 @@
       </c>
       <c r="D191" s="18" t="inlineStr">
         <is>
-          <t>605289.SS</t>
+          <t>TSEM</t>
         </is>
       </c>
       <c r="E191" s="19" t="inlineStr">
         <is>
-          <t>Shanghai Luoman Lighting Technologies Inc.</t>
+          <t>Tower Semiconductor Ltd.</t>
         </is>
       </c>
       <c r="F191" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G191" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H191" s="16" t="inlineStr">
@@ -25419,7 +25419,7 @@
         </is>
       </c>
       <c r="I191" s="22" t="n">
-        <v>2203383810.571838</v>
+        <v>23908368384</v>
       </c>
       <c r="J191" s="23" t="inlineStr">
         <is>
@@ -25427,21 +25427,21 @@
         </is>
       </c>
       <c r="K191" s="22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L191" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M191" s="21" t="inlineStr">
         <is>
-          <t>RegimeCyclical, KPIThreshold, OwnerOperator, TenBaggerPath, TenBaggerP</t>
+          <t>LindyMargin, LindyFCF, TaxEfficient, StrongCoverage, BAB-Becoming, Lyn</t>
         </is>
       </c>
       <c r="N191" s="24" t="n">
-        <v>0.3608547301929121</v>
+        <v>0.3773631975480304</v>
       </c>
       <c r="O191" s="24" t="n">
-        <v>0.273952194</v>
+        <v>0.2599449568</v>
       </c>
     </row>
     <row r="192" ht="16" customHeight="1">
@@ -25455,17 +25455,17 @@
       </c>
       <c r="D192" s="18" t="inlineStr">
         <is>
-          <t>TSEM</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="E192" s="19" t="inlineStr">
         <is>
-          <t>Tower Semiconductor Ltd.</t>
+          <t>Nan Ya Printed Circuit Board Corporation</t>
         </is>
       </c>
       <c r="F192" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G192" s="21" t="inlineStr">
@@ -25475,11 +25475,11 @@
       </c>
       <c r="H192" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I192" s="22" t="n">
-        <v>23908368384</v>
+        <v>22105121921.95675</v>
       </c>
       <c r="J192" s="23" t="inlineStr">
         <is>
@@ -25487,21 +25487,21 @@
         </is>
       </c>
       <c r="K192" s="22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L192" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M192" s="21" t="inlineStr">
         <is>
-          <t>LindyMargin, LindyFCF, TaxEfficient, StrongCoverage, BAB-Becoming, Lyn</t>
+          <t>KPIThreshold, StrongCoverage, XR-ForensicFloorGrowth, AsleepAtWheel-Be</t>
         </is>
       </c>
       <c r="N192" s="24" t="n">
-        <v>0.3773631975480304</v>
+        <v>0.4799905507601829</v>
       </c>
       <c r="O192" s="24" t="n">
-        <v>0.2599449568</v>
+        <v>0.257349768</v>
       </c>
     </row>
     <row r="193" ht="16" customHeight="1">
@@ -25515,17 +25515,17 @@
       </c>
       <c r="D193" s="18" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>002281.SZ</t>
         </is>
       </c>
       <c r="E193" s="19" t="inlineStr">
         <is>
-          <t>Nan Ya Printed Circuit Board Corporation</t>
+          <t>Accelink Technologies Co., Ltd.</t>
         </is>
       </c>
       <c r="F193" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G193" s="21" t="inlineStr">
@@ -25539,7 +25539,7 @@
         </is>
       </c>
       <c r="I193" s="22" t="n">
-        <v>22105121921.95675</v>
+        <v>21702351509.64355</v>
       </c>
       <c r="J193" s="23" t="inlineStr">
         <is>
@@ -25547,21 +25547,21 @@
         </is>
       </c>
       <c r="K193" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L193" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="L193" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="M193" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, XR-ForensicFloorGrowth, AsleepAtWheel-Be</t>
+          <t>KPIThreshold, StrongCoverage, BAB-Becoming</t>
         </is>
       </c>
       <c r="N193" s="24" t="n">
-        <v>0.4799905507601829</v>
+        <v>0.3843302829211299</v>
       </c>
       <c r="O193" s="24" t="n">
-        <v>0.257349768</v>
+        <v>0.2476969</v>
       </c>
     </row>
     <row r="194" ht="16" customHeight="1">
@@ -25575,17 +25575,17 @@
       </c>
       <c r="D194" s="18" t="inlineStr">
         <is>
-          <t>002281.SZ</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="E194" s="19" t="inlineStr">
         <is>
-          <t>Accelink Technologies Co., Ltd.</t>
+          <t>Nanya Technology Corporation</t>
         </is>
       </c>
       <c r="F194" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G194" s="21" t="inlineStr">
@@ -25599,7 +25599,7 @@
         </is>
       </c>
       <c r="I194" s="22" t="n">
-        <v>21702351509.64355</v>
+        <v>48388455383.3959</v>
       </c>
       <c r="J194" s="23" t="inlineStr">
         <is>
@@ -25607,21 +25607,21 @@
         </is>
       </c>
       <c r="K194" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L194" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M194" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, BAB-Becoming</t>
+          <t>KPIThreshold, MidCapGARP, LynchEV-GY, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="N194" s="24" t="n">
-        <v>0.3843302829211299</v>
+        <v>0.4402029645397208</v>
       </c>
       <c r="O194" s="24" t="n">
-        <v>0.2476969</v>
+        <v>0.2379541353</v>
       </c>
     </row>
     <row r="195" ht="16" customHeight="1">
@@ -25635,22 +25635,22 @@
       </c>
       <c r="D195" s="18" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>TSUSF</t>
         </is>
       </c>
       <c r="E195" s="19" t="inlineStr">
         <is>
-          <t>Nanya Technology Corporation</t>
+          <t>Tsuruha Holdings Inc.</t>
         </is>
       </c>
       <c r="F195" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G195" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H195" s="16" t="inlineStr">
@@ -25659,7 +25659,7 @@
         </is>
       </c>
       <c r="I195" s="22" t="n">
-        <v>48388455383.3959</v>
+        <v>7815836672</v>
       </c>
       <c r="J195" s="23" t="inlineStr">
         <is>
@@ -25670,18 +25670,18 @@
         <v>4</v>
       </c>
       <c r="L195" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M195" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, MidCapGARP, LynchEV-GY, AsleepAtWheel-Beats</t>
+          <t>Weinstein-Stage2, LynchEV-GY, ExceptionalEVSG, TenBaggerPath</t>
         </is>
       </c>
       <c r="N195" s="24" t="n">
-        <v>0.4402029645397208</v>
+        <v>0.4779755963784002</v>
       </c>
       <c r="O195" s="24" t="n">
-        <v>0.2379541353</v>
+        <v>0.197537508</v>
       </c>
     </row>
     <row r="196" ht="16" customHeight="1">
@@ -25695,12 +25695,12 @@
       </c>
       <c r="D196" s="18" t="inlineStr">
         <is>
-          <t>TSUSF</t>
+          <t>PTGCF</t>
         </is>
       </c>
       <c r="E196" s="19" t="inlineStr">
         <is>
-          <t>Tsuruha Holdings Inc.</t>
+          <t>PTT Global Chemical Public Company Limited</t>
         </is>
       </c>
       <c r="F196" s="26" t="inlineStr">
@@ -25710,7 +25710,7 @@
       </c>
       <c r="G196" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H196" s="16" t="inlineStr">
@@ -25719,7 +25719,7 @@
         </is>
       </c>
       <c r="I196" s="22" t="n">
-        <v>7815836672</v>
+        <v>6633611264</v>
       </c>
       <c r="J196" s="23" t="inlineStr">
         <is>
@@ -25727,21 +25727,21 @@
         </is>
       </c>
       <c r="K196" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L196" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M196" s="21" t="inlineStr">
         <is>
-          <t>LynchEV-GY, ExceptionalEVSG, TenBaggerPath</t>
+          <t>KPIThreshold, LynchEV-GY, Forensic-PayoutConfirmed, Forensic-SelfFunde</t>
         </is>
       </c>
       <c r="N196" s="24" t="n">
-        <v>0.4779755963784002</v>
+        <v>0.3707413323498978</v>
       </c>
       <c r="O196" s="24" t="n">
-        <v>0.197537508</v>
+        <v>0.156690258</v>
       </c>
     </row>
     <row r="197" ht="16" customHeight="1">
@@ -25755,12 +25755,12 @@
       </c>
       <c r="D197" s="18" t="inlineStr">
         <is>
-          <t>PTGCF</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="E197" s="19" t="inlineStr">
         <is>
-          <t>PTT Global Chemical Public Company Limited</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="F197" s="26" t="inlineStr">
@@ -25770,16 +25770,16 @@
       </c>
       <c r="G197" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H197" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I197" s="22" t="n">
-        <v>6633611264</v>
+        <v>83154591744</v>
       </c>
       <c r="J197" s="23" t="inlineStr">
         <is>
@@ -25794,78 +25794,18 @@
       </c>
       <c r="M197" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchEV-GY, Forensic-PayoutConfirmed, Forensic-SelfFunde</t>
+          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage, GeographicGlobal, Fa</t>
         </is>
       </c>
       <c r="N197" s="24" t="n">
-        <v>0.3707413323498978</v>
+        <v>0.3618874775226934</v>
       </c>
       <c r="O197" s="24" t="n">
-        <v>0.156690258</v>
-      </c>
-    </row>
-    <row r="198" ht="16" customHeight="1">
-      <c r="B198" s="16" t="n">
-        <v>195</v>
-      </c>
-      <c r="C198" s="17" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="D198" s="18" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="E198" s="19" t="inlineStr">
-        <is>
-          <t>Lumentum Holdings Inc.</t>
-        </is>
-      </c>
-      <c r="F198" s="26" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G198" s="21" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="H198" s="16" t="inlineStr">
-        <is>
-          <t>Large Cap</t>
-        </is>
-      </c>
-      <c r="I198" s="22" t="n">
-        <v>83154591744</v>
-      </c>
-      <c r="J198" s="23" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="K198" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="L198" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M198" s="21" t="inlineStr">
-        <is>
-          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage, GeographicGlobal, Fa</t>
-        </is>
-      </c>
-      <c r="N198" s="24" t="n">
-        <v>0.3618874775226934</v>
-      </c>
-      <c r="O198" s="24" t="n">
         <v>0.153989778</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:O198"/>
+  <autoFilter ref="B3:O197"/>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
@@ -30274,14 +30214,14 @@
         </is>
       </c>
       <c r="K75" s="22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M75" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, LynchEV-GY, XR-AssetOwnerCatalyst, XR-L</t>
+          <t>NarrativeLag, CapitalReturner, LynchEV-GY</t>
         </is>
       </c>
       <c r="N75" s="24" t="n">
@@ -33550,7 +33490,7 @@
         </is>
       </c>
       <c r="K130" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L130" s="22" t="n">
         <v>2</v>
@@ -39026,31 +38966,31 @@
       </c>
       <c r="D222" s="18" t="inlineStr">
         <is>
-          <t>AYYLF</t>
+          <t>T14.SI</t>
         </is>
       </c>
       <c r="E222" s="19" t="inlineStr">
         <is>
-          <t>Ayala Corporation</t>
+          <t>Tianjin Zhong Xin Pharmaceutical Group Corporation Limited</t>
         </is>
       </c>
       <c r="F222" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H222" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I222" s="22" t="n">
-        <v>5110343680</v>
+        <v>3199373568</v>
       </c>
       <c r="J222" s="23" t="inlineStr">
         <is>
@@ -39058,21 +38998,21 @@
         </is>
       </c>
       <c r="K222" s="22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L222" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M222" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, NetCashReturner, LynchEV-GY, XR-CyclicalTrou</t>
+          <t>CapitalReturner, BalanceSheetReturn, StrongCoverage, NegativeEV-Value,</t>
         </is>
       </c>
       <c r="N222" s="24" t="n">
-        <v>0.3289881211524816</v>
+        <v>0.4517436757803224</v>
       </c>
       <c r="O222" s="24" t="n">
-        <v>0.45203576</v>
+        <v>0.4519421004</v>
       </c>
     </row>
     <row r="223" ht="16" customHeight="1">
@@ -39086,31 +39026,31 @@
       </c>
       <c r="D223" s="18" t="inlineStr">
         <is>
-          <t>T14.SI</t>
+          <t>DFKCY</t>
         </is>
       </c>
       <c r="E223" s="19" t="inlineStr">
         <is>
-          <t>Tianjin Zhong Xin Pharmaceutical Group Corporation Limited</t>
+          <t>Daifuku Co., Ltd.</t>
         </is>
       </c>
       <c r="F223" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G223" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H223" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I223" s="22" t="n">
-        <v>3199373568</v>
+        <v>13645363200</v>
       </c>
       <c r="J223" s="23" t="inlineStr">
         <is>
@@ -39121,18 +39061,18 @@
         <v>5</v>
       </c>
       <c r="L223" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M223" s="21" t="inlineStr">
         <is>
-          <t>CapitalReturner, BalanceSheetReturn, StrongCoverage, NegativeEV-Value,</t>
+          <t xml:space="preserve">FixedCost+DemandShock, LargeCapQuality, StrongCoverage, BAB-Becoming, </t>
         </is>
       </c>
       <c r="N223" s="24" t="n">
-        <v>0.4517436757803224</v>
+        <v>0.4232151678705352</v>
       </c>
       <c r="O223" s="24" t="n">
-        <v>0.4519421004</v>
+        <v>0.4515879264</v>
       </c>
     </row>
     <row r="224" ht="16" customHeight="1">
@@ -39146,22 +39086,22 @@
       </c>
       <c r="D224" s="18" t="inlineStr">
         <is>
-          <t>DFKCY</t>
+          <t>012330.KS</t>
         </is>
       </c>
       <c r="E224" s="19" t="inlineStr">
         <is>
-          <t>Daifuku Co., Ltd.</t>
+          <t>Hyundai Mobis Co.,Ltd</t>
         </is>
       </c>
       <c r="F224" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G224" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H224" s="16" t="inlineStr">
@@ -39170,7 +39110,7 @@
         </is>
       </c>
       <c r="I224" s="22" t="n">
-        <v>13645363200</v>
+        <v>24236389593.5349</v>
       </c>
       <c r="J224" s="23" t="inlineStr">
         <is>
@@ -39178,21 +39118,21 @@
         </is>
       </c>
       <c r="K224" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L224" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M224" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FixedCost+DemandShock, LargeCapQuality, StrongCoverage, BAB-Becoming, </t>
+          <t>FixedCost+DemandShock, DeadOption, OwnerOperator, StrongCoverage, Lync</t>
         </is>
       </c>
       <c r="N224" s="24" t="n">
-        <v>0.4232151678705352</v>
+        <v>0.4186883604081197</v>
       </c>
       <c r="O224" s="24" t="n">
-        <v>0.4515879264</v>
+        <v>0.4515592523999999</v>
       </c>
     </row>
     <row r="225" ht="16" customHeight="1">
@@ -39206,31 +39146,31 @@
       </c>
       <c r="D225" s="18" t="inlineStr">
         <is>
-          <t>012330.KS</t>
+          <t>RSW.L</t>
         </is>
       </c>
       <c r="E225" s="19" t="inlineStr">
         <is>
-          <t>Hyundai Mobis Co.,Ltd</t>
+          <t>Renishaw plc</t>
         </is>
       </c>
       <c r="F225" s="26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G225" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H225" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I225" s="22" t="n">
-        <v>24236389593.5349</v>
+        <v>4990076432.360779</v>
       </c>
       <c r="J225" s="23" t="inlineStr">
         <is>
@@ -39238,21 +39178,21 @@
         </is>
       </c>
       <c r="K225" s="22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L225" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M225" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, DeadOption, OwnerOperator, StrongCoverage, Lync</t>
+          <t>OwnerOperator, Weinstein-Stage2, StrongCoverage, BAB-Becoming, Bottlen</t>
         </is>
       </c>
       <c r="N225" s="24" t="n">
-        <v>0.4186883604081197</v>
+        <v>0.4437992173207551</v>
       </c>
       <c r="O225" s="24" t="n">
-        <v>0.4515592523999999</v>
+        <v>0.4515036000000001</v>
       </c>
     </row>
     <row r="226" ht="16" customHeight="1">
@@ -39266,31 +39206,31 @@
       </c>
       <c r="D226" s="18" t="inlineStr">
         <is>
-          <t>RSW.L</t>
+          <t>DAIUF</t>
         </is>
       </c>
       <c r="E226" s="19" t="inlineStr">
         <is>
-          <t>Renishaw plc</t>
+          <t>Daifuku Co., Ltd.</t>
         </is>
       </c>
       <c r="F226" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G226" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H226" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I226" s="22" t="n">
-        <v>4990076432.360779</v>
+        <v>13448084480</v>
       </c>
       <c r="J226" s="23" t="inlineStr">
         <is>
@@ -39305,14 +39245,14 @@
       </c>
       <c r="M226" s="21" t="inlineStr">
         <is>
-          <t>OwnerOperator, Weinstein-Stage2, StrongCoverage, BAB-Becoming, Bottlen</t>
+          <t xml:space="preserve">FixedCost+DemandShock, LargeCapQuality, StrongCoverage, BAB-Becoming, </t>
         </is>
       </c>
       <c r="N226" s="24" t="n">
-        <v>0.4437992173207551</v>
+        <v>0.4263484149507274</v>
       </c>
       <c r="O226" s="24" t="n">
-        <v>0.4515036000000001</v>
+        <v>0.4510941784</v>
       </c>
     </row>
     <row r="227" ht="16" customHeight="1">
@@ -39326,12 +39266,12 @@
       </c>
       <c r="D227" s="18" t="inlineStr">
         <is>
-          <t>DAIUF</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="E227" s="19" t="inlineStr">
         <is>
-          <t>Daifuku Co., Ltd.</t>
+          <t>The Marzetti Company Common Stock</t>
         </is>
       </c>
       <c r="F227" s="26" t="inlineStr">
@@ -39341,16 +39281,16 @@
       </c>
       <c r="G227" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H227" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I227" s="22" t="n">
-        <v>13448084480</v>
+        <v>2839628544</v>
       </c>
       <c r="J227" s="23" t="inlineStr">
         <is>
@@ -39358,21 +39298,21 @@
         </is>
       </c>
       <c r="K227" s="22" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L227" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M227" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FixedCost+DemandShock, LargeCapQuality, StrongCoverage, BAB-Becoming, </t>
+          <t xml:space="preserve">NarrativeLag, CapitalDiscipline, CashReinvest, LindyMargin, LindyFCF, </t>
         </is>
       </c>
       <c r="N227" s="24" t="n">
-        <v>0.4263484149507274</v>
+        <v>0.4051250823000478</v>
       </c>
       <c r="O227" s="24" t="n">
-        <v>0.4510941784</v>
+        <v>0.4508804358000001</v>
       </c>
     </row>
     <row r="228" ht="16" customHeight="1">
@@ -39386,12 +39326,12 @@
       </c>
       <c r="D228" s="18" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>VIPS</t>
         </is>
       </c>
       <c r="E228" s="19" t="inlineStr">
         <is>
-          <t>The Marzetti Company Common Stock</t>
+          <t>Vipshop Holdings Limited</t>
         </is>
       </c>
       <c r="F228" s="26" t="inlineStr">
@@ -39401,16 +39341,16 @@
       </c>
       <c r="G228" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H228" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I228" s="22" t="n">
-        <v>2839628544</v>
+        <v>5929485312</v>
       </c>
       <c r="J228" s="23" t="inlineStr">
         <is>
@@ -39418,21 +39358,21 @@
         </is>
       </c>
       <c r="K228" s="22" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L228" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M228" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, CapitalDiscipline, CashReinvest, LindyMargin, LindyFCF, </t>
+          <t>CapitalDiscipline, LindyFCF, NoDilution, BuybackCompounder, CashQualit</t>
         </is>
       </c>
       <c r="N228" s="24" t="n">
-        <v>0.4051250823000478</v>
+        <v>0.3864873720390753</v>
       </c>
       <c r="O228" s="24" t="n">
-        <v>0.4508804358000001</v>
+        <v>0.4508448</v>
       </c>
     </row>
     <row r="229" ht="16" customHeight="1">
@@ -39446,31 +39386,31 @@
       </c>
       <c r="D229" s="18" t="inlineStr">
         <is>
-          <t>VIPS</t>
+          <t>ENKAI.IS</t>
         </is>
       </c>
       <c r="E229" s="19" t="inlineStr">
         <is>
-          <t>Vipshop Holdings Limited</t>
+          <t>Enka Insaat ve Sanayi A.S.</t>
         </is>
       </c>
       <c r="F229" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="G229" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H229" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I229" s="22" t="n">
-        <v>5929485312</v>
+        <v>11600218269.45748</v>
       </c>
       <c r="J229" s="23" t="inlineStr">
         <is>
@@ -39478,21 +39418,21 @@
         </is>
       </c>
       <c r="K229" s="22" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L229" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M229" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, LindyFCF, NoDilution, BuybackCompounder, CashQualit</t>
+          <t>QuietCompounder, OwnerOperator, LargeCapQuality, CapitalReturner, Bala</t>
         </is>
       </c>
       <c r="N229" s="24" t="n">
-        <v>0.3864873720390753</v>
+        <v>0.3794202195050716</v>
       </c>
       <c r="O229" s="24" t="n">
-        <v>0.4508448</v>
+        <v>0.4503777</v>
       </c>
     </row>
     <row r="230" ht="16" customHeight="1">
@@ -39506,22 +39446,22 @@
       </c>
       <c r="D230" s="18" t="inlineStr">
         <is>
-          <t>ENKAI.IS</t>
+          <t>2096.HK</t>
         </is>
       </c>
       <c r="E230" s="19" t="inlineStr">
         <is>
-          <t>Enka Insaat ve Sanayi A.S.</t>
+          <t>Simcere Pharmaceutical Group Limited</t>
         </is>
       </c>
       <c r="F230" s="26" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G230" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H230" s="16" t="inlineStr">
@@ -39530,7 +39470,7 @@
         </is>
       </c>
       <c r="I230" s="22" t="n">
-        <v>11600218269.45748</v>
+        <v>3616664637.675292</v>
       </c>
       <c r="J230" s="23" t="inlineStr">
         <is>
@@ -39538,21 +39478,21 @@
         </is>
       </c>
       <c r="K230" s="22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L230" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M230" s="21" t="inlineStr">
         <is>
-          <t>QuietCompounder, OwnerOperator, LargeCapQuality, CapitalReturner, Bala</t>
+          <t>NarrativeLag, QuietCompounder, OwnerOperator, MidCapGARP, StrongCovera</t>
         </is>
       </c>
       <c r="N230" s="24" t="n">
-        <v>0.3794202195050716</v>
+        <v>0.4039644086727061</v>
       </c>
       <c r="O230" s="24" t="n">
-        <v>0.4503777</v>
+        <v>0.4492246208</v>
       </c>
     </row>
     <row r="231" ht="16" customHeight="1">
@@ -39566,17 +39506,17 @@
       </c>
       <c r="D231" s="18" t="inlineStr">
         <is>
-          <t>2096.HK</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="E231" s="19" t="inlineStr">
         <is>
-          <t>Simcere Pharmaceutical Group Limited</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="F231" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" s="21" t="inlineStr">
@@ -39586,11 +39526,11 @@
       </c>
       <c r="H231" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I231" s="22" t="n">
-        <v>3616664637.675292</v>
+        <v>31332263936</v>
       </c>
       <c r="J231" s="23" t="inlineStr">
         <is>
@@ -39598,21 +39538,21 @@
         </is>
       </c>
       <c r="K231" s="22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L231" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M231" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, QuietCompounder, OwnerOperator, MidCapGARP, StrongCovera</t>
+          <t>NarrativeLag, CapitalDiscipline, DurableReinvest, CheapPerROIIC, Lindy</t>
         </is>
       </c>
       <c r="N231" s="24" t="n">
-        <v>0.4039644086727061</v>
+        <v>0.4215188071362087</v>
       </c>
       <c r="O231" s="24" t="n">
-        <v>0.4492246208</v>
+        <v>0.44916992</v>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1">
@@ -39626,31 +39566,31 @@
       </c>
       <c r="D232" s="18" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>CAI.VI</t>
         </is>
       </c>
       <c r="E232" s="19" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>CA Immobilien Anlagen AG</t>
         </is>
       </c>
       <c r="F232" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G232" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H232" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I232" s="22" t="n">
-        <v>31332263936</v>
+        <v>2385109775.233521</v>
       </c>
       <c r="J232" s="23" t="inlineStr">
         <is>
@@ -39658,21 +39598,17 @@
         </is>
       </c>
       <c r="K232" s="22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L232" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M232" s="21" t="inlineStr">
-        <is>
-          <t>NarrativeLag, CapitalDiscipline, DurableReinvest, CheapPerROIIC, Lindy</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M232" s="21" t="inlineStr"/>
       <c r="N232" s="24" t="n">
-        <v>0.4215188071362087</v>
+        <v>0.4009641502636362</v>
       </c>
       <c r="O232" s="24" t="n">
-        <v>0.44916992</v>
+        <v>0.4487032712</v>
       </c>
     </row>
     <row r="233" ht="16" customHeight="1">
@@ -39686,22 +39622,22 @@
       </c>
       <c r="D233" s="18" t="inlineStr">
         <is>
-          <t>CAI.VI</t>
+          <t>BEKSF</t>
         </is>
       </c>
       <c r="E233" s="19" t="inlineStr">
         <is>
-          <t>CA Immobilien Anlagen AG</t>
+          <t>Bekaert SA</t>
         </is>
       </c>
       <c r="F233" s="26" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G233" s="21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H233" s="16" t="inlineStr">
@@ -39710,7 +39646,7 @@
         </is>
       </c>
       <c r="I233" s="22" t="n">
-        <v>2385109775.233521</v>
+        <v>2045848064</v>
       </c>
       <c r="J233" s="23" t="inlineStr">
         <is>
@@ -39718,17 +39654,21 @@
         </is>
       </c>
       <c r="K233" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L233" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M233" s="21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M233" s="21" t="inlineStr">
+        <is>
+          <t>CapitalDiscipline, Forensic-PayoutConfirmed, Forensic-CannibalDiscount</t>
+        </is>
+      </c>
       <c r="N233" s="24" t="n">
-        <v>0.4009641502636362</v>
+        <v>0.3870411177909634</v>
       </c>
       <c r="O233" s="24" t="n">
-        <v>0.4487032712</v>
+        <v>0.4485883886000001</v>
       </c>
     </row>
     <row r="234" ht="16" customHeight="1">
@@ -39742,12 +39682,12 @@
       </c>
       <c r="D234" s="18" t="inlineStr">
         <is>
-          <t>BEKSF</t>
+          <t>NTIOF</t>
         </is>
       </c>
       <c r="E234" s="19" t="inlineStr">
         <is>
-          <t>Bekaert SA</t>
+          <t>National Bank of Canada</t>
         </is>
       </c>
       <c r="F234" s="26" t="inlineStr">
@@ -39757,16 +39697,16 @@
       </c>
       <c r="G234" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H234" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I234" s="22" t="n">
-        <v>2045848064</v>
+        <v>58451349504</v>
       </c>
       <c r="J234" s="23" t="inlineStr">
         <is>
@@ -39777,18 +39717,18 @@
         <v>3</v>
       </c>
       <c r="L234" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M234" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, Forensic-PayoutConfirmed, Forensic-CannibalDiscount</t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="N234" s="24" t="n">
-        <v>0.3870411177909634</v>
+        <v>0.3300708330172057</v>
       </c>
       <c r="O234" s="24" t="n">
-        <v>0.4485883886000001</v>
+        <v>0.448525755</v>
       </c>
     </row>
     <row r="235" ht="16" customHeight="1">
@@ -39802,12 +39742,12 @@
       </c>
       <c r="D235" s="18" t="inlineStr">
         <is>
-          <t>NTIOF</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="E235" s="19" t="inlineStr">
         <is>
-          <t>National Bank of Canada</t>
+          <t>SEI Investments Company</t>
         </is>
       </c>
       <c r="F235" s="26" t="inlineStr">
@@ -39822,11 +39762,11 @@
       </c>
       <c r="H235" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I235" s="22" t="n">
-        <v>58451349504</v>
+        <v>12833651712</v>
       </c>
       <c r="J235" s="23" t="inlineStr">
         <is>
@@ -39837,18 +39777,18 @@
         <v>3</v>
       </c>
       <c r="L235" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M235" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats</t>
+          <t>Weinstein-Stage2, AsleepAtWheel-Beats, AsleepUnrerated-BeatsNoRerate</t>
         </is>
       </c>
       <c r="N235" s="24" t="n">
-        <v>0.3300708330172057</v>
+        <v>0.3989498656675633</v>
       </c>
       <c r="O235" s="24" t="n">
-        <v>0.448525755</v>
+        <v>0.4484740360000001</v>
       </c>
     </row>
     <row r="236" ht="16" customHeight="1">
@@ -39862,22 +39802,22 @@
       </c>
       <c r="D236" s="18" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>600598.SS</t>
         </is>
       </c>
       <c r="E236" s="19" t="inlineStr">
         <is>
-          <t>SEI Investments Company</t>
+          <t>Heilongjiang Agriculture Company Limited</t>
         </is>
       </c>
       <c r="F236" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G236" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H236" s="16" t="inlineStr">
@@ -39886,7 +39826,7 @@
         </is>
       </c>
       <c r="I236" s="22" t="n">
-        <v>12833651712</v>
+        <v>3426346114.91687</v>
       </c>
       <c r="J236" s="23" t="inlineStr">
         <is>
@@ -39897,18 +39837,18 @@
         <v>3</v>
       </c>
       <c r="L236" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M236" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, AsleepAtWheel-Beats, AsleepUnrerated-BeatsNoRerate</t>
+          <t>BalanceSheetReturn, NetCashReturner, StrongCoverage</t>
         </is>
       </c>
       <c r="N236" s="24" t="n">
-        <v>0.3989498656675633</v>
+        <v>0.3676757349217148</v>
       </c>
       <c r="O236" s="24" t="n">
-        <v>0.4484740360000001</v>
+        <v>0.4478987663999999</v>
       </c>
     </row>
     <row r="237" ht="16" customHeight="1">
@@ -39922,22 +39862,22 @@
       </c>
       <c r="D237" s="18" t="inlineStr">
         <is>
-          <t>600598.SS</t>
+          <t>ENPH</t>
         </is>
       </c>
       <c r="E237" s="19" t="inlineStr">
         <is>
-          <t>Heilongjiang Agriculture Company Limited</t>
+          <t>Enphase Energy, Inc.</t>
         </is>
       </c>
       <c r="F237" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G237" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H237" s="16" t="inlineStr">
@@ -39946,7 +39886,7 @@
         </is>
       </c>
       <c r="I237" s="22" t="n">
-        <v>3426346114.91687</v>
+        <v>4803457536</v>
       </c>
       <c r="J237" s="23" t="inlineStr">
         <is>
@@ -39954,21 +39894,21 @@
         </is>
       </c>
       <c r="K237" s="22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L237" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M237" s="21" t="inlineStr">
         <is>
-          <t>BalanceSheetReturn, NetCashReturner, StrongCoverage</t>
+          <t>LindyMargin, LindyFCF, NoDilution, BuybackCompounder, CashQuality, Str</t>
         </is>
       </c>
       <c r="N237" s="24" t="n">
-        <v>0.3676757349217148</v>
+        <v>0.3827075287295285</v>
       </c>
       <c r="O237" s="24" t="n">
-        <v>0.4478987663999999</v>
+        <v>0.4477681</v>
       </c>
     </row>
     <row r="238" ht="16" customHeight="1">
@@ -39982,12 +39922,12 @@
       </c>
       <c r="D238" s="18" t="inlineStr">
         <is>
-          <t>ENPH</t>
+          <t>BFH</t>
         </is>
       </c>
       <c r="E238" s="19" t="inlineStr">
         <is>
-          <t>Enphase Energy, Inc.</t>
+          <t>Bread Financial Holdings, Inc.</t>
         </is>
       </c>
       <c r="F238" s="26" t="inlineStr">
@@ -39997,7 +39937,7 @@
       </c>
       <c r="G238" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H238" s="16" t="inlineStr">
@@ -40006,7 +39946,7 @@
         </is>
       </c>
       <c r="I238" s="22" t="n">
-        <v>4803457536</v>
+        <v>4086657536</v>
       </c>
       <c r="J238" s="23" t="inlineStr">
         <is>
@@ -40014,21 +39954,21 @@
         </is>
       </c>
       <c r="K238" s="22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L238" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M238" s="21" t="inlineStr">
         <is>
-          <t>LindyMargin, LindyFCF, NoDilution, BuybackCompounder, CashQuality, Str</t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, ReratingConfirmed-52</t>
         </is>
       </c>
       <c r="N238" s="24" t="n">
-        <v>0.3827075287295285</v>
+        <v>0.463623090803771</v>
       </c>
       <c r="O238" s="24" t="n">
-        <v>0.4477681</v>
+        <v>0.447512</v>
       </c>
     </row>
     <row r="239" ht="16" customHeight="1">
@@ -40042,22 +39982,22 @@
       </c>
       <c r="D239" s="18" t="inlineStr">
         <is>
-          <t>BFH</t>
+          <t>2181.T</t>
         </is>
       </c>
       <c r="E239" s="19" t="inlineStr">
         <is>
-          <t>Bread Financial Holdings, Inc.</t>
+          <t>PERSOL HOLDINGS CO. LTD.</t>
         </is>
       </c>
       <c r="F239" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G239" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H239" s="16" t="inlineStr">
@@ -40066,7 +40006,7 @@
         </is>
       </c>
       <c r="I239" s="22" t="n">
-        <v>4086657536</v>
+        <v>3950947633.189528</v>
       </c>
       <c r="J239" s="23" t="inlineStr">
         <is>
@@ -40074,21 +40014,21 @@
         </is>
       </c>
       <c r="K239" s="22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L239" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M239" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, ReratingConfirmed-52</t>
+          <t>FixedCost+DemandShock, CapitalDiscipline, QuietCompounder, OwnerOperat</t>
         </is>
       </c>
       <c r="N239" s="24" t="n">
-        <v>0.463623090803771</v>
+        <v>0.4000356204889777</v>
       </c>
       <c r="O239" s="24" t="n">
-        <v>0.447512</v>
+        <v>0.4472677536</v>
       </c>
     </row>
     <row r="240" ht="16" customHeight="1">
@@ -40102,17 +40042,17 @@
       </c>
       <c r="D240" s="18" t="inlineStr">
         <is>
-          <t>2181.T</t>
+          <t>HEI</t>
         </is>
       </c>
       <c r="E240" s="19" t="inlineStr">
         <is>
-          <t>PERSOL HOLDINGS CO. LTD.</t>
+          <t>Heico Corporation</t>
         </is>
       </c>
       <c r="F240" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G240" s="21" t="inlineStr">
@@ -40122,11 +40062,11 @@
       </c>
       <c r="H240" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I240" s="22" t="n">
-        <v>3950947633.189528</v>
+        <v>44163342336</v>
       </c>
       <c r="J240" s="23" t="inlineStr">
         <is>
@@ -40134,21 +40074,21 @@
         </is>
       </c>
       <c r="K240" s="22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L240" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M240" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, CapitalDiscipline, QuietCompounder, OwnerOperat</t>
+          <t>DurableReinvest, CashReinvest, LindyMargin, LindyFCF, NoDilution, Quie</t>
         </is>
       </c>
       <c r="N240" s="24" t="n">
-        <v>0.4000356204889777</v>
+        <v>0.4146045820041666</v>
       </c>
       <c r="O240" s="24" t="n">
-        <v>0.4472677536</v>
+        <v>0.4470265119999999</v>
       </c>
     </row>
     <row r="241" ht="16" customHeight="1">
@@ -40162,12 +40102,12 @@
       </c>
       <c r="D241" s="18" t="inlineStr">
         <is>
-          <t>HEI</t>
+          <t>CCOZY</t>
         </is>
       </c>
       <c r="E241" s="19" t="inlineStr">
         <is>
-          <t>Heico Corporation</t>
+          <t>China Coal Energy Company Limited</t>
         </is>
       </c>
       <c r="F241" s="26" t="inlineStr">
@@ -40177,7 +40117,7 @@
       </c>
       <c r="G241" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H241" s="16" t="inlineStr">
@@ -40186,7 +40126,7 @@
         </is>
       </c>
       <c r="I241" s="22" t="n">
-        <v>44163342336</v>
+        <v>20219461632</v>
       </c>
       <c r="J241" s="23" t="inlineStr">
         <is>
@@ -40194,21 +40134,21 @@
         </is>
       </c>
       <c r="K241" s="22" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L241" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M241" s="21" t="inlineStr">
         <is>
-          <t>DurableReinvest, CashReinvest, LindyMargin, LindyFCF, NoDilution, Quie</t>
+          <t>LargeCapQuality, StrongCoverage, LynchPEGY, CashAdjPE-NegOrCheap, Fore</t>
         </is>
       </c>
       <c r="N241" s="24" t="n">
-        <v>0.4146045820041666</v>
+        <v>0.428133266441641</v>
       </c>
       <c r="O241" s="24" t="n">
-        <v>0.4470265119999999</v>
+        <v>0.4469712000000001</v>
       </c>
     </row>
     <row r="242" ht="16" customHeight="1">
@@ -40222,12 +40162,12 @@
       </c>
       <c r="D242" s="18" t="inlineStr">
         <is>
-          <t>CCOZY</t>
+          <t>AYYLF</t>
         </is>
       </c>
       <c r="E242" s="19" t="inlineStr">
         <is>
-          <t>China Coal Energy Company Limited</t>
+          <t>Ayala Corporation</t>
         </is>
       </c>
       <c r="F242" s="26" t="inlineStr">
@@ -40237,7 +40177,7 @@
       </c>
       <c r="G242" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H242" s="16" t="inlineStr">
@@ -40246,7 +40186,7 @@
         </is>
       </c>
       <c r="I242" s="22" t="n">
-        <v>20219461632</v>
+        <v>5110343680</v>
       </c>
       <c r="J242" s="23" t="inlineStr">
         <is>
@@ -40257,18 +40197,18 @@
         <v>6</v>
       </c>
       <c r="L242" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M242" s="21" t="inlineStr">
         <is>
-          <t>LargeCapQuality, StrongCoverage, LynchPEGY, CashAdjPE-NegOrCheap, Fore</t>
+          <t>NarrativeLag, MidCapGARP, NetCashReturner, LynchEV-GY, XR-CyclicalTrou</t>
         </is>
       </c>
       <c r="N242" s="24" t="n">
-        <v>0.428133266441641</v>
+        <v>0.3289881211524816</v>
       </c>
       <c r="O242" s="24" t="n">
-        <v>0.4469712000000001</v>
+        <v>0.446969842</v>
       </c>
     </row>
     <row r="243" ht="16" customHeight="1">
@@ -40942,12 +40882,12 @@
       </c>
       <c r="D254" s="18" t="inlineStr">
         <is>
-          <t>OR.TO</t>
+          <t>NA.TO</t>
         </is>
       </c>
       <c r="E254" s="19" t="inlineStr">
         <is>
-          <t>OSISKO GOLD ROYALTIES LTD</t>
+          <t>National Bank of Canada</t>
         </is>
       </c>
       <c r="F254" s="26" t="inlineStr">
@@ -40957,16 +40897,16 @@
       </c>
       <c r="G254" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H254" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I254" s="22" t="n">
-        <v>6705157590.494202</v>
+        <v>58529043043.79883</v>
       </c>
       <c r="J254" s="23" t="inlineStr">
         <is>
@@ -40974,21 +40914,21 @@
         </is>
       </c>
       <c r="K254" s="22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L254" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M254" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, RegimeCyclical, LynchPEGY, LynchEV-GY, AsleepAt</t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="N254" s="24" t="n">
-        <v>0.4176102766225654</v>
+        <v>0.325166214075872</v>
       </c>
       <c r="O254" s="24" t="n">
-        <v>0.4438024991999999</v>
+        <v>0.4437136569999999</v>
       </c>
     </row>
     <row r="255" ht="16" customHeight="1">
@@ -41002,22 +40942,22 @@
       </c>
       <c r="D255" s="18" t="inlineStr">
         <is>
-          <t>NA.TO</t>
+          <t>MAHMF</t>
         </is>
       </c>
       <c r="E255" s="19" t="inlineStr">
         <is>
-          <t>National Bank of Canada</t>
+          <t>Mahindra &amp; Mahindra Ltd. Sponsored GDR RegS</t>
         </is>
       </c>
       <c r="F255" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G255" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H255" s="16" t="inlineStr">
@@ -41026,7 +40966,7 @@
         </is>
       </c>
       <c r="I255" s="22" t="n">
-        <v>58529043043.79883</v>
+        <v>40525725696</v>
       </c>
       <c r="J255" s="23" t="inlineStr">
         <is>
@@ -41034,21 +40974,21 @@
         </is>
       </c>
       <c r="K255" s="22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L255" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M255" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats</t>
+          <t>KPIThreshold, BalanceSheetReturn, NetCashReturner, LynchPEGY, LigerLag</t>
         </is>
       </c>
       <c r="N255" s="24" t="n">
-        <v>0.325166214075872</v>
+        <v>0.3376313694615844</v>
       </c>
       <c r="O255" s="24" t="n">
-        <v>0.4437136569999999</v>
+        <v>0.4433734368</v>
       </c>
     </row>
     <row r="256" ht="16" customHeight="1">
@@ -41062,12 +41002,12 @@
       </c>
       <c r="D256" s="18" t="inlineStr">
         <is>
-          <t>MAHMF</t>
+          <t>SNEJF</t>
         </is>
       </c>
       <c r="E256" s="19" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd. Sponsored GDR RegS</t>
+          <t>Sony Group Corporation</t>
         </is>
       </c>
       <c r="F256" s="26" t="inlineStr">
@@ -41077,7 +41017,7 @@
       </c>
       <c r="G256" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H256" s="16" t="inlineStr">
@@ -41086,7 +41026,7 @@
         </is>
       </c>
       <c r="I256" s="22" t="n">
-        <v>40525725696</v>
+        <v>138985766912</v>
       </c>
       <c r="J256" s="23" t="inlineStr">
         <is>
@@ -41094,21 +41034,21 @@
         </is>
       </c>
       <c r="K256" s="22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L256" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M256" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, BalanceSheetReturn, NetCashReturner, LynchPEGY, LigerLag</t>
+          <t>LargeCapQuality, StrongCoverage, BAB-Becoming, LynchPEGY, LigerLagging</t>
         </is>
       </c>
       <c r="N256" s="24" t="n">
-        <v>0.3376313694615844</v>
+        <v>0.3729587118824605</v>
       </c>
       <c r="O256" s="24" t="n">
-        <v>0.4433734368</v>
+        <v>0.44304465</v>
       </c>
     </row>
     <row r="257" ht="16" customHeight="1">
@@ -41122,31 +41062,31 @@
       </c>
       <c r="D257" s="18" t="inlineStr">
         <is>
-          <t>SNEJF</t>
+          <t>0270.HK</t>
         </is>
       </c>
       <c r="E257" s="19" t="inlineStr">
         <is>
-          <t>Sony Group Corporation</t>
+          <t>Guangdong Investment Limited</t>
         </is>
       </c>
       <c r="F257" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G257" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="H257" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I257" s="22" t="n">
-        <v>138985766912</v>
+        <v>7128725959.103208</v>
       </c>
       <c r="J257" s="23" t="inlineStr">
         <is>
@@ -41154,21 +41094,21 @@
         </is>
       </c>
       <c r="K257" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L257" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M257" s="21" t="inlineStr">
         <is>
-          <t>LargeCapQuality, StrongCoverage, BAB-Becoming, LynchPEGY, LigerLagging</t>
+          <t>FixedCost+DemandShock, Weinstein-Stage2, LynchPEGY</t>
         </is>
       </c>
       <c r="N257" s="24" t="n">
-        <v>0.3729587118824605</v>
+        <v>0.409827795251543</v>
       </c>
       <c r="O257" s="24" t="n">
-        <v>0.44304465</v>
+        <v>0.442614</v>
       </c>
     </row>
     <row r="258" ht="16" customHeight="1">
@@ -41182,31 +41122,31 @@
       </c>
       <c r="D258" s="18" t="inlineStr">
         <is>
-          <t>0270.HK</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="E258" s="19" t="inlineStr">
         <is>
-          <t>Guangdong Investment Limited</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="F258" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G258" s="21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H258" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I258" s="22" t="n">
-        <v>7128725959.103208</v>
+        <v>178206359552</v>
       </c>
       <c r="J258" s="23" t="inlineStr">
         <is>
@@ -41214,21 +41154,21 @@
         </is>
       </c>
       <c r="K258" s="22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L258" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M258" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, Weinstein-Stage2, LynchPEGY</t>
+          <t>LindyMargin, LindyFCF, NoDilution, CashQuality, LargeCapQuality, Weins</t>
         </is>
       </c>
       <c r="N258" s="24" t="n">
-        <v>0.409827795251543</v>
+        <v>0.3902513483778934</v>
       </c>
       <c r="O258" s="24" t="n">
-        <v>0.442614</v>
+        <v>0.44254476</v>
       </c>
     </row>
     <row r="259" ht="16" customHeight="1">
@@ -41242,12 +41182,12 @@
       </c>
       <c r="D259" s="18" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CRYCY</t>
         </is>
       </c>
       <c r="E259" s="19" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>China Railway Signal &amp; Communication Corporation Limited</t>
         </is>
       </c>
       <c r="F259" s="26" t="inlineStr">
@@ -41257,16 +41197,16 @@
       </c>
       <c r="G259" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H259" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I259" s="22" t="n">
-        <v>178206359552</v>
+        <v>4744239104</v>
       </c>
       <c r="J259" s="23" t="inlineStr">
         <is>
@@ -41274,21 +41214,21 @@
         </is>
       </c>
       <c r="K259" s="22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L259" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M259" s="21" t="inlineStr">
         <is>
-          <t>LindyMargin, LindyFCF, NoDilution, CashQuality, LargeCapQuality, Weins</t>
+          <t>BalanceSheetReturn, NetCashReturner, StrongCoverage, LynchEV-GY, Hidde</t>
         </is>
       </c>
       <c r="N259" s="24" t="n">
-        <v>0.3902513483778934</v>
+        <v>0.4020684481930092</v>
       </c>
       <c r="O259" s="24" t="n">
-        <v>0.44254476</v>
+        <v>0.4425421437000001</v>
       </c>
     </row>
     <row r="260" ht="16" customHeight="1">
@@ -41302,31 +41242,31 @@
       </c>
       <c r="D260" s="18" t="inlineStr">
         <is>
-          <t>CRYCY</t>
+          <t>TSFA.F</t>
         </is>
       </c>
       <c r="E260" s="19" t="inlineStr">
         <is>
-          <t>China Railway Signal &amp; Communication Corporation Limited</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="F260" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G260" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H260" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Mega Cap</t>
         </is>
       </c>
       <c r="I260" s="22" t="n">
-        <v>4744239104</v>
+        <v>2220380624508.375</v>
       </c>
       <c r="J260" s="23" t="inlineStr">
         <is>
@@ -41334,21 +41274,21 @@
         </is>
       </c>
       <c r="K260" s="22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L260" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M260" s="21" t="inlineStr">
         <is>
-          <t>BalanceSheetReturn, NetCashReturner, StrongCoverage, LynchEV-GY, Hidde</t>
+          <t>ONeil-CANSLIM, BAB-Becoming, LynchPEGY, LynchEV-GY, Bottleneck-Chokepo</t>
         </is>
       </c>
       <c r="N260" s="24" t="n">
-        <v>0.4020684481930092</v>
+        <v>0.4279470347045314</v>
       </c>
       <c r="O260" s="24" t="n">
-        <v>0.4425421437000001</v>
+        <v>0.4420092940000001</v>
       </c>
     </row>
     <row r="261" ht="16" customHeight="1">
@@ -41362,31 +41302,31 @@
       </c>
       <c r="D261" s="18" t="inlineStr">
         <is>
-          <t>TSFA.F</t>
+          <t>601000.SS</t>
         </is>
       </c>
       <c r="E261" s="19" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>TangShan Port Group Co.,Ltd</t>
         </is>
       </c>
       <c r="F261" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G261" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H261" s="16" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I261" s="22" t="n">
-        <v>2220380624508.375</v>
+        <v>3967845106.964722</v>
       </c>
       <c r="J261" s="23" t="inlineStr">
         <is>
@@ -41394,21 +41334,21 @@
         </is>
       </c>
       <c r="K261" s="22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L261" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M261" s="21" t="inlineStr">
         <is>
-          <t>ONeil-CANSLIM, BAB-Becoming, LynchPEGY, LynchEV-GY, Bottleneck-Chokepo</t>
+          <t>QuietCompounder, OwnerOperator, NetCashReturner, Weinstein-Stage2, Hid</t>
         </is>
       </c>
       <c r="N261" s="24" t="n">
-        <v>0.4279470347045314</v>
+        <v>0.4315007890965763</v>
       </c>
       <c r="O261" s="24" t="n">
-        <v>0.4420092940000001</v>
+        <v>0.4417912912</v>
       </c>
     </row>
     <row r="262" ht="16" customHeight="1">
@@ -41422,22 +41362,22 @@
       </c>
       <c r="D262" s="18" t="inlineStr">
         <is>
-          <t>601000.SS</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="E262" s="19" t="inlineStr">
         <is>
-          <t>TangShan Port Group Co.,Ltd</t>
+          <t>Dillard’S, Inc.</t>
         </is>
       </c>
       <c r="F262" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G262" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H262" s="16" t="inlineStr">
@@ -41446,7 +41386,7 @@
         </is>
       </c>
       <c r="I262" s="22" t="n">
-        <v>3967845106.964722</v>
+        <v>10161546240</v>
       </c>
       <c r="J262" s="23" t="inlineStr">
         <is>
@@ -41454,21 +41394,21 @@
         </is>
       </c>
       <c r="K262" s="22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L262" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M262" s="21" t="inlineStr">
         <is>
-          <t>QuietCompounder, OwnerOperator, NetCashReturner, Weinstein-Stage2, Hid</t>
+          <t>FixedCost+DemandShock, CapitalReturner, LowSBCQuality, StrongCoverage,</t>
         </is>
       </c>
       <c r="N262" s="24" t="n">
-        <v>0.4315007890965763</v>
+        <v>0.3775645548364431</v>
       </c>
       <c r="O262" s="24" t="n">
-        <v>0.4417912912</v>
+        <v>0.4417504</v>
       </c>
     </row>
     <row r="263" ht="16" customHeight="1">
@@ -41482,22 +41422,22 @@
       </c>
       <c r="D263" s="18" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>G24.F</t>
         </is>
       </c>
       <c r="E263" s="19" t="inlineStr">
         <is>
-          <t>Dillard’S, Inc.</t>
+          <t>Scout24 AG</t>
         </is>
       </c>
       <c r="F263" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G263" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H263" s="16" t="inlineStr">
@@ -41506,7 +41446,7 @@
         </is>
       </c>
       <c r="I263" s="22" t="n">
-        <v>10161546240</v>
+        <v>5822103083.405273</v>
       </c>
       <c r="J263" s="23" t="inlineStr">
         <is>
@@ -41514,21 +41454,21 @@
         </is>
       </c>
       <c r="K263" s="22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L263" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M263" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, CapitalReturner, LowSBCQuality, StrongCoverage,</t>
+          <t xml:space="preserve">NarrativeLag, MidCapGARP, LynchPEGY, LynchEV-GY, AsleepAtWheel-Beats, </t>
         </is>
       </c>
       <c r="N263" s="24" t="n">
-        <v>0.3775645548364431</v>
+        <v>0.3849548344202952</v>
       </c>
       <c r="O263" s="24" t="n">
-        <v>0.4417504</v>
+        <v>0.441735225</v>
       </c>
     </row>
     <row r="264" ht="16" customHeight="1">
@@ -41542,31 +41482,31 @@
       </c>
       <c r="D264" s="18" t="inlineStr">
         <is>
-          <t>G24.F</t>
+          <t>BDNNY</t>
         </is>
       </c>
       <c r="E264" s="19" t="inlineStr">
         <is>
-          <t>Scout24 AG</t>
+          <t>Boliden AB (publ)</t>
         </is>
       </c>
       <c r="F264" s="26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G264" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H264" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I264" s="22" t="n">
-        <v>5822103083.405273</v>
+        <v>16056656896</v>
       </c>
       <c r="J264" s="23" t="inlineStr">
         <is>
@@ -41581,14 +41521,14 @@
       </c>
       <c r="M264" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, MidCapGARP, LynchPEGY, LynchEV-GY, AsleepAtWheel-Beats, </t>
+          <t>LargeCapQuality, MidCapGARP, LynchEV-GY, Forensic-OwnerEarnings, Foren</t>
         </is>
       </c>
       <c r="N264" s="24" t="n">
-        <v>0.3849548344202952</v>
+        <v>0.4207577265308759</v>
       </c>
       <c r="O264" s="24" t="n">
-        <v>0.441735225</v>
+        <v>0.4416946848</v>
       </c>
     </row>
     <row r="265" ht="16" customHeight="1">
@@ -41602,31 +41542,31 @@
       </c>
       <c r="D265" s="18" t="inlineStr">
         <is>
-          <t>BDNNY</t>
+          <t>DLN.L</t>
         </is>
       </c>
       <c r="E265" s="19" t="inlineStr">
         <is>
-          <t>Boliden AB (publ)</t>
+          <t>Derwent London plc</t>
         </is>
       </c>
       <c r="F265" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G265" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H265" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I265" s="22" t="n">
-        <v>16056656896</v>
+        <v>2693926203.90065</v>
       </c>
       <c r="J265" s="23" t="inlineStr">
         <is>
@@ -41634,21 +41574,17 @@
         </is>
       </c>
       <c r="K265" s="22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L265" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M265" s="21" t="inlineStr">
-        <is>
-          <t>LargeCapQuality, MidCapGARP, LynchEV-GY, Forensic-OwnerEarnings, Foren</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M265" s="21" t="inlineStr"/>
       <c r="N265" s="24" t="n">
-        <v>0.4207577265308759</v>
+        <v>0.4263471791089161</v>
       </c>
       <c r="O265" s="24" t="n">
-        <v>0.4416946848</v>
+        <v>0.441431755</v>
       </c>
     </row>
     <row r="266" ht="16" customHeight="1">
@@ -41662,22 +41598,22 @@
       </c>
       <c r="D266" s="18" t="inlineStr">
         <is>
-          <t>DLN.L</t>
+          <t>1093.HK</t>
         </is>
       </c>
       <c r="E266" s="19" t="inlineStr">
         <is>
-          <t>Derwent London plc</t>
+          <t>CSPC Pharmaceutical Group Limited</t>
         </is>
       </c>
       <c r="F266" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G266" s="21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H266" s="16" t="inlineStr">
@@ -41686,7 +41622,7 @@
         </is>
       </c>
       <c r="I266" s="22" t="n">
-        <v>2693926203.90065</v>
+        <v>12676444030.29956</v>
       </c>
       <c r="J266" s="23" t="inlineStr">
         <is>
@@ -41694,17 +41630,21 @@
         </is>
       </c>
       <c r="K266" s="22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L266" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M266" s="21" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M266" s="21" t="inlineStr">
+        <is>
+          <t>QuietCompounder, OwnerOperator, LargeCapQuality, Weinstein-Stage2, Str</t>
+        </is>
+      </c>
       <c r="N266" s="24" t="n">
-        <v>0.4263471791089161</v>
+        <v>0.3922433699418057</v>
       </c>
       <c r="O266" s="24" t="n">
-        <v>0.441431755</v>
+        <v>0.44127375</v>
       </c>
     </row>
     <row r="267" ht="16" customHeight="1">
@@ -41718,22 +41658,22 @@
       </c>
       <c r="D267" s="18" t="inlineStr">
         <is>
-          <t>1093.HK</t>
+          <t>5269.TW</t>
         </is>
       </c>
       <c r="E267" s="19" t="inlineStr">
         <is>
-          <t>CSPC Pharmaceutical Group Limited</t>
+          <t>ASMedia Technology Inc.</t>
         </is>
       </c>
       <c r="F267" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G267" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H267" s="16" t="inlineStr">
@@ -41742,7 +41682,7 @@
         </is>
       </c>
       <c r="I267" s="22" t="n">
-        <v>12676444030.29956</v>
+        <v>3088869408.424829</v>
       </c>
       <c r="J267" s="23" t="inlineStr">
         <is>
@@ -41757,14 +41697,14 @@
       </c>
       <c r="M267" s="21" t="inlineStr">
         <is>
-          <t>QuietCompounder, OwnerOperator, LargeCapQuality, Weinstein-Stage2, Str</t>
+          <t>NarrativeLag, StrongCoverage, LynchPEGY, LynchEV-GY, TenBaggerPath, Te</t>
         </is>
       </c>
       <c r="N267" s="24" t="n">
-        <v>0.3922433699418057</v>
+        <v>0.4266109994844136</v>
       </c>
       <c r="O267" s="24" t="n">
-        <v>0.44127375</v>
+        <v>0.441120155</v>
       </c>
     </row>
     <row r="268" ht="16" customHeight="1">
@@ -41778,31 +41718,31 @@
       </c>
       <c r="D268" s="18" t="inlineStr">
         <is>
-          <t>5269.TW</t>
+          <t>ZTO</t>
         </is>
       </c>
       <c r="E268" s="19" t="inlineStr">
         <is>
-          <t>ASMedia Technology Inc.</t>
+          <t>Zto Express (Cayman) Inc.</t>
         </is>
       </c>
       <c r="F268" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G268" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H268" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I268" s="22" t="n">
-        <v>3088869408.424829</v>
+        <v>15584094208</v>
       </c>
       <c r="J268" s="23" t="inlineStr">
         <is>
@@ -41810,21 +41750,21 @@
         </is>
       </c>
       <c r="K268" s="22" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L268" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M268" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, StrongCoverage, LynchPEGY, LynchEV-GY, TenBaggerPath, Te</t>
+          <t>LindyFCF, NoDilution, QARP, LargeCapQuality, MidCapGARP, BalanceSheetR</t>
         </is>
       </c>
       <c r="N268" s="24" t="n">
-        <v>0.4266109994844136</v>
+        <v>0.4016653921347458</v>
       </c>
       <c r="O268" s="24" t="n">
-        <v>0.441120155</v>
+        <v>0.4410287800000001</v>
       </c>
     </row>
     <row r="269" ht="16" customHeight="1">
@@ -41838,12 +41778,12 @@
       </c>
       <c r="D269" s="18" t="inlineStr">
         <is>
-          <t>ZTO</t>
+          <t>TLTZF</t>
         </is>
       </c>
       <c r="E269" s="19" t="inlineStr">
         <is>
-          <t>Zto Express (Cayman) Inc.</t>
+          <t>Tele2 AB (publ)</t>
         </is>
       </c>
       <c r="F269" s="26" t="inlineStr">
@@ -41853,16 +41793,16 @@
       </c>
       <c r="G269" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H269" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I269" s="22" t="n">
-        <v>15584094208</v>
+        <v>12072852480</v>
       </c>
       <c r="J269" s="23" t="inlineStr">
         <is>
@@ -41870,21 +41810,21 @@
         </is>
       </c>
       <c r="K269" s="22" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L269" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M269" s="21" t="inlineStr">
         <is>
-          <t>LindyFCF, NoDilution, QARP, LargeCapQuality, MidCapGARP, BalanceSheetR</t>
+          <t>LargeCapQuality, MidCapGARP, CapitalReturner, LynchEV-GY, Forensic-Own</t>
         </is>
       </c>
       <c r="N269" s="24" t="n">
-        <v>0.4016653921347458</v>
+        <v>0.43264599434016</v>
       </c>
       <c r="O269" s="24" t="n">
-        <v>0.4410287800000001</v>
+        <v>0.4410129206</v>
       </c>
     </row>
     <row r="270" ht="16" customHeight="1">
@@ -41898,12 +41838,12 @@
       </c>
       <c r="D270" s="18" t="inlineStr">
         <is>
-          <t>TLTZF</t>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E270" s="19" t="inlineStr">
         <is>
-          <t>Tele2 AB (publ)</t>
+          <t>Paymentus Holdings Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="F270" s="26" t="inlineStr">
@@ -41913,7 +41853,7 @@
       </c>
       <c r="G270" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H270" s="16" t="inlineStr">
@@ -41922,7 +41862,7 @@
         </is>
       </c>
       <c r="I270" s="22" t="n">
-        <v>12072852480</v>
+        <v>4581684736</v>
       </c>
       <c r="J270" s="23" t="inlineStr">
         <is>
@@ -41930,21 +41870,21 @@
         </is>
       </c>
       <c r="K270" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L270" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M270" s="21" t="inlineStr">
         <is>
-          <t>LargeCapQuality, MidCapGARP, CapitalReturner, LynchEV-GY, Forensic-Own</t>
+          <t>NarrativeLag, LindyFCF, CapitalLightPivot, LowSBCQuality, StrongCovera</t>
         </is>
       </c>
       <c r="N270" s="24" t="n">
-        <v>0.43264599434016</v>
+        <v>0.3885786122020522</v>
       </c>
       <c r="O270" s="24" t="n">
-        <v>0.4410129206</v>
+        <v>0.4409928213000001</v>
       </c>
     </row>
     <row r="271" ht="16" customHeight="1">
@@ -41958,22 +41898,22 @@
       </c>
       <c r="D271" s="18" t="inlineStr">
         <is>
-          <t>PAY</t>
+          <t>OR.TO</t>
         </is>
       </c>
       <c r="E271" s="19" t="inlineStr">
         <is>
-          <t>Paymentus Holdings Inc. Class A Common Stock</t>
+          <t>OSISKO GOLD ROYALTIES LTD</t>
         </is>
       </c>
       <c r="F271" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G271" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H271" s="16" t="inlineStr">
@@ -41982,7 +41922,7 @@
         </is>
       </c>
       <c r="I271" s="22" t="n">
-        <v>4581684736</v>
+        <v>6705157590.494202</v>
       </c>
       <c r="J271" s="23" t="inlineStr">
         <is>
@@ -41990,21 +41930,21 @@
         </is>
       </c>
       <c r="K271" s="22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L271" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M271" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, LindyFCF, CapitalLightPivot, LowSBCQuality, StrongCovera</t>
+          <t>FixedCost+DemandShock, RegimeCyclical, LynchPEGY, LynchEV-GY, AsleepAt</t>
         </is>
       </c>
       <c r="N271" s="24" t="n">
-        <v>0.3885786122020522</v>
+        <v>0.4176102766225654</v>
       </c>
       <c r="O271" s="24" t="n">
-        <v>0.4409928213000001</v>
+        <v>0.4409460468</v>
       </c>
     </row>
     <row r="272" ht="16" customHeight="1">
@@ -44682,14 +44622,14 @@
         </is>
       </c>
       <c r="K316" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L316" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M316" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, NetCashReturner, StrongCoverage, LigerL</t>
+          <t>NarrativeLag, CapitalReturner, NetCashReturner, StrongCoverage, LynchE</t>
         </is>
       </c>
       <c r="N316" s="24" t="n">
@@ -47278,31 +47218,31 @@
       </c>
       <c r="D360" s="18" t="inlineStr">
         <is>
-          <t>UVRBF</t>
+          <t>601766.SS</t>
         </is>
       </c>
       <c r="E360" s="19" t="inlineStr">
         <is>
-          <t>Universal Robina Corporation</t>
+          <t>CRRC Corporation Limited</t>
         </is>
       </c>
       <c r="F360" s="26" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G360" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H360" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I360" s="22" t="n">
-        <v>2129043200</v>
+        <v>22142938335.93945</v>
       </c>
       <c r="J360" s="23" t="inlineStr">
         <is>
@@ -47310,21 +47250,21 @@
         </is>
       </c>
       <c r="K360" s="22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L360" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M360" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, LynchEV-GY, LigerLaggingInflect</t>
+          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, CapitalReturner, Stron</t>
         </is>
       </c>
       <c r="N360" s="24" t="n">
-        <v>0.3732668102239384</v>
+        <v>0.3959524499636956</v>
       </c>
       <c r="O360" s="24" t="n">
-        <v>0.4232844</v>
+        <v>0.4232808446</v>
       </c>
     </row>
     <row r="361" ht="16" customHeight="1">
@@ -47338,22 +47278,22 @@
       </c>
       <c r="D361" s="18" t="inlineStr">
         <is>
-          <t>601766.SS</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="E361" s="19" t="inlineStr">
         <is>
-          <t>CRRC Corporation Limited</t>
+          <t>West Pharmaceutical Services, Inc.</t>
         </is>
       </c>
       <c r="F361" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G361" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H361" s="16" t="inlineStr">
@@ -47362,7 +47302,7 @@
         </is>
       </c>
       <c r="I361" s="22" t="n">
-        <v>22142938335.93945</v>
+        <v>24366200832</v>
       </c>
       <c r="J361" s="23" t="inlineStr">
         <is>
@@ -47370,21 +47310,21 @@
         </is>
       </c>
       <c r="K361" s="22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L361" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M361" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, CapitalReturner, Stron</t>
+          <t>LindyMargin, LindyFCF, NoDilution, BuybackCompounder, LargeCapQuality,</t>
         </is>
       </c>
       <c r="N361" s="24" t="n">
-        <v>0.3959524499636956</v>
+        <v>0.3807445036921761</v>
       </c>
       <c r="O361" s="24" t="n">
-        <v>0.4232808446</v>
+        <v>0.422991848</v>
       </c>
     </row>
     <row r="362" ht="16" customHeight="1">
@@ -47398,31 +47338,31 @@
       </c>
       <c r="D362" s="18" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>PE&amp;OLES.MX</t>
         </is>
       </c>
       <c r="E362" s="19" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services, Inc.</t>
+          <t>Industrias Penoles, S.A.B. de C.V.</t>
         </is>
       </c>
       <c r="F362" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G362" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H362" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I362" s="22" t="n">
-        <v>24366200832</v>
+        <v>20621886716.5946</v>
       </c>
       <c r="J362" s="23" t="inlineStr">
         <is>
@@ -47430,21 +47370,21 @@
         </is>
       </c>
       <c r="K362" s="22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L362" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M362" s="21" t="inlineStr">
         <is>
-          <t>LindyMargin, LindyFCF, NoDilution, BuybackCompounder, LargeCapQuality,</t>
+          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, LargeCapQuality</t>
         </is>
       </c>
       <c r="N362" s="24" t="n">
-        <v>0.3807445036921761</v>
+        <v>0.3833726868748546</v>
       </c>
       <c r="O362" s="24" t="n">
-        <v>0.422991848</v>
+        <v>0.4226678749999999</v>
       </c>
     </row>
     <row r="363" ht="16" customHeight="1">
@@ -47458,31 +47398,31 @@
       </c>
       <c r="D363" s="18" t="inlineStr">
         <is>
-          <t>PE&amp;OLES.MX</t>
+          <t>YASKY</t>
         </is>
       </c>
       <c r="E363" s="19" t="inlineStr">
         <is>
-          <t>Industrias Penoles, S.A.B. de C.V.</t>
+          <t>YASKAWA Electric Corporation</t>
         </is>
       </c>
       <c r="F363" s="26" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G363" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H363" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I363" s="22" t="n">
-        <v>20621886716.5946</v>
+        <v>7316770304</v>
       </c>
       <c r="J363" s="23" t="inlineStr">
         <is>
@@ -47490,21 +47430,21 @@
         </is>
       </c>
       <c r="K363" s="22" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L363" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M363" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, LargeCapQuality</t>
+          <t>BalanceSheetReturn, NetCashReturner, BAB-Becoming</t>
         </is>
       </c>
       <c r="N363" s="24" t="n">
-        <v>0.3833726868748546</v>
+        <v>0.3687501748423951</v>
       </c>
       <c r="O363" s="24" t="n">
-        <v>0.4226678749999999</v>
+        <v>0.4226544207999999</v>
       </c>
     </row>
     <row r="364" ht="16" customHeight="1">
@@ -47518,31 +47458,31 @@
       </c>
       <c r="D364" s="18" t="inlineStr">
         <is>
-          <t>YASKY</t>
+          <t>PAAS.TO</t>
         </is>
       </c>
       <c r="E364" s="19" t="inlineStr">
         <is>
-          <t>YASKAWA Electric Corporation</t>
+          <t>PAN AMERICAN SILVER CORP</t>
         </is>
       </c>
       <c r="F364" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G364" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H364" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I364" s="22" t="n">
-        <v>7316770304</v>
+        <v>20718569823.74561</v>
       </c>
       <c r="J364" s="23" t="inlineStr">
         <is>
@@ -47550,21 +47490,21 @@
         </is>
       </c>
       <c r="K364" s="22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L364" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M364" s="21" t="inlineStr">
         <is>
-          <t>BalanceSheetReturn, NetCashReturner, BAB-Becoming</t>
+          <t>FixedCost+DemandShock, RegimeCyclical, LargeCapQuality, MidCapGARP, St</t>
         </is>
       </c>
       <c r="N364" s="24" t="n">
-        <v>0.3687501748423951</v>
+        <v>0.4101897986043997</v>
       </c>
       <c r="O364" s="24" t="n">
-        <v>0.4226544207999999</v>
+        <v>0.4225874622</v>
       </c>
     </row>
     <row r="365" ht="16" customHeight="1">
@@ -47578,22 +47518,22 @@
       </c>
       <c r="D365" s="18" t="inlineStr">
         <is>
-          <t>PAAS.TO</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="E365" s="19" t="inlineStr">
         <is>
-          <t>PAN AMERICAN SILVER CORP</t>
+          <t>Cathay General Bancorp</t>
         </is>
       </c>
       <c r="F365" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G365" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H365" s="16" t="inlineStr">
@@ -47602,7 +47542,7 @@
         </is>
       </c>
       <c r="I365" s="22" t="n">
-        <v>20718569823.74561</v>
+        <v>4136923904</v>
       </c>
       <c r="J365" s="23" t="inlineStr">
         <is>
@@ -47610,21 +47550,21 @@
         </is>
       </c>
       <c r="K365" s="22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L365" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M365" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, RegimeCyclical, LargeCapQuality, MidCapGARP, St</t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="N365" s="24" t="n">
-        <v>0.4101897986043997</v>
+        <v>0.3770113202227308</v>
       </c>
       <c r="O365" s="24" t="n">
-        <v>0.4225874622</v>
+        <v>0.4225767</v>
       </c>
     </row>
     <row r="366" ht="16" customHeight="1">
@@ -47638,22 +47578,22 @@
       </c>
       <c r="D366" s="18" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>B8O.F</t>
         </is>
       </c>
       <c r="E366" s="19" t="inlineStr">
         <is>
-          <t>Cathay General Bancorp</t>
+          <t>Yangzijiang Shipbuilding Holdings, Ltd.</t>
         </is>
       </c>
       <c r="F366" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G366" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H366" s="16" t="inlineStr">
@@ -47662,7 +47602,7 @@
         </is>
       </c>
       <c r="I366" s="22" t="n">
-        <v>4136923904</v>
+        <v>15013914247.77686</v>
       </c>
       <c r="J366" s="23" t="inlineStr">
         <is>
@@ -47670,21 +47610,21 @@
         </is>
       </c>
       <c r="K366" s="22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L366" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M366" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats</t>
+          <t>OwnerOperator, LargeCapQuality, MidCapGARP, Weinstein-Stage2, StrongCo</t>
         </is>
       </c>
       <c r="N366" s="24" t="n">
-        <v>0.3770113202227308</v>
+        <v>0.4551581311869413</v>
       </c>
       <c r="O366" s="24" t="n">
-        <v>0.4225767</v>
+        <v>0.422511232</v>
       </c>
     </row>
     <row r="367" ht="16" customHeight="1">
@@ -47698,17 +47638,17 @@
       </c>
       <c r="D367" s="18" t="inlineStr">
         <is>
-          <t>B8O.F</t>
+          <t>AYI</t>
         </is>
       </c>
       <c r="E367" s="19" t="inlineStr">
         <is>
-          <t>Yangzijiang Shipbuilding Holdings, Ltd.</t>
+          <t>Acuity Brands, Inc.</t>
         </is>
       </c>
       <c r="F367" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G367" s="21" t="inlineStr">
@@ -47722,7 +47662,7 @@
         </is>
       </c>
       <c r="I367" s="22" t="n">
-        <v>15013914247.77686</v>
+        <v>9548241920</v>
       </c>
       <c r="J367" s="23" t="inlineStr">
         <is>
@@ -47730,21 +47670,21 @@
         </is>
       </c>
       <c r="K367" s="22" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L367" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M367" s="21" t="inlineStr">
         <is>
-          <t>OwnerOperator, LargeCapQuality, MidCapGARP, Weinstein-Stage2, StrongCo</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CashReinvest, LindyMargin, LindyF</t>
         </is>
       </c>
       <c r="N367" s="24" t="n">
-        <v>0.4551581311869413</v>
+        <v>0.3666860393161141</v>
       </c>
       <c r="O367" s="24" t="n">
-        <v>0.422511232</v>
+        <v>0.42242176</v>
       </c>
     </row>
     <row r="368" ht="16" customHeight="1">
@@ -47758,12 +47698,12 @@
       </c>
       <c r="D368" s="18" t="inlineStr">
         <is>
-          <t>AYI</t>
+          <t>OUTKY</t>
         </is>
       </c>
       <c r="E368" s="19" t="inlineStr">
         <is>
-          <t>Acuity Brands, Inc.</t>
+          <t>Outokumpu Oyj</t>
         </is>
       </c>
       <c r="F368" s="26" t="inlineStr">
@@ -47773,7 +47713,7 @@
       </c>
       <c r="G368" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H368" s="16" t="inlineStr">
@@ -47782,7 +47722,7 @@
         </is>
       </c>
       <c r="I368" s="22" t="n">
-        <v>9548241920</v>
+        <v>3111092992</v>
       </c>
       <c r="J368" s="23" t="inlineStr">
         <is>
@@ -47790,21 +47730,21 @@
         </is>
       </c>
       <c r="K368" s="22" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L368" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M368" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CashReinvest, LindyMargin, LindyF</t>
+          <t>CapitalReturner, Weinstein-Stage2</t>
         </is>
       </c>
       <c r="N368" s="24" t="n">
-        <v>0.3666860393161141</v>
+        <v>0.3858093600321536</v>
       </c>
       <c r="O368" s="24" t="n">
-        <v>0.42242176</v>
+        <v>0.4224210439</v>
       </c>
     </row>
     <row r="369" ht="16" customHeight="1">
@@ -47818,12 +47758,12 @@
       </c>
       <c r="D369" s="18" t="inlineStr">
         <is>
-          <t>OUTKY</t>
+          <t>TWODY</t>
         </is>
       </c>
       <c r="E369" s="19" t="inlineStr">
         <is>
-          <t>Outokumpu Oyj</t>
+          <t>Taylor Wimpey plc</t>
         </is>
       </c>
       <c r="F369" s="26" t="inlineStr">
@@ -47833,7 +47773,7 @@
       </c>
       <c r="G369" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H369" s="16" t="inlineStr">
@@ -47842,7 +47782,7 @@
         </is>
       </c>
       <c r="I369" s="22" t="n">
-        <v>3111092992</v>
+        <v>3639735552</v>
       </c>
       <c r="J369" s="23" t="inlineStr">
         <is>
@@ -47850,21 +47790,21 @@
         </is>
       </c>
       <c r="K369" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L369" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="L369" s="22" t="n">
-        <v>4</v>
-      </c>
       <c r="M369" s="21" t="inlineStr">
         <is>
-          <t>CapitalReturner, Weinstein-Stage2</t>
+          <t>NarrativeLag, CapitalReturner, Cundill-DeepValue, StrongCoverage, Lync</t>
         </is>
       </c>
       <c r="N369" s="24" t="n">
-        <v>0.3858093600321536</v>
+        <v>0.3901809834895145</v>
       </c>
       <c r="O369" s="24" t="n">
-        <v>0.4224210439</v>
+        <v>0.4223788563999999</v>
       </c>
     </row>
     <row r="370" ht="16" customHeight="1">
@@ -47878,12 +47818,12 @@
       </c>
       <c r="D370" s="18" t="inlineStr">
         <is>
-          <t>TWODY</t>
+          <t>HTHIY</t>
         </is>
       </c>
       <c r="E370" s="19" t="inlineStr">
         <is>
-          <t>Taylor Wimpey plc</t>
+          <t>Hitachi, Ltd.</t>
         </is>
       </c>
       <c r="F370" s="26" t="inlineStr">
@@ -47898,11 +47838,11 @@
       </c>
       <c r="H370" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I370" s="22" t="n">
-        <v>3639735552</v>
+        <v>153218285568</v>
       </c>
       <c r="J370" s="23" t="inlineStr">
         <is>
@@ -47910,21 +47850,21 @@
         </is>
       </c>
       <c r="K370" s="22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L370" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M370" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, Cundill-DeepValue, StrongCoverage, Lync</t>
+          <t>FixedCost+DemandShock, LargeCapQuality, StrongCoverage, LynchEV-GY, As</t>
         </is>
       </c>
       <c r="N370" s="24" t="n">
-        <v>0.3901809834895145</v>
+        <v>0.3813455325780232</v>
       </c>
       <c r="O370" s="24" t="n">
-        <v>0.4223788563999999</v>
+        <v>0.4223554566</v>
       </c>
     </row>
     <row r="371" ht="16" customHeight="1">
@@ -47938,12 +47878,12 @@
       </c>
       <c r="D371" s="18" t="inlineStr">
         <is>
-          <t>HTHIY</t>
+          <t>HDALF</t>
         </is>
       </c>
       <c r="E371" s="19" t="inlineStr">
         <is>
-          <t>Hitachi, Ltd.</t>
+          <t>Haidilao International Holding Ltd.</t>
         </is>
       </c>
       <c r="F371" s="26" t="inlineStr">
@@ -47953,7 +47893,7 @@
       </c>
       <c r="G371" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H371" s="16" t="inlineStr">
@@ -47962,7 +47902,7 @@
         </is>
       </c>
       <c r="I371" s="22" t="n">
-        <v>153218285568</v>
+        <v>7323992576</v>
       </c>
       <c r="J371" s="23" t="inlineStr">
         <is>
@@ -47970,21 +47910,21 @@
         </is>
       </c>
       <c r="K371" s="22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L371" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M371" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, LargeCapQuality, StrongCoverage, LynchEV-GY, As</t>
+          <t>CapitalDiscipline, CapitalReturner, BalanceSheetReturn, StrongCoverage</t>
         </is>
       </c>
       <c r="N371" s="24" t="n">
-        <v>0.3813455325780232</v>
+        <v>0.4129622445692864</v>
       </c>
       <c r="O371" s="24" t="n">
-        <v>0.4223554566</v>
+        <v>0.4222869091999999</v>
       </c>
     </row>
     <row r="372" ht="16" customHeight="1">
@@ -47998,12 +47938,12 @@
       </c>
       <c r="D372" s="18" t="inlineStr">
         <is>
-          <t>HDALF</t>
+          <t>WTM</t>
         </is>
       </c>
       <c r="E372" s="19" t="inlineStr">
         <is>
-          <t>Haidilao International Holding Ltd.</t>
+          <t>White Mountains Insurance Group, Ltd</t>
         </is>
       </c>
       <c r="F372" s="26" t="inlineStr">
@@ -48013,16 +47953,16 @@
       </c>
       <c r="G372" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H372" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I372" s="22" t="n">
-        <v>7323992576</v>
+        <v>4900296192</v>
       </c>
       <c r="J372" s="23" t="inlineStr">
         <is>
@@ -48030,21 +47970,21 @@
         </is>
       </c>
       <c r="K372" s="22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L372" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M372" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, CapitalReturner, BalanceSheetReturn, StrongCoverage</t>
+          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY, Forensic-PayoutConfirmed</t>
         </is>
       </c>
       <c r="N372" s="24" t="n">
-        <v>0.4129622445692864</v>
+        <v>0.3974987868012517</v>
       </c>
       <c r="O372" s="24" t="n">
-        <v>0.4222869091999999</v>
+        <v>0.4221438200000001</v>
       </c>
     </row>
     <row r="373" ht="16" customHeight="1">
@@ -48058,12 +47998,12 @@
       </c>
       <c r="D373" s="18" t="inlineStr">
         <is>
-          <t>WTM</t>
+          <t>IDCC</t>
         </is>
       </c>
       <c r="E373" s="19" t="inlineStr">
         <is>
-          <t>White Mountains Insurance Group, Ltd</t>
+          <t>Interdigital, Inc.</t>
         </is>
       </c>
       <c r="F373" s="26" t="inlineStr">
@@ -48073,7 +48013,7 @@
       </c>
       <c r="G373" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H373" s="16" t="inlineStr">
@@ -48082,7 +48022,7 @@
         </is>
       </c>
       <c r="I373" s="22" t="n">
-        <v>4900296192</v>
+        <v>9035457536</v>
       </c>
       <c r="J373" s="23" t="inlineStr">
         <is>
@@ -48090,21 +48030,21 @@
         </is>
       </c>
       <c r="K373" s="22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L373" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M373" s="21" t="inlineStr">
         <is>
-          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY, Forensic-PayoutConfirmed</t>
+          <t>CheapPerROIIC, LindyMargin, LindyFCF, CapitalLightPivot, TaxEfficient,</t>
         </is>
       </c>
       <c r="N373" s="24" t="n">
-        <v>0.3974987868012517</v>
+        <v>0.3992601592504489</v>
       </c>
       <c r="O373" s="24" t="n">
-        <v>0.4221438200000001</v>
+        <v>0.4216425156</v>
       </c>
     </row>
     <row r="374" ht="16" customHeight="1">
@@ -48118,22 +48058,22 @@
       </c>
       <c r="D374" s="18" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>BI5.F</t>
         </is>
       </c>
       <c r="E374" s="19" t="inlineStr">
         <is>
-          <t>Interdigital, Inc.</t>
+          <t>Brother Industries, Ltd.</t>
         </is>
       </c>
       <c r="F374" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G374" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H374" s="16" t="inlineStr">
@@ -48142,7 +48082,7 @@
         </is>
       </c>
       <c r="I374" s="22" t="n">
-        <v>9035457536</v>
+        <v>6892886778.509033</v>
       </c>
       <c r="J374" s="23" t="inlineStr">
         <is>
@@ -48153,18 +48093,18 @@
         <v>8</v>
       </c>
       <c r="L374" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M374" s="21" t="inlineStr">
         <is>
-          <t>CheapPerROIIC, LindyMargin, LindyFCF, CapitalLightPivot, TaxEfficient,</t>
+          <t>NarrativeLag, FixedCost+DemandShock, BalanceSheetReturn, Kullamagi-Bre</t>
         </is>
       </c>
       <c r="N374" s="24" t="n">
-        <v>0.3992601592504489</v>
+        <v>0.3844296374012034</v>
       </c>
       <c r="O374" s="24" t="n">
-        <v>0.4216425156</v>
+        <v>0.4215505608</v>
       </c>
     </row>
     <row r="375" ht="16" customHeight="1">
@@ -48178,22 +48118,22 @@
       </c>
       <c r="D375" s="18" t="inlineStr">
         <is>
-          <t>BI5.F</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="E375" s="19" t="inlineStr">
         <is>
-          <t>Brother Industries, Ltd.</t>
+          <t>Urban Outfitters, Inc.</t>
         </is>
       </c>
       <c r="F375" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G375" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H375" s="16" t="inlineStr">
@@ -48202,7 +48142,7 @@
         </is>
       </c>
       <c r="I375" s="22" t="n">
-        <v>6892886778.509033</v>
+        <v>6731177472</v>
       </c>
       <c r="J375" s="23" t="inlineStr">
         <is>
@@ -48210,21 +48150,21 @@
         </is>
       </c>
       <c r="K375" s="22" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="L375" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M375" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, BalanceSheetReturn, Kullamagi-Bre</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, DurableReinves</t>
         </is>
       </c>
       <c r="N375" s="24" t="n">
-        <v>0.3844296374012034</v>
+        <v>0.3968373164228453</v>
       </c>
       <c r="O375" s="24" t="n">
-        <v>0.4215505608</v>
+        <v>0.4214417200000001</v>
       </c>
     </row>
     <row r="376" ht="16" customHeight="1">
@@ -48238,12 +48178,12 @@
       </c>
       <c r="D376" s="18" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>BZZUF</t>
         </is>
       </c>
       <c r="E376" s="19" t="inlineStr">
         <is>
-          <t>Urban Outfitters, Inc.</t>
+          <t>Buzzi Unicem S.p.A.</t>
         </is>
       </c>
       <c r="F376" s="26" t="inlineStr">
@@ -48253,7 +48193,7 @@
       </c>
       <c r="G376" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H376" s="16" t="inlineStr">
@@ -48262,7 +48202,7 @@
         </is>
       </c>
       <c r="I376" s="22" t="n">
-        <v>6731177472</v>
+        <v>8472559104</v>
       </c>
       <c r="J376" s="23" t="inlineStr">
         <is>
@@ -48270,21 +48210,21 @@
         </is>
       </c>
       <c r="K376" s="22" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="L376" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M376" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, DurableReinves</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, StrongCoverage</t>
         </is>
       </c>
       <c r="N376" s="24" t="n">
-        <v>0.3968373164228453</v>
+        <v>0.395675285290647</v>
       </c>
       <c r="O376" s="24" t="n">
-        <v>0.4214417200000001</v>
+        <v>0.4214182072</v>
       </c>
     </row>
     <row r="377" ht="16" customHeight="1">
@@ -48298,12 +48238,12 @@
       </c>
       <c r="D377" s="18" t="inlineStr">
         <is>
-          <t>BZZUF</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="E377" s="19" t="inlineStr">
         <is>
-          <t>Buzzi Unicem S.p.A.</t>
+          <t>Best Buy Co., Inc.</t>
         </is>
       </c>
       <c r="F377" s="26" t="inlineStr">
@@ -48313,16 +48253,16 @@
       </c>
       <c r="G377" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H377" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I377" s="22" t="n">
-        <v>8472559104</v>
+        <v>19043274752</v>
       </c>
       <c r="J377" s="23" t="inlineStr">
         <is>
@@ -48330,21 +48270,21 @@
         </is>
       </c>
       <c r="K377" s="22" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L377" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M377" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, StrongCoverage</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, LindyFCF, NoDi</t>
         </is>
       </c>
       <c r="N377" s="24" t="n">
-        <v>0.395675285290647</v>
+        <v>0.3667768398497389</v>
       </c>
       <c r="O377" s="24" t="n">
-        <v>0.4214182072</v>
+        <v>0.4214043834</v>
       </c>
     </row>
     <row r="378" ht="16" customHeight="1">
@@ -48358,22 +48298,22 @@
       </c>
       <c r="D378" s="18" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>GGBR4.SA</t>
         </is>
       </c>
       <c r="E378" s="19" t="inlineStr">
         <is>
-          <t>Best Buy Co., Inc.</t>
+          <t>Gerdau S.A.</t>
         </is>
       </c>
       <c r="F378" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G378" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H378" s="16" t="inlineStr">
@@ -48382,7 +48322,7 @@
         </is>
       </c>
       <c r="I378" s="22" t="n">
-        <v>19043274752</v>
+        <v>9842497539.897947</v>
       </c>
       <c r="J378" s="23" t="inlineStr">
         <is>
@@ -48390,21 +48330,21 @@
         </is>
       </c>
       <c r="K378" s="22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L378" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M378" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, LindyFCF, NoDi</t>
+          <t>Weinstein-Stage2, BAB-Becoming, LynchPEGY, Forensic-PayoutConfirmed, F</t>
         </is>
       </c>
       <c r="N378" s="24" t="n">
-        <v>0.3667768398497389</v>
+        <v>0.3918790758786376</v>
       </c>
       <c r="O378" s="24" t="n">
-        <v>0.4214043834</v>
+        <v>0.4210889270000001</v>
       </c>
     </row>
     <row r="379" ht="16" customHeight="1">
@@ -48418,31 +48358,31 @@
       </c>
       <c r="D379" s="18" t="inlineStr">
         <is>
-          <t>GGBR4.SA</t>
+          <t>MDNDF</t>
         </is>
       </c>
       <c r="E379" s="19" t="inlineStr">
         <is>
-          <t>Gerdau S.A.</t>
+          <t>McDonald's Holdings Company (Japan), Ltd.</t>
         </is>
       </c>
       <c r="F379" s="26" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G379" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H379" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I379" s="22" t="n">
-        <v>9842497539.897947</v>
+        <v>6363401216</v>
       </c>
       <c r="J379" s="23" t="inlineStr">
         <is>
@@ -48450,21 +48390,21 @@
         </is>
       </c>
       <c r="K379" s="22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L379" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M379" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, BAB-Becoming, LynchPEGY, Forensic-PayoutConfirmed, F</t>
+          <t>OwnerOperator, StrongCoverage, Flyover-QuietQuality</t>
         </is>
       </c>
       <c r="N379" s="24" t="n">
-        <v>0.3918790758786376</v>
+        <v>0.4327686142481414</v>
       </c>
       <c r="O379" s="24" t="n">
-        <v>0.4210889270000001</v>
+        <v>0.4210217112</v>
       </c>
     </row>
     <row r="380" ht="16" customHeight="1">
@@ -48478,31 +48418,31 @@
       </c>
       <c r="D380" s="18" t="inlineStr">
         <is>
-          <t>MDNDF</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="E380" s="19" t="inlineStr">
         <is>
-          <t>McDonald's Holdings Company (Japan), Ltd.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="F380" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G380" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H380" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Mega Cap</t>
         </is>
       </c>
       <c r="I380" s="22" t="n">
-        <v>6363401216</v>
+        <v>401863442432</v>
       </c>
       <c r="J380" s="23" t="inlineStr">
         <is>
@@ -48510,21 +48450,21 @@
         </is>
       </c>
       <c r="K380" s="22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L380" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M380" s="21" t="inlineStr">
         <is>
-          <t>OwnerOperator, StrongCoverage, Flyover-QuietQuality</t>
+          <t>LindyGrowth, ReinvestInflect, StrongCoverage, FastestSegment, AsleepAt</t>
         </is>
       </c>
       <c r="N380" s="24" t="n">
-        <v>0.4327686142481414</v>
+        <v>0.3726294462798649</v>
       </c>
       <c r="O380" s="24" t="n">
-        <v>0.4210217112</v>
+        <v>0.42066008</v>
       </c>
     </row>
     <row r="381" ht="16" customHeight="1">
@@ -48538,17 +48478,17 @@
       </c>
       <c r="D381" s="18" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SCT.L</t>
         </is>
       </c>
       <c r="E381" s="19" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Softcat plc</t>
         </is>
       </c>
       <c r="F381" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G381" s="21" t="inlineStr">
@@ -48558,11 +48498,11 @@
       </c>
       <c r="H381" s="16" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I381" s="22" t="n">
-        <v>401863442432</v>
+        <v>4874979959.599915</v>
       </c>
       <c r="J381" s="23" t="inlineStr">
         <is>
@@ -48570,21 +48510,21 @@
         </is>
       </c>
       <c r="K381" s="22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L381" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M381" s="21" t="inlineStr">
         <is>
-          <t>LindyGrowth, ReinvestInflect, StrongCoverage, FastestSegment, AsleepAt</t>
+          <t>NarrativeLag, CapitalDiscipline, Weinstein-Stage2, Kullamagi-Breakout,</t>
         </is>
       </c>
       <c r="N381" s="24" t="n">
-        <v>0.3726294462798649</v>
+        <v>0.4154131964770285</v>
       </c>
       <c r="O381" s="24" t="n">
-        <v>0.42066008</v>
+        <v>0.420606</v>
       </c>
     </row>
     <row r="382" ht="16" customHeight="1">
@@ -48598,22 +48538,22 @@
       </c>
       <c r="D382" s="18" t="inlineStr">
         <is>
-          <t>SCT.L</t>
+          <t>UVRBF</t>
         </is>
       </c>
       <c r="E382" s="19" t="inlineStr">
         <is>
-          <t>Softcat plc</t>
+          <t>Universal Robina Corporation</t>
         </is>
       </c>
       <c r="F382" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="G382" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H382" s="16" t="inlineStr">
@@ -48622,7 +48562,7 @@
         </is>
       </c>
       <c r="I382" s="22" t="n">
-        <v>4874979959.599915</v>
+        <v>2129043200</v>
       </c>
       <c r="J382" s="23" t="inlineStr">
         <is>
@@ -48630,21 +48570,21 @@
         </is>
       </c>
       <c r="K382" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L382" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M382" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, Weinstein-Stage2, Kullamagi-Breakout,</t>
+          <t>CapitalDiscipline, LynchEV-GY, LigerLaggingInflect</t>
         </is>
       </c>
       <c r="N382" s="24" t="n">
-        <v>0.4154131964770285</v>
+        <v>0.3732668102239384</v>
       </c>
       <c r="O382" s="24" t="n">
-        <v>0.420606</v>
+        <v>0.420462504</v>
       </c>
     </row>
     <row r="383" ht="16" customHeight="1">
@@ -50218,12 +50158,12 @@
       </c>
       <c r="D409" s="18" t="inlineStr">
         <is>
-          <t>ALFVF</t>
+          <t>MBUMY</t>
         </is>
       </c>
       <c r="E409" s="19" t="inlineStr">
         <is>
-          <t>Alfa Laval AB (publ)</t>
+          <t>Mabuchi Motor Co., Ltd.</t>
         </is>
       </c>
       <c r="F409" s="26" t="inlineStr">
@@ -50233,16 +50173,16 @@
       </c>
       <c r="G409" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H409" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I409" s="22" t="n">
-        <v>24592914432</v>
+        <v>2602398720</v>
       </c>
       <c r="J409" s="23" t="inlineStr">
         <is>
@@ -50250,21 +50190,21 @@
         </is>
       </c>
       <c r="K409" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L409" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M409" s="21" t="inlineStr">
         <is>
-          <t>BAB-Becoming, Forensic-OwnerEarnings, Forensic-PayoutConfirmed</t>
+          <t>MidCapGARP, Weinstein-Stage2, StrongCoverage, LynchPEGY, HiddenAssets-</t>
         </is>
       </c>
       <c r="N409" s="24" t="n">
-        <v>0.4466159478357573</v>
+        <v>0.3702110899415803</v>
       </c>
       <c r="O409" s="24" t="n">
-        <v>0.4167301152</v>
+        <v>0.4164875</v>
       </c>
     </row>
     <row r="410" ht="16" customHeight="1">
@@ -50278,12 +50218,12 @@
       </c>
       <c r="D410" s="18" t="inlineStr">
         <is>
-          <t>MBUMY</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="E410" s="19" t="inlineStr">
         <is>
-          <t>Mabuchi Motor Co., Ltd.</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="F410" s="26" t="inlineStr">
@@ -50293,16 +50233,16 @@
       </c>
       <c r="G410" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H410" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I410" s="22" t="n">
-        <v>2602398720</v>
+        <v>85935079424</v>
       </c>
       <c r="J410" s="23" t="inlineStr">
         <is>
@@ -50310,21 +50250,21 @@
         </is>
       </c>
       <c r="K410" s="22" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="L410" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M410" s="21" t="inlineStr">
         <is>
-          <t>MidCapGARP, Weinstein-Stage2, StrongCoverage, LynchPEGY, HiddenAssets-</t>
+          <t>NarrativeLag, CapitalDiscipline, DeadOption, CashReinvest, LindyMargin</t>
         </is>
       </c>
       <c r="N410" s="24" t="n">
-        <v>0.3702110899415803</v>
+        <v>0.3728795062499949</v>
       </c>
       <c r="O410" s="24" t="n">
-        <v>0.4164875</v>
+        <v>0.41613408</v>
       </c>
     </row>
     <row r="411" ht="16" customHeight="1">
@@ -50338,22 +50278,22 @@
       </c>
       <c r="D411" s="18" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CCOZF</t>
         </is>
       </c>
       <c r="E411" s="19" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>China Coal Energy Company Limited</t>
         </is>
       </c>
       <c r="F411" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G411" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H411" s="16" t="inlineStr">
@@ -50362,7 +50302,7 @@
         </is>
       </c>
       <c r="I411" s="22" t="n">
-        <v>85935079424</v>
+        <v>16705914880</v>
       </c>
       <c r="J411" s="23" t="inlineStr">
         <is>
@@ -50370,21 +50310,21 @@
         </is>
       </c>
       <c r="K411" s="22" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="L411" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M411" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, DeadOption, CashReinvest, LindyMargin</t>
+          <t>LargeCapQuality, StrongCoverage, LynchPEGY, Forensic-UnderstatedE, Cas</t>
         </is>
       </c>
       <c r="N411" s="24" t="n">
-        <v>0.3728795062499949</v>
+        <v>0.388530783439194</v>
       </c>
       <c r="O411" s="24" t="n">
-        <v>0.41613408</v>
+        <v>0.4160073024</v>
       </c>
     </row>
     <row r="412" ht="16" customHeight="1">
@@ -50398,22 +50338,22 @@
       </c>
       <c r="D412" s="18" t="inlineStr">
         <is>
-          <t>CCOZF</t>
+          <t>ALBHF</t>
         </is>
       </c>
       <c r="E412" s="19" t="inlineStr">
         <is>
-          <t>China Coal Energy Company Limited</t>
+          <t>Alibaba Health Information Technology Limited</t>
         </is>
       </c>
       <c r="F412" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G412" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H412" s="16" t="inlineStr">
@@ -50422,7 +50362,7 @@
         </is>
       </c>
       <c r="I412" s="22" t="n">
-        <v>16705914880</v>
+        <v>6308366848</v>
       </c>
       <c r="J412" s="23" t="inlineStr">
         <is>
@@ -50433,18 +50373,18 @@
         <v>6</v>
       </c>
       <c r="L412" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M412" s="21" t="inlineStr">
         <is>
-          <t>LargeCapQuality, StrongCoverage, LynchPEGY, Forensic-UnderstatedE, Cas</t>
+          <t>NarrativeLag, CapitalDiscipline, DeadOption, StrongCoverage, LynchEV-G</t>
         </is>
       </c>
       <c r="N412" s="24" t="n">
-        <v>0.388530783439194</v>
+        <v>0.4201716159698607</v>
       </c>
       <c r="O412" s="24" t="n">
-        <v>0.4160073024</v>
+        <v>0.4159694</v>
       </c>
     </row>
     <row r="413" ht="16" customHeight="1">
@@ -50458,31 +50398,31 @@
       </c>
       <c r="D413" s="18" t="inlineStr">
         <is>
-          <t>ALBHF</t>
+          <t>9904.TW</t>
         </is>
       </c>
       <c r="E413" s="19" t="inlineStr">
         <is>
-          <t>Alibaba Health Information Technology Limited</t>
+          <t>Pou Chen Corporation</t>
         </is>
       </c>
       <c r="F413" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G413" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H413" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I413" s="22" t="n">
-        <v>6308366848</v>
+        <v>2258861286.538234</v>
       </c>
       <c r="J413" s="23" t="inlineStr">
         <is>
@@ -50490,21 +50430,21 @@
         </is>
       </c>
       <c r="K413" s="22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L413" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M413" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, DeadOption, StrongCoverage, LynchEV-G</t>
+          <t>NarrativeLag, BalanceSheetReturn, Cundill-DeepValue, XR-BigBathRebound</t>
         </is>
       </c>
       <c r="N413" s="24" t="n">
-        <v>0.4201716159698607</v>
+        <v>0.3797248195209564</v>
       </c>
       <c r="O413" s="24" t="n">
-        <v>0.4159694</v>
+        <v>0.415916604</v>
       </c>
     </row>
     <row r="414" ht="16" customHeight="1">
@@ -50518,22 +50458,22 @@
       </c>
       <c r="D414" s="18" t="inlineStr">
         <is>
-          <t>9904.TW</t>
+          <t>000408.SZ</t>
         </is>
       </c>
       <c r="E414" s="19" t="inlineStr">
         <is>
-          <t>Pou Chen Corporation</t>
+          <t>Zangge Holding Company Limited</t>
         </is>
       </c>
       <c r="F414" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G414" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H414" s="16" t="inlineStr">
@@ -50542,7 +50482,7 @@
         </is>
       </c>
       <c r="I414" s="22" t="n">
-        <v>2258861286.538234</v>
+        <v>16847484651.54443</v>
       </c>
       <c r="J414" s="23" t="inlineStr">
         <is>
@@ -50550,21 +50490,21 @@
         </is>
       </c>
       <c r="K414" s="22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L414" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M414" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, BalanceSheetReturn, Cundill-DeepValue, XR-BigBathRebound</t>
+          <t>FixedCost+DemandShock, OwnerOperator, LargeCapQuality, StrongCoverage,</t>
         </is>
       </c>
       <c r="N414" s="24" t="n">
-        <v>0.3797248195209564</v>
+        <v>0.3973707203500089</v>
       </c>
       <c r="O414" s="24" t="n">
-        <v>0.415916604</v>
+        <v>0.4158351195</v>
       </c>
     </row>
     <row r="415" ht="16" customHeight="1">
@@ -50578,12 +50518,12 @@
       </c>
       <c r="D415" s="18" t="inlineStr">
         <is>
-          <t>000408.SZ</t>
+          <t>605117.SS</t>
         </is>
       </c>
       <c r="E415" s="19" t="inlineStr">
         <is>
-          <t>Zangge Holding Company Limited</t>
+          <t>Ningbo Deye Technology Group Co., Ltd.</t>
         </is>
       </c>
       <c r="F415" s="26" t="inlineStr">
@@ -50593,16 +50533,16 @@
       </c>
       <c r="G415" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H415" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I415" s="22" t="n">
-        <v>16847484651.54443</v>
+        <v>16091288790.98633</v>
       </c>
       <c r="J415" s="23" t="inlineStr">
         <is>
@@ -50610,21 +50550,21 @@
         </is>
       </c>
       <c r="K415" s="22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L415" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M415" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, OwnerOperator, LargeCapQuality, StrongCoverage,</t>
+          <t>FixedCost+DemandShock, LargeCapQuality, StrongCoverage, LynchPEGY, Fly</t>
         </is>
       </c>
       <c r="N415" s="24" t="n">
-        <v>0.3973707203500089</v>
+        <v>0.4542315256215689</v>
       </c>
       <c r="O415" s="24" t="n">
-        <v>0.4158351195</v>
+        <v>0.4155419388000001</v>
       </c>
     </row>
     <row r="416" ht="16" customHeight="1">
@@ -50638,22 +50578,22 @@
       </c>
       <c r="D416" s="18" t="inlineStr">
         <is>
-          <t>605117.SS</t>
+          <t>BECEF</t>
         </is>
       </c>
       <c r="E416" s="19" t="inlineStr">
         <is>
-          <t>Ningbo Deye Technology Group Co., Ltd.</t>
+          <t>BCE Inc.</t>
         </is>
       </c>
       <c r="F416" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G416" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H416" s="16" t="inlineStr">
@@ -50662,7 +50602,7 @@
         </is>
       </c>
       <c r="I416" s="22" t="n">
-        <v>16091288790.98633</v>
+        <v>13843309367.2</v>
       </c>
       <c r="J416" s="23" t="inlineStr">
         <is>
@@ -50670,21 +50610,21 @@
         </is>
       </c>
       <c r="K416" s="22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L416" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M416" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, LargeCapQuality, StrongCoverage, LynchPEGY, Fly</t>
+          <t>CapitalReturner, Weinstein-Stage2, LynchEV-GY, Forensic-OverDepreciate</t>
         </is>
       </c>
       <c r="N416" s="24" t="n">
-        <v>0.4542315256215689</v>
+        <v>0.3551236632141656</v>
       </c>
       <c r="O416" s="24" t="n">
-        <v>0.4155419388000001</v>
+        <v>0.4154943</v>
       </c>
     </row>
     <row r="417" ht="16" customHeight="1">
@@ -50698,17 +50638,17 @@
       </c>
       <c r="D417" s="18" t="inlineStr">
         <is>
-          <t>BECEF</t>
+          <t>035720.KS</t>
         </is>
       </c>
       <c r="E417" s="19" t="inlineStr">
         <is>
-          <t>BCE Inc.</t>
+          <t>Kakao Corp.</t>
         </is>
       </c>
       <c r="F417" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G417" s="21" t="inlineStr">
@@ -50722,7 +50662,7 @@
         </is>
       </c>
       <c r="I417" s="22" t="n">
-        <v>13843309367.2</v>
+        <v>9944268598.80011</v>
       </c>
       <c r="J417" s="23" t="inlineStr">
         <is>
@@ -50730,21 +50670,21 @@
         </is>
       </c>
       <c r="K417" s="22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L417" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M417" s="21" t="inlineStr">
         <is>
-          <t>CapitalReturner, Weinstein-Stage2, LynchEV-GY, Forensic-OverDepreciate</t>
+          <t>NarrativeLag, CapitalDiscipline, DeadOption, OwnerOperator, MidCapGARP</t>
         </is>
       </c>
       <c r="N417" s="24" t="n">
-        <v>0.3551236632141656</v>
+        <v>0.3579927189939343</v>
       </c>
       <c r="O417" s="24" t="n">
-        <v>0.4154943</v>
+        <v>0.41547952</v>
       </c>
     </row>
     <row r="418" ht="16" customHeight="1">
@@ -50758,31 +50698,31 @@
       </c>
       <c r="D418" s="18" t="inlineStr">
         <is>
-          <t>035720.KS</t>
+          <t>002532.SZ</t>
         </is>
       </c>
       <c r="E418" s="19" t="inlineStr">
         <is>
-          <t>Kakao Corp.</t>
+          <t>Tianshan Aluminum Group Co., Ltd.</t>
         </is>
       </c>
       <c r="F418" s="26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G418" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H418" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I418" s="22" t="n">
-        <v>9944268598.80011</v>
+        <v>9044699053.419922</v>
       </c>
       <c r="J418" s="23" t="inlineStr">
         <is>
@@ -50790,21 +50730,21 @@
         </is>
       </c>
       <c r="K418" s="22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L418" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M418" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, DeadOption, OwnerOperator, MidCapGARP</t>
+          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, MidCapGARP, Cap</t>
         </is>
       </c>
       <c r="N418" s="24" t="n">
-        <v>0.3579927189939343</v>
+        <v>0.3644402200917971</v>
       </c>
       <c r="O418" s="24" t="n">
-        <v>0.41547952</v>
+        <v>0.4154725332</v>
       </c>
     </row>
     <row r="419" ht="16" customHeight="1">
@@ -50818,12 +50758,12 @@
       </c>
       <c r="D419" s="18" t="inlineStr">
         <is>
-          <t>002532.SZ</t>
+          <t>000733.SZ</t>
         </is>
       </c>
       <c r="E419" s="19" t="inlineStr">
         <is>
-          <t>Tianshan Aluminum Group Co., Ltd.</t>
+          <t>China Zhenhua (Group) Science &amp; Technology Co., Ltd</t>
         </is>
       </c>
       <c r="F419" s="26" t="inlineStr">
@@ -50833,7 +50773,7 @@
       </c>
       <c r="G419" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H419" s="16" t="inlineStr">
@@ -50842,7 +50782,7 @@
         </is>
       </c>
       <c r="I419" s="22" t="n">
-        <v>9044699053.419922</v>
+        <v>3346067423.612915</v>
       </c>
       <c r="J419" s="23" t="inlineStr">
         <is>
@@ -50850,21 +50790,21 @@
         </is>
       </c>
       <c r="K419" s="22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L419" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M419" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, MidCapGARP, Cap</t>
+          <t>NarrativeLag, DeadOption, StrongCoverage</t>
         </is>
       </c>
       <c r="N419" s="24" t="n">
-        <v>0.3644402200917971</v>
+        <v>0.3940748539926582</v>
       </c>
       <c r="O419" s="24" t="n">
-        <v>0.4154725332</v>
+        <v>0.4154352</v>
       </c>
     </row>
     <row r="420" ht="16" customHeight="1">
@@ -50878,31 +50818,31 @@
       </c>
       <c r="D420" s="18" t="inlineStr">
         <is>
-          <t>000733.SZ</t>
+          <t>PETFF</t>
         </is>
       </c>
       <c r="E420" s="19" t="inlineStr">
         <is>
-          <t>China Zhenhua (Group) Science &amp; Technology Co., Ltd</t>
+          <t>PTT Public Company Limited</t>
         </is>
       </c>
       <c r="F420" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G420" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H420" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I420" s="22" t="n">
-        <v>3346067423.612915</v>
+        <v>15829835776</v>
       </c>
       <c r="J420" s="23" t="inlineStr">
         <is>
@@ -50910,21 +50850,21 @@
         </is>
       </c>
       <c r="K420" s="22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L420" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M420" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, StrongCoverage</t>
+          <t>LargeCapQuality, CapitalReturner, LynchPEGY, LynchEV-GY, OakDeleveragi</t>
         </is>
       </c>
       <c r="N420" s="24" t="n">
-        <v>0.3940748539926582</v>
+        <v>0.3916436345083097</v>
       </c>
       <c r="O420" s="24" t="n">
-        <v>0.4154352</v>
+        <v>0.4153612535999999</v>
       </c>
     </row>
     <row r="421" ht="16" customHeight="1">
@@ -50938,31 +50878,31 @@
       </c>
       <c r="D421" s="18" t="inlineStr">
         <is>
-          <t>PETFF</t>
+          <t>000921.SZ</t>
         </is>
       </c>
       <c r="E421" s="19" t="inlineStr">
         <is>
-          <t>PTT Public Company Limited</t>
+          <t>Hisense Home Appliances Group Co. Ltd. Class H</t>
         </is>
       </c>
       <c r="F421" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G421" s="21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H421" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I421" s="22" t="n">
-        <v>15829835776</v>
+        <v>5960706300.015137</v>
       </c>
       <c r="J421" s="23" t="inlineStr">
         <is>
@@ -50970,21 +50910,21 @@
         </is>
       </c>
       <c r="K421" s="22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L421" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M421" s="21" t="inlineStr">
         <is>
-          <t>LargeCapQuality, CapitalReturner, LynchPEGY, LynchEV-GY, OakDeleveragi</t>
+          <t>MidCapGARP, BalanceSheetReturn, NetCashReturner, Weinstein-Stage2, Str</t>
         </is>
       </c>
       <c r="N421" s="24" t="n">
-        <v>0.3916436345083097</v>
+        <v>0.3507010982146961</v>
       </c>
       <c r="O421" s="24" t="n">
-        <v>0.4153612535999999</v>
+        <v>0.4153227764</v>
       </c>
     </row>
     <row r="422" ht="16" customHeight="1">
@@ -50998,22 +50938,22 @@
       </c>
       <c r="D422" s="18" t="inlineStr">
         <is>
-          <t>000921.SZ</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="E422" s="19" t="inlineStr">
         <is>
-          <t>Hisense Home Appliances Group Co. Ltd. Class H</t>
+          <t>Duolingo Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="F422" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G422" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H422" s="16" t="inlineStr">
@@ -51022,29 +50962,29 @@
         </is>
       </c>
       <c r="I422" s="22" t="n">
-        <v>5960706300.015137</v>
-      </c>
-      <c r="J422" s="23" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>6694498816</v>
+      </c>
+      <c r="J422" s="26" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K422" s="22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L422" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M422" s="21" t="inlineStr">
         <is>
-          <t>MidCapGARP, BalanceSheetReturn, NetCashReturner, Weinstein-Stage2, Str</t>
+          <t>NarrativeLag, DeadOption, MidCapGARP, StrongCoverage, BAB-Becoming, BA</t>
         </is>
       </c>
       <c r="N422" s="24" t="n">
-        <v>0.3507010982146961</v>
+        <v>0.4138522932726113</v>
       </c>
       <c r="O422" s="24" t="n">
-        <v>0.4153227764</v>
+        <v>0.4150627461999999</v>
       </c>
     </row>
     <row r="423" ht="16" customHeight="1">
@@ -51058,12 +50998,12 @@
       </c>
       <c r="D423" s="18" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>PARXF</t>
         </is>
       </c>
       <c r="E423" s="19" t="inlineStr">
         <is>
-          <t>Duolingo Inc. Class A Common Stock</t>
+          <t>Parex Resources Inc.</t>
         </is>
       </c>
       <c r="F423" s="26" t="inlineStr">
@@ -51073,7 +51013,7 @@
       </c>
       <c r="G423" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H423" s="16" t="inlineStr">
@@ -51082,29 +51022,29 @@
         </is>
       </c>
       <c r="I423" s="22" t="n">
-        <v>6694498816</v>
-      </c>
-      <c r="J423" s="26" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>2008243712</v>
+      </c>
+      <c r="J423" s="23" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K423" s="22" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L423" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M423" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, MidCapGARP, StrongCoverage, BAB-Becoming, BA</t>
+          <t>CapitalReturner, Weinstein-Stage2, LynchPEGY, LynchEV-GY, Forensic-Pay</t>
         </is>
       </c>
       <c r="N423" s="24" t="n">
-        <v>0.4138522932726113</v>
+        <v>0.4139473138304793</v>
       </c>
       <c r="O423" s="24" t="n">
-        <v>0.4150627461999999</v>
+        <v>0.4150038524</v>
       </c>
     </row>
     <row r="424" ht="16" customHeight="1">
@@ -51118,22 +51058,22 @@
       </c>
       <c r="D424" s="18" t="inlineStr">
         <is>
-          <t>PARXF</t>
+          <t>7988.T</t>
         </is>
       </c>
       <c r="E424" s="19" t="inlineStr">
         <is>
-          <t>Parex Resources Inc.</t>
+          <t>Nifco Inc.</t>
         </is>
       </c>
       <c r="F424" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G424" s="21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H424" s="16" t="inlineStr">
@@ -51142,7 +51082,7 @@
         </is>
       </c>
       <c r="I424" s="22" t="n">
-        <v>2008243712</v>
+        <v>2848831616.592395</v>
       </c>
       <c r="J424" s="23" t="inlineStr">
         <is>
@@ -51150,21 +51090,21 @@
         </is>
       </c>
       <c r="K424" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L424" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M424" s="21" t="inlineStr">
         <is>
-          <t>CapitalReturner, Weinstein-Stage2, LynchPEGY, LynchEV-GY, Forensic-Pay</t>
+          <t>QuietCompounder, Weinstein-Stage2, StrongCoverage, BAB-Becoming, Foren</t>
         </is>
       </c>
       <c r="N424" s="24" t="n">
-        <v>0.4139473138304793</v>
+        <v>0.3573928129339497</v>
       </c>
       <c r="O424" s="24" t="n">
-        <v>0.4150038524</v>
+        <v>0.4148926499999999</v>
       </c>
     </row>
     <row r="425" ht="16" customHeight="1">
@@ -51178,31 +51118,27 @@
       </c>
       <c r="D425" s="18" t="inlineStr">
         <is>
-          <t>7988.T</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="E425" s="19" t="inlineStr">
         <is>
-          <t>Nifco Inc.</t>
+          <t>PT Unilever Indonesia Tbk</t>
         </is>
       </c>
       <c r="F425" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G425" s="21" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="G425" s="21" t="n"/>
       <c r="H425" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Mega Cap</t>
         </is>
       </c>
       <c r="I425" s="22" t="n">
-        <v>2848831616.592395</v>
+        <v>3403429839.739838</v>
       </c>
       <c r="J425" s="23" t="inlineStr">
         <is>
@@ -51213,18 +51149,18 @@
         <v>7</v>
       </c>
       <c r="L425" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M425" s="21" t="inlineStr">
         <is>
-          <t>QuietCompounder, Weinstein-Stage2, StrongCoverage, BAB-Becoming, Foren</t>
+          <t>NarrativeLag, MidCapGARP, CapitalReturner, StrongCoverage, LynchEV-GY,</t>
         </is>
       </c>
       <c r="N425" s="24" t="n">
-        <v>0.3573928129339497</v>
+        <v>0.4034489395326359</v>
       </c>
       <c r="O425" s="24" t="n">
-        <v>0.4148926499999999</v>
+        <v>0.4148100095999999</v>
       </c>
     </row>
     <row r="426" ht="16" customHeight="1">
@@ -51238,27 +51174,31 @@
       </c>
       <c r="D426" s="18" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>DPW.F</t>
         </is>
       </c>
       <c r="E426" s="19" t="inlineStr">
         <is>
-          <t>PT Unilever Indonesia Tbk</t>
+          <t>Deutsche Post AG</t>
         </is>
       </c>
       <c r="F426" s="26" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="G426" s="21" t="n"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G426" s="21" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="H426" s="16" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I426" s="22" t="n">
-        <v>3403429839.739838</v>
+        <v>12360374018.39502</v>
       </c>
       <c r="J426" s="23" t="inlineStr">
         <is>
@@ -51266,21 +51206,21 @@
         </is>
       </c>
       <c r="K426" s="22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L426" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M426" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, CapitalReturner, StrongCoverage, LynchEV-GY,</t>
+          <t>LynchEV-GY, Forensic-PayoutConfirmed, Forensic-CannibalDiscount</t>
         </is>
       </c>
       <c r="N426" s="24" t="n">
-        <v>0.4034489395326359</v>
+        <v>0.3684196461383954</v>
       </c>
       <c r="O426" s="24" t="n">
-        <v>0.4148100095999999</v>
+        <v>0.41472945</v>
       </c>
     </row>
     <row r="427" ht="16" customHeight="1">
@@ -51294,31 +51234,31 @@
       </c>
       <c r="D427" s="18" t="inlineStr">
         <is>
-          <t>DPW.F</t>
+          <t>HTO.AT</t>
         </is>
       </c>
       <c r="E427" s="19" t="inlineStr">
         <is>
-          <t>Deutsche Post AG</t>
+          <t>Hellenic Telecommunications Organization S.A.</t>
         </is>
       </c>
       <c r="F427" s="26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G427" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H427" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I427" s="22" t="n">
-        <v>12360374018.39502</v>
+        <v>9320566820.531982</v>
       </c>
       <c r="J427" s="23" t="inlineStr">
         <is>
@@ -51326,21 +51266,21 @@
         </is>
       </c>
       <c r="K427" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L427" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M427" s="21" t="inlineStr">
         <is>
-          <t>LynchEV-GY, Forensic-PayoutConfirmed, Forensic-CannibalDiscount</t>
+          <t>CapitalDiscipline, MidCapGARP, Weinstein-Stage2, AnalystAwakening-52wH</t>
         </is>
       </c>
       <c r="N427" s="24" t="n">
-        <v>0.3684196461383954</v>
+        <v>0.3806646163630942</v>
       </c>
       <c r="O427" s="24" t="n">
-        <v>0.41472945</v>
+        <v>0.4145435800000001</v>
       </c>
     </row>
     <row r="428" ht="16" customHeight="1">
@@ -51354,31 +51294,31 @@
       </c>
       <c r="D428" s="18" t="inlineStr">
         <is>
-          <t>HTO.AT</t>
+          <t>EMBVF</t>
         </is>
       </c>
       <c r="E428" s="19" t="inlineStr">
         <is>
-          <t>Hellenic Telecommunications Organization S.A.</t>
+          <t>Arca Continental, S.A.B. de C.V.</t>
         </is>
       </c>
       <c r="F428" s="26" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G428" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H428" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I428" s="22" t="n">
-        <v>9320566820.531982</v>
+        <v>19580153856</v>
       </c>
       <c r="J428" s="23" t="inlineStr">
         <is>
@@ -51386,21 +51326,21 @@
         </is>
       </c>
       <c r="K428" s="22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L428" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M428" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, MidCapGARP, Weinstein-Stage2, AnalystAwakening-52wH</t>
+          <t>CapitalDiscipline, LargeCapQuality, LynchEV-GY, Forensic-OwnerEarnings</t>
         </is>
       </c>
       <c r="N428" s="24" t="n">
-        <v>0.3806646163630942</v>
+        <v>0.4140018598798103</v>
       </c>
       <c r="O428" s="24" t="n">
-        <v>0.4145435800000001</v>
+        <v>0.4144824648</v>
       </c>
     </row>
     <row r="429" ht="16" customHeight="1">
@@ -51414,12 +51354,12 @@
       </c>
       <c r="D429" s="18" t="inlineStr">
         <is>
-          <t>EMBVF</t>
+          <t>GPI</t>
         </is>
       </c>
       <c r="E429" s="19" t="inlineStr">
         <is>
-          <t>Arca Continental, S.A.B. de C.V.</t>
+          <t>Group 1 Automotive, Inc</t>
         </is>
       </c>
       <c r="F429" s="26" t="inlineStr">
@@ -51429,16 +51369,16 @@
       </c>
       <c r="G429" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H429" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I429" s="22" t="n">
-        <v>19580153856</v>
+        <v>3317597440</v>
       </c>
       <c r="J429" s="23" t="inlineStr">
         <is>
@@ -51446,21 +51386,21 @@
         </is>
       </c>
       <c r="K429" s="22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L429" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M429" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, LargeCapQuality, LynchEV-GY, Forensic-OwnerEarnings</t>
+          <t>NarrativeLag, LindyFCF, NoDilution, MidCapGARP, CapitalReturner, Conce</t>
         </is>
       </c>
       <c r="N429" s="24" t="n">
-        <v>0.4140018598798103</v>
+        <v>0.3793337601273714</v>
       </c>
       <c r="O429" s="24" t="n">
-        <v>0.4144824648</v>
+        <v>0.41425476</v>
       </c>
     </row>
     <row r="430" ht="16" customHeight="1">
@@ -51474,22 +51414,22 @@
       </c>
       <c r="D430" s="18" t="inlineStr">
         <is>
-          <t>GPI</t>
+          <t>1801.HK</t>
         </is>
       </c>
       <c r="E430" s="19" t="inlineStr">
         <is>
-          <t>Group 1 Automotive, Inc</t>
+          <t>Innovent Biologics Inc.</t>
         </is>
       </c>
       <c r="F430" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G430" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H430" s="16" t="inlineStr">
@@ -51498,7 +51438,7 @@
         </is>
       </c>
       <c r="I430" s="22" t="n">
-        <v>3317597440</v>
+        <v>20817252141.2312</v>
       </c>
       <c r="J430" s="23" t="inlineStr">
         <is>
@@ -51506,21 +51446,21 @@
         </is>
       </c>
       <c r="K430" s="22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L430" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M430" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, LindyFCF, NoDilution, MidCapGARP, CapitalReturner, Conce</t>
+          <t>KPIThreshold, Weinstein-Stage2, StrongCoverage, AnalystAwakening-52wHi</t>
         </is>
       </c>
       <c r="N430" s="24" t="n">
-        <v>0.3793337601273714</v>
+        <v>0.3678815299233989</v>
       </c>
       <c r="O430" s="24" t="n">
-        <v>0.41425476</v>
+        <v>0.4140876</v>
       </c>
     </row>
     <row r="431" ht="16" customHeight="1">
@@ -51534,31 +51474,31 @@
       </c>
       <c r="D431" s="18" t="inlineStr">
         <is>
-          <t>1801.HK</t>
+          <t>AHCHF</t>
         </is>
       </c>
       <c r="E431" s="19" t="inlineStr">
         <is>
-          <t>Innovent Biologics Inc.</t>
+          <t>Anhui Conch Cement Company Limited</t>
         </is>
       </c>
       <c r="F431" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G431" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H431" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I431" s="22" t="n">
-        <v>20817252141.2312</v>
+        <v>14838046720</v>
       </c>
       <c r="J431" s="23" t="inlineStr">
         <is>
@@ -51566,21 +51506,21 @@
         </is>
       </c>
       <c r="K431" s="22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L431" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M431" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Weinstein-Stage2, StrongCoverage, AnalystAwakening-52wHi</t>
+          <t>NarrativeLag, NetCashReturner, StrongCoverage, HiddenAssets-Overcap, F</t>
         </is>
       </c>
       <c r="N431" s="24" t="n">
-        <v>0.3678815299233989</v>
+        <v>0.3904570354425637</v>
       </c>
       <c r="O431" s="24" t="n">
-        <v>0.4140876</v>
+        <v>0.4140411</v>
       </c>
     </row>
     <row r="432" ht="16" customHeight="1">
@@ -51594,12 +51534,12 @@
       </c>
       <c r="D432" s="18" t="inlineStr">
         <is>
-          <t>AHCHF</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="E432" s="19" t="inlineStr">
         <is>
-          <t>Anhui Conch Cement Company Limited</t>
+          <t>Alliance Resource Partners, L.P.</t>
         </is>
       </c>
       <c r="F432" s="26" t="inlineStr">
@@ -51614,11 +51554,11 @@
       </c>
       <c r="H432" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I432" s="22" t="n">
-        <v>14838046720</v>
+        <v>3413318144</v>
       </c>
       <c r="J432" s="23" t="inlineStr">
         <is>
@@ -51626,21 +51566,21 @@
         </is>
       </c>
       <c r="K432" s="22" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L432" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M432" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, NetCashReturner, StrongCoverage, HiddenAssets-Overcap, F</t>
+          <t>NarrativeLag, CapitalDiscipline, LindyMargin, LindyFCF, NoDilution, Ca</t>
         </is>
       </c>
       <c r="N432" s="24" t="n">
-        <v>0.3904570354425637</v>
+        <v>0.3781315075450787</v>
       </c>
       <c r="O432" s="24" t="n">
-        <v>0.4140411</v>
+        <v>0.4140308788000001</v>
       </c>
     </row>
     <row r="433" ht="16" customHeight="1">
@@ -51654,12 +51594,12 @@
       </c>
       <c r="D433" s="18" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="E433" s="19" t="inlineStr">
         <is>
-          <t>Alliance Resource Partners, L.P.</t>
+          <t>Exelixis, Inc.</t>
         </is>
       </c>
       <c r="F433" s="26" t="inlineStr">
@@ -51669,16 +51609,16 @@
       </c>
       <c r="G433" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H433" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I433" s="22" t="n">
-        <v>3413318144</v>
+        <v>13905508352</v>
       </c>
       <c r="J433" s="23" t="inlineStr">
         <is>
@@ -51686,21 +51626,21 @@
         </is>
       </c>
       <c r="K433" s="22" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L433" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M433" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, LindyMargin, LindyFCF, NoDilution, Ca</t>
+          <t>CapitalDiscipline, CheapPerROIIC, LindyMargin, LindyFCF, NoDilution, B</t>
         </is>
       </c>
       <c r="N433" s="24" t="n">
-        <v>0.3781315075450787</v>
+        <v>0.3915092230673357</v>
       </c>
       <c r="O433" s="24" t="n">
-        <v>0.4140308788000001</v>
+        <v>0.4139676528</v>
       </c>
     </row>
     <row r="434" ht="16" customHeight="1">
@@ -51714,12 +51654,12 @@
       </c>
       <c r="D434" s="18" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>ALFVF</t>
         </is>
       </c>
       <c r="E434" s="19" t="inlineStr">
         <is>
-          <t>Exelixis, Inc.</t>
+          <t>Alfa Laval AB (publ)</t>
         </is>
       </c>
       <c r="F434" s="26" t="inlineStr">
@@ -51729,7 +51669,7 @@
       </c>
       <c r="G434" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H434" s="16" t="inlineStr">
@@ -51738,7 +51678,7 @@
         </is>
       </c>
       <c r="I434" s="22" t="n">
-        <v>13905508352</v>
+        <v>24592914432</v>
       </c>
       <c r="J434" s="23" t="inlineStr">
         <is>
@@ -51746,21 +51686,21 @@
         </is>
       </c>
       <c r="K434" s="22" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L434" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M434" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, CheapPerROIIC, LindyMargin, LindyFCF, NoDilution, B</t>
+          <t>BAB-Becoming, Forensic-OwnerEarnings, Forensic-PayoutConfirmed</t>
         </is>
       </c>
       <c r="N434" s="24" t="n">
-        <v>0.3915092230673357</v>
+        <v>0.4466159478357573</v>
       </c>
       <c r="O434" s="24" t="n">
-        <v>0.4139676528</v>
+        <v>0.413928816</v>
       </c>
     </row>
     <row r="435" ht="16" customHeight="1">
@@ -52826,14 +52766,14 @@
         </is>
       </c>
       <c r="K452" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L452" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M452" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, MidCapGARP, BAB-Becoming, BAB-Multibagger, X</t>
+          <t>NarrativeLag, DeadOption, BAB-Becoming, BAB-Multibagger, XR-ForcedSell</t>
         </is>
       </c>
       <c r="N452" s="24" t="n">
@@ -53186,7 +53126,7 @@
         </is>
       </c>
       <c r="K458" s="22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L458" s="22" t="n">
         <v>2</v>

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 4,208 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (217) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (216) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3775) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 4,211 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (217) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (216) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3778) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>3,775</t>
+          <t>3,778</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 4,211 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (217) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (216) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3778) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 4,212 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (217) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (216) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3779) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>3,778</t>
+          <t>3,779</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'STRICT'!$B$3:$O$220</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'STRONG'!$B$3:$O$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'STRONG'!$B$3:$O$220</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CANDIDATE_Top500'!$B$3:$O$503</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 4,212 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (217) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (216) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3779) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 4,229 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (217) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (217) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3795) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>3,779</t>
+          <t>3,795</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="K36" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L36" s="22" t="n">
         <v>5</v>
@@ -5228,14 +5228,14 @@
         </is>
       </c>
       <c r="K74" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L74" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M74" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, KPIThreshold, For</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, KPIThreshold, Oak</t>
         </is>
       </c>
       <c r="N74" s="24" t="n">
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="K80" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L80" s="22" t="n">
         <v>3</v>
@@ -6188,14 +6188,14 @@
         </is>
       </c>
       <c r="K90" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L90" s="22" t="n">
         <v>5</v>
       </c>
       <c r="M90" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Weinstein-Stage2, LynchPEGY, LynchEV-GY, CheapSalesScale</t>
+          <t>KPIThreshold, Weinstein-Stage2, LynchPEGY, LynchEV-GY, OakDeleveraging</t>
         </is>
       </c>
       <c r="N90" s="24" t="n">
@@ -6368,14 +6368,14 @@
         </is>
       </c>
       <c r="K93" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L93" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M93" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, LynchPEGY, LynchEV-GY, NegativeEV-Value, TenBag</t>
+          <t>FixedCost+DemandShock, LynchPEGY, LynchEV-GY, OakDeleveraging, Negativ</t>
         </is>
       </c>
       <c r="N93" s="24" t="n">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="K95" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L95" s="22" t="n">
         <v>3</v>
@@ -7148,14 +7148,14 @@
         </is>
       </c>
       <c r="K106" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L106" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M106" s="21" t="inlineStr">
         <is>
-          <t>MidCapGARP, LynchPEGY, LynchEV-GY, Forensic-PayoutConfirmed, Forensic-</t>
+          <t>MidCapGARP, LynchPEGY, LynchEV-GY, OakDeleveraging, Forensic-PayoutCon</t>
         </is>
       </c>
       <c r="N106" s="24" t="n">
@@ -7508,14 +7508,14 @@
         </is>
       </c>
       <c r="K112" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L112" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M112" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchPEGY, LynchEV-GY, Forensic-OverDepreciated, Forensi</t>
+          <t>KPIThreshold, LynchPEGY, LynchEV-GY, OakDeleveraging, Forensic-OverDep</t>
         </is>
       </c>
       <c r="N112" s="24" t="n">
@@ -8820,14 +8820,14 @@
         </is>
       </c>
       <c r="K134" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L134" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M134" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, KPIThreshold, MidCapGARP, LynchEV-GY, OakDee</t>
+          <t>NarrativeLag, DeadOption, KPIThreshold, MidCapGARP, LynchEV-GY, OakDel</t>
         </is>
       </c>
       <c r="N134" s="24" t="n">
@@ -8940,14 +8940,14 @@
         </is>
       </c>
       <c r="K136" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L136" s="22" t="n">
         <v>5</v>
       </c>
       <c r="M136" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchEV-GY, Forensic-OverDepreciated, Forensic-PayoutCon</t>
+          <t>KPIThreshold, LynchEV-GY, OakDeleveraging, Forensic-OverDepreciated, F</t>
         </is>
       </c>
       <c r="N136" s="24" t="n">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="K138" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L138" s="22" t="n">
         <v>3</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="K139" s="22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L139" s="22" t="n">
         <v>5</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="K145" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L145" s="22" t="n">
         <v>5</v>
@@ -9960,14 +9960,14 @@
         </is>
       </c>
       <c r="K153" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L153" s="22" t="n">
         <v>5</v>
       </c>
       <c r="M153" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Weinstein-Stage2, LynchPEGY, LynchEV-GY, CheapSalesScale</t>
+          <t>KPIThreshold, Weinstein-Stage2, LynchPEGY, LynchEV-GY, OakDeleveraging</t>
         </is>
       </c>
       <c r="N153" s="24" t="n">
@@ -10020,14 +10020,14 @@
         </is>
       </c>
       <c r="K154" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L154" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M154" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, LargeCapQuality, MidCapGARP, LynchPEGY, XR-ForensicFloor</t>
+          <t>NarrativeLag, LargeCapQuality, MidCapGARP, LynchPEGY, OakDeleveraging,</t>
         </is>
       </c>
       <c r="N154" s="24" t="n">
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="K159" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L159" s="22" t="n">
         <v>3</v>
@@ -10380,7 +10380,7 @@
         </is>
       </c>
       <c r="K160" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L160" s="22" t="n">
         <v>4</v>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="K173" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L173" s="22" t="n">
         <v>3</v>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="K178" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L178" s="22" t="n">
         <v>4</v>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="K181" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L181" s="22" t="n">
         <v>4</v>
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="K191" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L191" s="22" t="n">
         <v>3</v>
@@ -13380,14 +13380,14 @@
         </is>
       </c>
       <c r="K210" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L210" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M210" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchPEGY, LynchEV-GY, Forensic-UnderstatedE, Forensic-P</t>
+          <t>KPIThreshold, LynchPEGY, LynchEV-GY, OakDeleveraging, Forensic-Underst</t>
         </is>
       </c>
       <c r="N210" s="24" t="n">
@@ -13920,14 +13920,14 @@
         </is>
       </c>
       <c r="K219" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L219" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M219" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchEV-GY, Forensic-PayoutConfirmed, Forensic-SelfFunde</t>
+          <t>KPIThreshold, LynchEV-GY, OakDeleveraging, Forensic-PayoutConfirmed, F</t>
         </is>
       </c>
       <c r="N219" s="24" t="n">
@@ -14013,7 +14013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O219"/>
+  <dimension ref="A1:O220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -14037,7 +14037,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG — watchlist — 216 names</t>
+          <t xml:space="preserve">  STRONG — watchlist — 217 names</t>
         </is>
       </c>
       <c r="B1" s="11" t="n"/>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="K73" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L73" s="22" t="n">
         <v>3</v>
@@ -19375,14 +19375,14 @@
         </is>
       </c>
       <c r="K91" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L91" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M91" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, LynchEV-GY, LigerLaggingInflect</t>
+          <t>NarrativeLag, MidCapGARP, LynchEV-GY, LigerLaggingInflect, OakDelevera</t>
         </is>
       </c>
       <c r="N91" s="24" t="n">
@@ -19731,14 +19731,14 @@
         </is>
       </c>
       <c r="K97" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L97" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M97" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, OakDeepValue, XR-Asse</t>
+          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, OakDeleveraging, OakD</t>
         </is>
       </c>
       <c r="N97" s="24" t="n">
@@ -20991,7 +20991,7 @@
         </is>
       </c>
       <c r="K118" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L118" s="22" t="n">
         <v>3</v>
@@ -21831,14 +21831,14 @@
         </is>
       </c>
       <c r="K132" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L132" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M132" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, XR-LatentInflectionFl</t>
+          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, OakDeleveraging, XR-L</t>
         </is>
       </c>
       <c r="N132" s="24" t="n">
@@ -22219,12 +22219,12 @@
       </c>
       <c r="D139" s="18" t="inlineStr">
         <is>
-          <t>NJDCY</t>
+          <t>KBSTF</t>
         </is>
       </c>
       <c r="E139" s="19" t="inlineStr">
         <is>
-          <t>Nidec Corp.</t>
+          <t>Kobe Steel, Ltd.</t>
         </is>
       </c>
       <c r="F139" s="26" t="inlineStr">
@@ -22234,16 +22234,16 @@
       </c>
       <c r="G139" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H139" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I139" s="22" t="n">
-        <v>17872109568</v>
+        <v>5014344704</v>
       </c>
       <c r="J139" s="25" t="inlineStr">
         <is>
@@ -22251,21 +22251,21 @@
         </is>
       </c>
       <c r="K139" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L139" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M139" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, BAB-Becoming, LynchPEGY, XR-Foren</t>
+          <t>OakDeleveraging, Forensic-OverDepreciated, Forensic-PayoutConfirmed</t>
         </is>
       </c>
       <c r="N139" s="24" t="n">
-        <v>0.3921379635500283</v>
+        <v>0.3753235416018903</v>
       </c>
       <c r="O139" s="24" t="n">
-        <v>0.391039792</v>
+        <v>0.3912970944</v>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1">
@@ -22279,12 +22279,12 @@
       </c>
       <c r="D140" s="18" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>NJDCY</t>
         </is>
       </c>
       <c r="E140" s="19" t="inlineStr">
         <is>
-          <t>Global-E Online Ltd.</t>
+          <t>Nidec Corp.</t>
         </is>
       </c>
       <c r="F140" s="26" t="inlineStr">
@@ -22294,16 +22294,16 @@
       </c>
       <c r="G140" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H140" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I140" s="22" t="n">
-        <v>6245027840</v>
+        <v>17872109568</v>
       </c>
       <c r="J140" s="25" t="inlineStr">
         <is>
@@ -22311,21 +22311,21 @@
         </is>
       </c>
       <c r="K140" s="22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L140" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M140" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ROICInflect, TaxEfficient, StrongCoverage, BAB-Becoming,</t>
+          <t>NarrativeLag, FixedCost+DemandShock, BAB-Becoming, LynchPEGY, XR-Foren</t>
         </is>
       </c>
       <c r="N140" s="24" t="n">
-        <v>0.3672068470436617</v>
+        <v>0.3921379635500283</v>
       </c>
       <c r="O140" s="24" t="n">
-        <v>0.390964938</v>
+        <v>0.391039792</v>
       </c>
     </row>
     <row r="141" ht="16" customHeight="1">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="D141" s="18" t="inlineStr">
         <is>
-          <t>NNDNF</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="E141" s="19" t="inlineStr">
         <is>
-          <t>Nidec Corp.</t>
+          <t>Global-E Online Ltd.</t>
         </is>
       </c>
       <c r="F141" s="26" t="inlineStr">
@@ -22354,16 +22354,16 @@
       </c>
       <c r="G141" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H141" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I141" s="22" t="n">
-        <v>19198672896</v>
+        <v>6245027840</v>
       </c>
       <c r="J141" s="25" t="inlineStr">
         <is>
@@ -22371,21 +22371,21 @@
         </is>
       </c>
       <c r="K141" s="22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L141" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M141" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, BAB-Becoming, Lyn</t>
+          <t>KPIThreshold, ROICInflect, TaxEfficient, StrongCoverage, BAB-Becoming,</t>
         </is>
       </c>
       <c r="N141" s="24" t="n">
-        <v>0.391851000844459</v>
+        <v>0.3672068470436617</v>
       </c>
       <c r="O141" s="24" t="n">
-        <v>0.3907539279999999</v>
+        <v>0.390964938</v>
       </c>
     </row>
     <row r="142" ht="16" customHeight="1">
@@ -22399,12 +22399,12 @@
       </c>
       <c r="D142" s="18" t="inlineStr">
         <is>
-          <t>KPTCY</t>
+          <t>NNDNF</t>
         </is>
       </c>
       <c r="E142" s="19" t="inlineStr">
         <is>
-          <t>Kansai Paint Co., Ltd.</t>
+          <t>Nidec Corp.</t>
         </is>
       </c>
       <c r="F142" s="26" t="inlineStr">
@@ -22414,16 +22414,16 @@
       </c>
       <c r="G142" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H142" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I142" s="22" t="n">
-        <v>2848554752</v>
+        <v>19198672896</v>
       </c>
       <c r="J142" s="25" t="inlineStr">
         <is>
@@ -22431,21 +22431,21 @@
         </is>
       </c>
       <c r="K142" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L142" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M142" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, BalanceSheetReturn, LigerLaggingInflect, CashAdjPE-NegOr</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, BAB-Becoming, Lyn</t>
         </is>
       </c>
       <c r="N142" s="24" t="n">
-        <v>0.3710612178554294</v>
+        <v>0.391851000844459</v>
       </c>
       <c r="O142" s="24" t="n">
-        <v>0.389591903</v>
+        <v>0.3907539279999999</v>
       </c>
     </row>
     <row r="143" ht="16" customHeight="1">
@@ -22459,22 +22459,22 @@
       </c>
       <c r="D143" s="18" t="inlineStr">
         <is>
-          <t>ANN.AX</t>
+          <t>KPTCY</t>
         </is>
       </c>
       <c r="E143" s="19" t="inlineStr">
         <is>
-          <t>Ansell Limited</t>
+          <t>Kansai Paint Co., Ltd.</t>
         </is>
       </c>
       <c r="F143" s="26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G143" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H143" s="16" t="inlineStr">
@@ -22483,7 +22483,7 @@
         </is>
       </c>
       <c r="I143" s="22" t="n">
-        <v>4084636989.372345</v>
+        <v>2848554752</v>
       </c>
       <c r="J143" s="25" t="inlineStr">
         <is>
@@ -22491,21 +22491,21 @@
         </is>
       </c>
       <c r="K143" s="22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L143" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M143" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, Weinstein-Stage2, Kullamagi-Breakout, LynchPEGY, LynchEV</t>
+          <t>NarrativeLag, BalanceSheetReturn, LigerLaggingInflect, CashAdjPE-NegOr</t>
         </is>
       </c>
       <c r="N143" s="24" t="n">
-        <v>0.3857511141741039</v>
+        <v>0.3710612178554294</v>
       </c>
       <c r="O143" s="24" t="n">
-        <v>0.389184296</v>
+        <v>0.389591903</v>
       </c>
     </row>
     <row r="144" ht="16" customHeight="1">
@@ -22519,22 +22519,22 @@
       </c>
       <c r="D144" s="18" t="inlineStr">
         <is>
-          <t>002151.SZ</t>
+          <t>ANN.AX</t>
         </is>
       </c>
       <c r="E144" s="19" t="inlineStr">
         <is>
-          <t>Beijing BDStar Navigation Co., Ltd.</t>
+          <t>Ansell Limited</t>
         </is>
       </c>
       <c r="F144" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G144" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H144" s="16" t="inlineStr">
@@ -22543,7 +22543,7 @@
         </is>
       </c>
       <c r="I144" s="22" t="n">
-        <v>2319137505.357178</v>
+        <v>4084636989.372345</v>
       </c>
       <c r="J144" s="25" t="inlineStr">
         <is>
@@ -22551,21 +22551,21 @@
         </is>
       </c>
       <c r="K144" s="22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L144" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M144" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, LigerLaggingInflect, TenBaggerPath, EVSa</t>
+          <t>NarrativeLag, Weinstein-Stage2, Kullamagi-Breakout, LynchPEGY, LynchEV</t>
         </is>
       </c>
       <c r="N144" s="24" t="n">
-        <v>0.3761359066663185</v>
+        <v>0.3857511141741039</v>
       </c>
       <c r="O144" s="24" t="n">
-        <v>0.388961778</v>
+        <v>0.389184296</v>
       </c>
     </row>
     <row r="145" ht="16" customHeight="1">
@@ -22579,31 +22579,31 @@
       </c>
       <c r="D145" s="18" t="inlineStr">
         <is>
-          <t>WHGLY</t>
+          <t>002151.SZ</t>
         </is>
       </c>
       <c r="E145" s="19" t="inlineStr">
         <is>
-          <t>WH Group Limited</t>
+          <t>Beijing BDStar Navigation Co., Ltd.</t>
         </is>
       </c>
       <c r="F145" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G145" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H145" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I145" s="22" t="n">
-        <v>10856197120</v>
+        <v>2319137505.357178</v>
       </c>
       <c r="J145" s="25" t="inlineStr">
         <is>
@@ -22614,18 +22614,18 @@
         <v>5</v>
       </c>
       <c r="L145" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M145" s="21" t="inlineStr">
         <is>
-          <t>CapitalReturner, LynchEV-GY, LigerLaggingInflect, Forensic-Understated</t>
+          <t>KPIThreshold, StrongCoverage, LigerLaggingInflect, TenBaggerPath, EVSa</t>
         </is>
       </c>
       <c r="N145" s="24" t="n">
-        <v>0.3638064698017346</v>
+        <v>0.3761359066663185</v>
       </c>
       <c r="O145" s="24" t="n">
-        <v>0.3889166028</v>
+        <v>0.388961778</v>
       </c>
     </row>
     <row r="146" ht="16" customHeight="1">
@@ -22639,31 +22639,31 @@
       </c>
       <c r="D146" s="18" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>WHGLY</t>
         </is>
       </c>
       <c r="E146" s="19" t="inlineStr">
         <is>
-          <t>Independent Bank Corp.</t>
+          <t>WH Group Limited</t>
         </is>
       </c>
       <c r="F146" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G146" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H146" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I146" s="22" t="n">
-        <v>3919319296</v>
+        <v>10856197120</v>
       </c>
       <c r="J146" s="25" t="inlineStr">
         <is>
@@ -22671,21 +22671,21 @@
         </is>
       </c>
       <c r="K146" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L146" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M146" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
+          <t>CapitalReturner, LynchEV-GY, LigerLaggingInflect, Forensic-Understated</t>
         </is>
       </c>
       <c r="N146" s="24" t="n">
-        <v>0.361219333070793</v>
+        <v>0.3638064698017346</v>
       </c>
       <c r="O146" s="24" t="n">
-        <v>0.388816012</v>
+        <v>0.3889166028</v>
       </c>
     </row>
     <row r="147" ht="16" customHeight="1">
@@ -22699,22 +22699,22 @@
       </c>
       <c r="D147" s="18" t="inlineStr">
         <is>
-          <t>KAP.F</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="E147" s="19" t="inlineStr">
         <is>
-          <t>Kansai Paint Co., Ltd.</t>
+          <t>Independent Bank Corp.</t>
         </is>
       </c>
       <c r="F147" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G147" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H147" s="16" t="inlineStr">
@@ -22723,7 +22723,7 @@
         </is>
       </c>
       <c r="I147" s="22" t="n">
-        <v>3196878534.611938</v>
+        <v>3919319296</v>
       </c>
       <c r="J147" s="25" t="inlineStr">
         <is>
@@ -22731,21 +22731,21 @@
         </is>
       </c>
       <c r="K147" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L147" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M147" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, BalanceSheetReturn, LigerLaggingInflect, NegativeEV-Valu</t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
         </is>
       </c>
       <c r="N147" s="24" t="n">
-        <v>0.3697911019670961</v>
+        <v>0.361219333070793</v>
       </c>
       <c r="O147" s="24" t="n">
-        <v>0.3882584792</v>
+        <v>0.388816012</v>
       </c>
     </row>
     <row r="148" ht="16" customHeight="1">
@@ -22759,17 +22759,17 @@
       </c>
       <c r="D148" s="18" t="inlineStr">
         <is>
-          <t>300037.SZ</t>
+          <t>KAP.F</t>
         </is>
       </c>
       <c r="E148" s="19" t="inlineStr">
         <is>
-          <t>Shenzhen Capchem Technology Co., Ltd.</t>
+          <t>Kansai Paint Co., Ltd.</t>
         </is>
       </c>
       <c r="F148" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G148" s="21" t="inlineStr">
@@ -22783,7 +22783,7 @@
         </is>
       </c>
       <c r="I148" s="22" t="n">
-        <v>7970660141.971191</v>
+        <v>3196878534.611938</v>
       </c>
       <c r="J148" s="25" t="inlineStr">
         <is>
@@ -22791,21 +22791,21 @@
         </is>
       </c>
       <c r="K148" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L148" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M148" s="21" t="inlineStr">
         <is>
-          <t>StrongCoverage, LynchPEGY, TenBaggerPath, TenBaggerPath-Credible</t>
+          <t>NarrativeLag, BalanceSheetReturn, LigerLaggingInflect, NegativeEV-Valu</t>
         </is>
       </c>
       <c r="N148" s="24" t="n">
-        <v>0.3713001478339162</v>
+        <v>0.3697911019670961</v>
       </c>
       <c r="O148" s="24" t="n">
-        <v>0.3879379530000001</v>
+        <v>0.3882584792</v>
       </c>
     </row>
     <row r="149" ht="16" customHeight="1">
@@ -22819,31 +22819,31 @@
       </c>
       <c r="D149" s="18" t="inlineStr">
         <is>
-          <t>SAF.PA</t>
+          <t>300037.SZ</t>
         </is>
       </c>
       <c r="E149" s="19" t="inlineStr">
         <is>
-          <t>Safran SA</t>
+          <t>Shenzhen Capchem Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="F149" s="26" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G149" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H149" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I149" s="22" t="n">
-        <v>157889622194.3906</v>
+        <v>7970660141.971191</v>
       </c>
       <c r="J149" s="25" t="inlineStr">
         <is>
@@ -22851,21 +22851,21 @@
         </is>
       </c>
       <c r="K149" s="22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L149" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M149" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, QuietCompounder, LargeCapQuality, Weinstein-Stage2, Stro</t>
+          <t>StrongCoverage, LynchPEGY, TenBaggerPath, TenBaggerPath-Credible</t>
         </is>
       </c>
       <c r="N149" s="24" t="n">
-        <v>0.3660304211525898</v>
+        <v>0.3713001478339162</v>
       </c>
       <c r="O149" s="24" t="n">
-        <v>0.3878014644</v>
+        <v>0.3879379530000001</v>
       </c>
     </row>
     <row r="150" ht="16" customHeight="1">
@@ -22879,27 +22879,31 @@
       </c>
       <c r="D150" s="18" t="inlineStr">
         <is>
-          <t>HONAUT.NS</t>
+          <t>SAF.PA</t>
         </is>
       </c>
       <c r="E150" s="19" t="inlineStr">
         <is>
-          <t>Honeywell Automation India Limited</t>
+          <t>Safran SA</t>
         </is>
       </c>
       <c r="F150" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G150" s="21" t="n"/>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G150" s="21" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="H150" s="16" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I150" s="22" t="n">
-        <v>3197273707.45102</v>
+        <v>157889622194.3906</v>
       </c>
       <c r="J150" s="25" t="inlineStr">
         <is>
@@ -22907,21 +22911,21 @@
         </is>
       </c>
       <c r="K150" s="22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L150" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M150" s="21" t="inlineStr">
         <is>
-          <t>StrongCoverage, LigerLaggingInflect, LynchReward-YearsInOne</t>
+          <t>KPIThreshold, QuietCompounder, LargeCapQuality, Weinstein-Stage2, Stro</t>
         </is>
       </c>
       <c r="N150" s="24" t="n">
-        <v>0.3727423030020012</v>
+        <v>0.3660304211525898</v>
       </c>
       <c r="O150" s="24" t="n">
-        <v>0.3857882</v>
+        <v>0.3878014644</v>
       </c>
     </row>
     <row r="151" ht="16" customHeight="1">
@@ -22935,31 +22939,27 @@
       </c>
       <c r="D151" s="18" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>HONAUT.NS</t>
         </is>
       </c>
       <c r="E151" s="19" t="inlineStr">
         <is>
-          <t>Bio-Rad Laboratories, Inc. Class A</t>
+          <t>Honeywell Automation India Limited</t>
         </is>
       </c>
       <c r="F151" s="26" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G151" s="21" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G151" s="21" t="n"/>
       <c r="H151" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Mega Cap</t>
         </is>
       </c>
       <c r="I151" s="22" t="n">
-        <v>9874942976</v>
+        <v>3197273707.45102</v>
       </c>
       <c r="J151" s="25" t="inlineStr">
         <is>
@@ -22967,21 +22967,21 @@
         </is>
       </c>
       <c r="K151" s="22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L151" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M151" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LindyMargin, LindyFCF, NoDilution, StrongCoverage, Geogr</t>
+          <t>StrongCoverage, LigerLaggingInflect, LynchReward-YearsInOne</t>
         </is>
       </c>
       <c r="N151" s="24" t="n">
-        <v>0.358304353516232</v>
+        <v>0.3727423030020012</v>
       </c>
       <c r="O151" s="24" t="n">
-        <v>0.3846469872</v>
+        <v>0.3857882</v>
       </c>
     </row>
     <row r="152" ht="16" customHeight="1">
@@ -22995,12 +22995,12 @@
       </c>
       <c r="D152" s="18" t="inlineStr">
         <is>
-          <t>CSPKF</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="E152" s="19" t="inlineStr">
         <is>
-          <t>COSCO SHIPPING Ports Limited</t>
+          <t>Bio-Rad Laboratories, Inc. Class A</t>
         </is>
       </c>
       <c r="F152" s="26" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="G152" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H152" s="16" t="inlineStr">
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="I152" s="22" t="n">
-        <v>2575635200</v>
+        <v>9874942976</v>
       </c>
       <c r="J152" s="25" t="inlineStr">
         <is>
@@ -23027,21 +23027,21 @@
         </is>
       </c>
       <c r="K152" s="22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L152" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M152" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, LynchPEGY, Forensic-UnderstatedE, Foren</t>
+          <t>KPIThreshold, LindyMargin, LindyFCF, NoDilution, StrongCoverage, Geogr</t>
         </is>
       </c>
       <c r="N152" s="24" t="n">
-        <v>0.3841295792935499</v>
+        <v>0.358304353516232</v>
       </c>
       <c r="O152" s="24" t="n">
-        <v>0.3841607304</v>
+        <v>0.3846469872</v>
       </c>
     </row>
     <row r="153" ht="16" customHeight="1">
@@ -23055,22 +23055,22 @@
       </c>
       <c r="D153" s="18" t="inlineStr">
         <is>
-          <t>SDF.F</t>
+          <t>CSPKF</t>
         </is>
       </c>
       <c r="E153" s="19" t="inlineStr">
         <is>
-          <t>K+S Aktiengesellschaft</t>
+          <t>COSCO SHIPPING Ports Limited</t>
         </is>
       </c>
       <c r="F153" s="26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G153" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H153" s="16" t="inlineStr">
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="I153" s="22" t="n">
-        <v>3403850671.506592</v>
+        <v>2575635200</v>
       </c>
       <c r="J153" s="25" t="inlineStr">
         <is>
@@ -23087,21 +23087,21 @@
         </is>
       </c>
       <c r="K153" s="22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L153" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M153" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, LynchEV-GY, NegativeEV-Value</t>
+          <t>NarrativeLag, CapitalReturner, LynchPEGY, Forensic-UnderstatedE, Foren</t>
         </is>
       </c>
       <c r="N153" s="24" t="n">
-        <v>0.3690623359922279</v>
+        <v>0.3841295792935499</v>
       </c>
       <c r="O153" s="24" t="n">
-        <v>0.3834698577</v>
+        <v>0.3841607304</v>
       </c>
     </row>
     <row r="154" ht="16" customHeight="1">
@@ -23115,31 +23115,31 @@
       </c>
       <c r="D154" s="18" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>SDF.F</t>
         </is>
       </c>
       <c r="E154" s="19" t="inlineStr">
         <is>
-          <t>Atlassian Corporation</t>
+          <t>K+S Aktiengesellschaft</t>
         </is>
       </c>
       <c r="F154" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G154" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H154" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I154" s="22" t="n">
-        <v>45489045504</v>
+        <v>3403850671.506592</v>
       </c>
       <c r="J154" s="25" t="inlineStr">
         <is>
@@ -23147,21 +23147,21 @@
         </is>
       </c>
       <c r="K154" s="22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L154" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M154" s="21" t="inlineStr">
         <is>
-          <t>Kullamagi-Breakout, StrongCoverage, GeographicGlobal, BAB-Becoming, As</t>
+          <t>NarrativeLag, FixedCost+DemandShock, LynchEV-GY, NegativeEV-Value</t>
         </is>
       </c>
       <c r="N154" s="24" t="n">
-        <v>0.3502736800079303</v>
+        <v>0.3690623359922279</v>
       </c>
       <c r="O154" s="24" t="n">
-        <v>0.3831238242</v>
+        <v>0.3834698577</v>
       </c>
     </row>
     <row r="155" ht="16" customHeight="1">
@@ -23175,12 +23175,12 @@
       </c>
       <c r="D155" s="18" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="E155" s="19" t="inlineStr">
         <is>
-          <t>AGCO Corporation</t>
+          <t>Atlassian Corporation</t>
         </is>
       </c>
       <c r="F155" s="26" t="inlineStr">
@@ -23190,16 +23190,16 @@
       </c>
       <c r="G155" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H155" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I155" s="22" t="n">
-        <v>8480842240</v>
+        <v>45489045504</v>
       </c>
       <c r="J155" s="25" t="inlineStr">
         <is>
@@ -23210,18 +23210,18 @@
         <v>7</v>
       </c>
       <c r="L155" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M155" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LindyFCF, NoDilution, CapitalReturner, GeographicGlobal,</t>
+          <t>Kullamagi-Breakout, StrongCoverage, GeographicGlobal, BAB-Becoming, As</t>
         </is>
       </c>
       <c r="N155" s="24" t="n">
-        <v>0.3706128876057463</v>
+        <v>0.3502736800079303</v>
       </c>
       <c r="O155" s="24" t="n">
-        <v>0.3830829072</v>
+        <v>0.3831238242</v>
       </c>
     </row>
     <row r="156" ht="16" customHeight="1">
@@ -23235,12 +23235,12 @@
       </c>
       <c r="D156" s="18" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="E156" s="19" t="inlineStr">
         <is>
-          <t>Albemarle Corporation</t>
+          <t>AGCO Corporation</t>
         </is>
       </c>
       <c r="F156" s="26" t="inlineStr">
@@ -23250,16 +23250,16 @@
       </c>
       <c r="G156" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H156" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I156" s="22" t="n">
-        <v>13867954176</v>
+        <v>8480842240</v>
       </c>
       <c r="J156" s="25" t="inlineStr">
         <is>
@@ -23267,21 +23267,21 @@
         </is>
       </c>
       <c r="K156" s="22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L156" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M156" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, DeadOption, KPIThreshold, GeographicGlobal, Lyn</t>
+          <t>KPIThreshold, LindyFCF, NoDilution, CapitalReturner, GeographicGlobal,</t>
         </is>
       </c>
       <c r="N156" s="24" t="n">
-        <v>0.3582195655093522</v>
+        <v>0.3706128876057463</v>
       </c>
       <c r="O156" s="24" t="n">
-        <v>0.3828153852</v>
+        <v>0.3830829072</v>
       </c>
     </row>
     <row r="157" ht="16" customHeight="1">
@@ -23295,17 +23295,17 @@
       </c>
       <c r="D157" s="18" t="inlineStr">
         <is>
-          <t>603737.SS</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="E157" s="19" t="inlineStr">
         <is>
-          <t>SKSHU Paint Co.,Ltd.</t>
+          <t>Albemarle Corporation</t>
         </is>
       </c>
       <c r="F157" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G157" s="21" t="inlineStr">
@@ -23315,11 +23315,11 @@
       </c>
       <c r="H157" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I157" s="22" t="n">
-        <v>2725960409.335937</v>
+        <v>13867954176</v>
       </c>
       <c r="J157" s="25" t="inlineStr">
         <is>
@@ -23327,21 +23327,21 @@
         </is>
       </c>
       <c r="K157" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L157" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M157" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, DeadOption, KPITh</t>
+          <t>FixedCost+DemandShock, DeadOption, KPIThreshold, GeographicGlobal, Lyn</t>
         </is>
       </c>
       <c r="N157" s="24" t="n">
-        <v>0.3714343729270581</v>
+        <v>0.3582195655093522</v>
       </c>
       <c r="O157" s="24" t="n">
-        <v>0.3822283294</v>
+        <v>0.3828153852</v>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1">
@@ -23355,22 +23355,22 @@
       </c>
       <c r="D158" s="18" t="inlineStr">
         <is>
-          <t>7733.T</t>
+          <t>603737.SS</t>
         </is>
       </c>
       <c r="E158" s="19" t="inlineStr">
         <is>
-          <t>Olympus Corporation</t>
+          <t>SKSHU Paint Co.,Ltd.</t>
         </is>
       </c>
       <c r="F158" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G158" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H158" s="16" t="inlineStr">
@@ -23379,7 +23379,7 @@
         </is>
       </c>
       <c r="I158" s="22" t="n">
-        <v>13053820012.70416</v>
+        <v>2725960409.335937</v>
       </c>
       <c r="J158" s="25" t="inlineStr">
         <is>
@@ -23387,21 +23387,21 @@
         </is>
       </c>
       <c r="K158" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L158" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M158" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, KPIThreshold, LargeCapQuality, LynchPEGY, LynchEV-GY, As</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, DeadOption, KPITh</t>
         </is>
       </c>
       <c r="N158" s="24" t="n">
-        <v>0.3538493502952167</v>
+        <v>0.3714343729270581</v>
       </c>
       <c r="O158" s="24" t="n">
-        <v>0.3821568000000001</v>
+        <v>0.3822283294</v>
       </c>
     </row>
     <row r="159" ht="16" customHeight="1">
@@ -23415,31 +23415,31 @@
       </c>
       <c r="D159" s="18" t="inlineStr">
         <is>
-          <t>SEOJF</t>
+          <t>7733.T</t>
         </is>
       </c>
       <c r="E159" s="19" t="inlineStr">
         <is>
-          <t>Stora Enso Oyj Class R</t>
+          <t>Olympus Corporation</t>
         </is>
       </c>
       <c r="F159" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H159" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I159" s="22" t="n">
-        <v>9463439360</v>
+        <v>13053820012.70416</v>
       </c>
       <c r="J159" s="25" t="inlineStr">
         <is>
@@ -23447,21 +23447,21 @@
         </is>
       </c>
       <c r="K159" s="22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L159" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M159" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, RegimeCyclical, KPIThreshold, BalanceSheetRetur</t>
+          <t>NarrativeLag, KPIThreshold, LargeCapQuality, LynchPEGY, LynchEV-GY, As</t>
         </is>
       </c>
       <c r="N159" s="24" t="n">
-        <v>0.3712952851410653</v>
+        <v>0.3538493502952167</v>
       </c>
       <c r="O159" s="24" t="n">
-        <v>0.3817512384</v>
+        <v>0.3821568000000001</v>
       </c>
     </row>
     <row r="160" ht="16" customHeight="1">
@@ -23475,31 +23475,31 @@
       </c>
       <c r="D160" s="18" t="inlineStr">
         <is>
-          <t>688390.SS</t>
+          <t>SEOJF</t>
         </is>
       </c>
       <c r="E160" s="19" t="inlineStr">
         <is>
-          <t>Jiangsu Goodwe Power Supply Technology Co., Ltd</t>
+          <t>Stora Enso Oyj Class R</t>
         </is>
       </c>
       <c r="F160" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H160" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I160" s="22" t="n">
-        <v>2062710538.162109</v>
+        <v>9463439360</v>
       </c>
       <c r="J160" s="25" t="inlineStr">
         <is>
@@ -23507,21 +23507,21 @@
         </is>
       </c>
       <c r="K160" s="22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L160" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M160" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, LynchPEGY, LynchEV-GY, LigerLaggingInfle</t>
+          <t>FixedCost+DemandShock, RegimeCyclical, KPIThreshold, BalanceSheetRetur</t>
         </is>
       </c>
       <c r="N160" s="24" t="n">
-        <v>0.3540865778268979</v>
+        <v>0.3712952851410653</v>
       </c>
       <c r="O160" s="24" t="n">
-        <v>0.3801509862</v>
+        <v>0.3817512384</v>
       </c>
     </row>
     <row r="161" ht="16" customHeight="1">
@@ -23535,31 +23535,31 @@
       </c>
       <c r="D161" s="18" t="inlineStr">
         <is>
-          <t>HWHG.F</t>
+          <t>688390.SS</t>
         </is>
       </c>
       <c r="E161" s="19" t="inlineStr">
         <is>
-          <t>Tata Steel Limited Sponsored GDR RegS</t>
+          <t>Jiangsu Goodwe Power Supply Technology Co., Ltd</t>
         </is>
       </c>
       <c r="F161" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G161" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H161" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I161" s="22" t="n">
-        <v>23607059969.18555</v>
+        <v>2062710538.162109</v>
       </c>
       <c r="J161" s="25" t="inlineStr">
         <is>
@@ -23567,21 +23567,21 @@
         </is>
       </c>
       <c r="K161" s="22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L161" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M161" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, LargeCapQuality, BAB-Becoming, LynchEV-GY</t>
+          <t>KPIThreshold, StrongCoverage, LynchPEGY, LynchEV-GY, LigerLaggingInfle</t>
         </is>
       </c>
       <c r="N161" s="24" t="n">
-        <v>0.3516241963426553</v>
+        <v>0.3540865778268979</v>
       </c>
       <c r="O161" s="24" t="n">
-        <v>0.3797544</v>
+        <v>0.3801509862</v>
       </c>
     </row>
     <row r="162" ht="16" customHeight="1">
@@ -23595,22 +23595,22 @@
       </c>
       <c r="D162" s="18" t="inlineStr">
         <is>
-          <t>OCDO.L</t>
+          <t>HWHG.F</t>
         </is>
       </c>
       <c r="E162" s="19" t="inlineStr">
         <is>
-          <t>Ocado Group plc</t>
+          <t>Tata Steel Limited Sponsored GDR RegS</t>
         </is>
       </c>
       <c r="F162" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G162" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H162" s="16" t="inlineStr">
@@ -23619,7 +23619,7 @@
         </is>
       </c>
       <c r="I162" s="22" t="n">
-        <v>2272372931.272613</v>
+        <v>23607059969.18555</v>
       </c>
       <c r="J162" s="25" t="inlineStr">
         <is>
@@ -23627,21 +23627,21 @@
         </is>
       </c>
       <c r="K162" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L162" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M162" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, KPIThreshold, CheapSalesScaler</t>
+          <t>FixedCost+DemandShock, LargeCapQuality, BAB-Becoming, LynchEV-GY</t>
         </is>
       </c>
       <c r="N162" s="24" t="n">
-        <v>0.3835453850086642</v>
+        <v>0.3516241963426553</v>
       </c>
       <c r="O162" s="24" t="n">
-        <v>0.3795720236</v>
+        <v>0.3797544</v>
       </c>
     </row>
     <row r="163" ht="16" customHeight="1">
@@ -23655,22 +23655,22 @@
       </c>
       <c r="D163" s="18" t="inlineStr">
         <is>
-          <t>NHYDY</t>
+          <t>OCDO.L</t>
         </is>
       </c>
       <c r="E163" s="19" t="inlineStr">
         <is>
-          <t>Norsk Hydro ASA</t>
+          <t>Ocado Group plc</t>
         </is>
       </c>
       <c r="F163" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G163" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H163" s="16" t="inlineStr">
@@ -23679,7 +23679,7 @@
         </is>
       </c>
       <c r="I163" s="22" t="n">
-        <v>18689798144</v>
+        <v>2272372931.272613</v>
       </c>
       <c r="J163" s="25" t="inlineStr">
         <is>
@@ -23687,21 +23687,21 @@
         </is>
       </c>
       <c r="K163" s="22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L163" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M163" s="21" t="inlineStr">
         <is>
-          <t>RegimeCyclical, LargeCapQuality, LynchPEGY, LynchEV-GY, Forensic-Owner</t>
+          <t>NarrativeLag, KPIThreshold, CheapSalesScaler</t>
         </is>
       </c>
       <c r="N163" s="24" t="n">
-        <v>0.3708078557306304</v>
+        <v>0.3835453850086642</v>
       </c>
       <c r="O163" s="24" t="n">
-        <v>0.3795496704</v>
+        <v>0.3795720236</v>
       </c>
     </row>
     <row r="164" ht="16" customHeight="1">
@@ -23715,12 +23715,12 @@
       </c>
       <c r="D164" s="18" t="inlineStr">
         <is>
-          <t>WMMVY</t>
+          <t>NHYDY</t>
         </is>
       </c>
       <c r="E164" s="19" t="inlineStr">
         <is>
-          <t>Wal-Mart de Mexico, S.A.B. de C.V.</t>
+          <t>Norsk Hydro ASA</t>
         </is>
       </c>
       <c r="F164" s="26" t="inlineStr">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="G164" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H164" s="16" t="inlineStr">
@@ -23739,7 +23739,7 @@
         </is>
       </c>
       <c r="I164" s="22" t="n">
-        <v>46150217728</v>
+        <v>18689798144</v>
       </c>
       <c r="J164" s="25" t="inlineStr">
         <is>
@@ -23747,21 +23747,21 @@
         </is>
       </c>
       <c r="K164" s="22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L164" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M164" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, LigerLaggingInflect, Forensic-OwnerEarnings, Forensic-Pa</t>
+          <t>RegimeCyclical, LargeCapQuality, LynchPEGY, LynchEV-GY, Forensic-Owner</t>
         </is>
       </c>
       <c r="N164" s="24" t="n">
-        <v>0.3604217619997997</v>
+        <v>0.3708078557306304</v>
       </c>
       <c r="O164" s="24" t="n">
-        <v>0.3790055919999999</v>
+        <v>0.3795496704</v>
       </c>
     </row>
     <row r="165" ht="16" customHeight="1">
@@ -23775,31 +23775,31 @@
       </c>
       <c r="D165" s="18" t="inlineStr">
         <is>
-          <t>002414.SZ</t>
+          <t>WMMVY</t>
         </is>
       </c>
       <c r="E165" s="19" t="inlineStr">
         <is>
-          <t>Wuhan Guide Infrared Co., Ltd.</t>
+          <t>Wal-Mart de Mexico, S.A.B. de C.V.</t>
         </is>
       </c>
       <c r="F165" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H165" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I165" s="22" t="n">
-        <v>7758088313.668457</v>
+        <v>46150217728</v>
       </c>
       <c r="J165" s="25" t="inlineStr">
         <is>
@@ -23807,21 +23807,21 @@
         </is>
       </c>
       <c r="K165" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L165" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M165" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, OwnerOperator, StrongCoverage, LynchPEGY, LynchEV-GY, Li</t>
+          <t>NarrativeLag, LigerLaggingInflect, Forensic-OwnerEarnings, Forensic-Pa</t>
         </is>
       </c>
       <c r="N165" s="24" t="n">
-        <v>0.3523945846555655</v>
+        <v>0.3604217619997997</v>
       </c>
       <c r="O165" s="24" t="n">
-        <v>0.3787220432</v>
+        <v>0.3790055919999999</v>
       </c>
     </row>
     <row r="166" ht="16" customHeight="1">
@@ -23835,31 +23835,31 @@
       </c>
       <c r="D166" s="18" t="inlineStr">
         <is>
-          <t>SEOAY</t>
+          <t>002414.SZ</t>
         </is>
       </c>
       <c r="E166" s="19" t="inlineStr">
         <is>
-          <t>Stora Enso Oyj Class R</t>
+          <t>Wuhan Guide Infrared Co., Ltd.</t>
         </is>
       </c>
       <c r="F166" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G166" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H166" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I166" s="22" t="n">
-        <v>9384577024</v>
+        <v>7758088313.668457</v>
       </c>
       <c r="J166" s="25" t="inlineStr">
         <is>
@@ -23867,21 +23867,21 @@
         </is>
       </c>
       <c r="K166" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L166" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M166" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, KPIThreshold, Bal</t>
+          <t>KPIThreshold, OwnerOperator, StrongCoverage, LynchPEGY, LynchEV-GY, Li</t>
         </is>
       </c>
       <c r="N166" s="24" t="n">
-        <v>0.3679860516254969</v>
+        <v>0.3523945846555655</v>
       </c>
       <c r="O166" s="24" t="n">
-        <v>0.3783480288</v>
+        <v>0.3787220432</v>
       </c>
     </row>
     <row r="167" ht="16" customHeight="1">
@@ -23895,22 +23895,22 @@
       </c>
       <c r="D167" s="18" t="inlineStr">
         <is>
-          <t>MARUTI.NS</t>
+          <t>SEOAY</t>
         </is>
       </c>
       <c r="E167" s="19" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Limited</t>
+          <t>Stora Enso Oyj Class R</t>
         </is>
       </c>
       <c r="F167" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G167" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H167" s="16" t="inlineStr">
@@ -23919,7 +23919,7 @@
         </is>
       </c>
       <c r="I167" s="22" t="n">
-        <v>40742617410.64819</v>
+        <v>9384577024</v>
       </c>
       <c r="J167" s="25" t="inlineStr">
         <is>
@@ -23927,21 +23927,21 @@
         </is>
       </c>
       <c r="K167" s="22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L167" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M167" s="21" t="inlineStr">
         <is>
-          <t>OwnerOperator, LargeCapQuality, StrongCoverage, AnalystAwakening-52wHi</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, KPIThreshold, Bal</t>
         </is>
       </c>
       <c r="N167" s="24" t="n">
-        <v>0.3642046731109475</v>
+        <v>0.3679860516254969</v>
       </c>
       <c r="O167" s="24" t="n">
-        <v>0.3769516</v>
+        <v>0.3783480288</v>
       </c>
     </row>
     <row r="168" ht="16" customHeight="1">
@@ -23955,31 +23955,31 @@
       </c>
       <c r="D168" s="18" t="inlineStr">
         <is>
-          <t>SEK.AX</t>
+          <t>MARUTI.NS</t>
         </is>
       </c>
       <c r="E168" s="19" t="inlineStr">
         <is>
-          <t>SEEK Limited</t>
+          <t>Maruti Suzuki India Limited</t>
         </is>
       </c>
       <c r="F168" s="26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G168" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H168" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I168" s="22" t="n">
-        <v>3113330625.604523</v>
+        <v>40742617410.64819</v>
       </c>
       <c r="J168" s="25" t="inlineStr">
         <is>
@@ -23987,21 +23987,21 @@
         </is>
       </c>
       <c r="K168" s="22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L168" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M168" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, KPIThreshold, Lyn</t>
+          <t>OwnerOperator, LargeCapQuality, StrongCoverage, AnalystAwakening-52wHi</t>
         </is>
       </c>
       <c r="N168" s="24" t="n">
-        <v>0.3753634737784538</v>
+        <v>0.3642046731109475</v>
       </c>
       <c r="O168" s="24" t="n">
-        <v>0.3767446704</v>
+        <v>0.3769516</v>
       </c>
     </row>
     <row r="169" ht="16" customHeight="1">
@@ -24015,31 +24015,31 @@
       </c>
       <c r="D169" s="18" t="inlineStr">
         <is>
-          <t>ORSTED.CO</t>
+          <t>SEK.AX</t>
         </is>
       </c>
       <c r="E169" s="19" t="inlineStr">
         <is>
-          <t>Orsted A/S</t>
+          <t>SEEK Limited</t>
         </is>
       </c>
       <c r="F169" s="26" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G169" s="21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H169" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I169" s="22" t="n">
-        <v>27603703110.71558</v>
+        <v>3113330625.604523</v>
       </c>
       <c r="J169" s="25" t="inlineStr">
         <is>
@@ -24047,21 +24047,21 @@
         </is>
       </c>
       <c r="K169" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L169" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M169" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, RegimeCyclical, AnalystAwakening-52wHigh</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, KPIThreshold, Lyn</t>
         </is>
       </c>
       <c r="N169" s="24" t="n">
-        <v>0.3625412253242738</v>
+        <v>0.3753634737784538</v>
       </c>
       <c r="O169" s="24" t="n">
-        <v>0.3767309702</v>
+        <v>0.3767446704</v>
       </c>
     </row>
     <row r="170" ht="16" customHeight="1">
@@ -24075,22 +24075,22 @@
       </c>
       <c r="D170" s="18" t="inlineStr">
         <is>
-          <t>TITAN.NS</t>
+          <t>ORSTED.CO</t>
         </is>
       </c>
       <c r="E170" s="19" t="inlineStr">
         <is>
-          <t>Titan Company Limited</t>
+          <t>Orsted A/S</t>
         </is>
       </c>
       <c r="F170" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G170" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="H170" s="16" t="inlineStr">
@@ -24099,7 +24099,7 @@
         </is>
       </c>
       <c r="I170" s="22" t="n">
-        <v>46452820241.33789</v>
+        <v>27603703110.71558</v>
       </c>
       <c r="J170" s="25" t="inlineStr">
         <is>
@@ -24107,21 +24107,21 @@
         </is>
       </c>
       <c r="K170" s="22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L170" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M170" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, KPIThreshold, OwnerOperator, ONeil-CANSLIM, Wei</t>
+          <t>FixedCost+DemandShock, RegimeCyclical, AnalystAwakening-52wHigh</t>
         </is>
       </c>
       <c r="N170" s="24" t="n">
-        <v>0.36502231020031</v>
+        <v>0.3625412253242738</v>
       </c>
       <c r="O170" s="24" t="n">
-        <v>0.376643493</v>
+        <v>0.3767309702</v>
       </c>
     </row>
     <row r="171" ht="16" customHeight="1">
@@ -24135,31 +24135,31 @@
       </c>
       <c r="D171" s="18" t="inlineStr">
         <is>
-          <t>TOU.TO</t>
+          <t>TITAN.NS</t>
         </is>
       </c>
       <c r="E171" s="19" t="inlineStr">
         <is>
-          <t>Tourmaline Oil Corp.</t>
+          <t>Titan Company Limited</t>
         </is>
       </c>
       <c r="F171" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G171" s="21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H171" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I171" s="22" t="n">
-        <v>17087970663.48047</v>
+        <v>46452820241.33789</v>
       </c>
       <c r="J171" s="25" t="inlineStr">
         <is>
@@ -24167,21 +24167,21 @@
         </is>
       </c>
       <c r="K171" s="22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L171" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M171" s="21" t="inlineStr">
         <is>
-          <t>LynchEV-GY, Forensic-PayoutConfirmed, Forensic-SelfFunded, EVSalesDera</t>
+          <t>FixedCost+DemandShock, KPIThreshold, OwnerOperator, ONeil-CANSLIM, Wei</t>
         </is>
       </c>
       <c r="N171" s="24" t="n">
-        <v>0.3653035830134152</v>
+        <v>0.36502231020031</v>
       </c>
       <c r="O171" s="24" t="n">
-        <v>0.376445085</v>
+        <v>0.376643493</v>
       </c>
     </row>
     <row r="172" ht="16" customHeight="1">
@@ -24195,31 +24195,31 @@
       </c>
       <c r="D172" s="18" t="inlineStr">
         <is>
-          <t>XYIGY</t>
+          <t>TOU.TO</t>
         </is>
       </c>
       <c r="E172" s="19" t="inlineStr">
         <is>
-          <t>Xinyi Glass Holdings Limited</t>
+          <t>Tourmaline Oil Corp.</t>
         </is>
       </c>
       <c r="F172" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G172" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H172" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I172" s="22" t="n">
-        <v>5135813632</v>
+        <v>17087970663.48047</v>
       </c>
       <c r="J172" s="25" t="inlineStr">
         <is>
@@ -24227,21 +24227,21 @@
         </is>
       </c>
       <c r="K172" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L172" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M172" s="21" t="inlineStr">
         <is>
-          <t>LynchPEGY, Forensic-UnderstatedE, Forensic-PayoutConfirmed, Templeton-</t>
+          <t>LynchEV-GY, Forensic-PayoutConfirmed, Forensic-SelfFunded, EVSalesDera</t>
         </is>
       </c>
       <c r="N172" s="24" t="n">
-        <v>0.3702095700124536</v>
+        <v>0.3653035830134152</v>
       </c>
       <c r="O172" s="24" t="n">
-        <v>0.374837625</v>
+        <v>0.376445085</v>
       </c>
     </row>
     <row r="173" ht="16" customHeight="1">
@@ -24255,31 +24255,31 @@
       </c>
       <c r="D173" s="18" t="inlineStr">
         <is>
-          <t>002568.SZ</t>
+          <t>XYIGY</t>
         </is>
       </c>
       <c r="E173" s="19" t="inlineStr">
         <is>
-          <t>Shanghai Bairun Investment Holding Group Co., Ltd.</t>
+          <t>Xinyi Glass Holdings Limited</t>
         </is>
       </c>
       <c r="F173" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G173" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H173" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I173" s="22" t="n">
-        <v>2640432384.379761</v>
+        <v>5135813632</v>
       </c>
       <c r="J173" s="25" t="inlineStr">
         <is>
@@ -24290,18 +24290,18 @@
         <v>4</v>
       </c>
       <c r="L173" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M173" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, OwnerOperator, Bottleneck-Chokepoint, Flyover-QuietQuali</t>
+          <t>LynchPEGY, Forensic-UnderstatedE, Forensic-PayoutConfirmed, Templeton-</t>
         </is>
       </c>
       <c r="N173" s="24" t="n">
-        <v>0.3605033975265482</v>
+        <v>0.3702095700124536</v>
       </c>
       <c r="O173" s="24" t="n">
-        <v>0.3747931242</v>
+        <v>0.374837625</v>
       </c>
     </row>
     <row r="174" ht="16" customHeight="1">
@@ -24315,22 +24315,22 @@
       </c>
       <c r="D174" s="18" t="inlineStr">
         <is>
-          <t>SKLTY</t>
+          <t>002568.SZ</t>
         </is>
       </c>
       <c r="E174" s="19" t="inlineStr">
         <is>
-          <t>SEEK Limited</t>
+          <t>Shanghai Bairun Investment Holding Group Co., Ltd.</t>
         </is>
       </c>
       <c r="F174" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G174" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H174" s="16" t="inlineStr">
@@ -24339,7 +24339,7 @@
         </is>
       </c>
       <c r="I174" s="22" t="n">
-        <v>3184144896</v>
+        <v>2640432384.379761</v>
       </c>
       <c r="J174" s="25" t="inlineStr">
         <is>
@@ -24347,21 +24347,21 @@
         </is>
       </c>
       <c r="K174" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L174" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M174" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, KPIThreshold, Lyn</t>
+          <t>KPIThreshold, OwnerOperator, Bottleneck-Chokepoint, Flyover-QuietQuali</t>
         </is>
       </c>
       <c r="N174" s="24" t="n">
-        <v>0.3733520627675464</v>
+        <v>0.3605033975265482</v>
       </c>
       <c r="O174" s="24" t="n">
-        <v>0.3747261584</v>
+        <v>0.3747931242</v>
       </c>
     </row>
     <row r="175" ht="16" customHeight="1">
@@ -24375,22 +24375,22 @@
       </c>
       <c r="D175" s="18" t="inlineStr">
         <is>
-          <t>IRE.MI</t>
+          <t>SKLTY</t>
         </is>
       </c>
       <c r="E175" s="19" t="inlineStr">
         <is>
-          <t>Iren SpA</t>
+          <t>SEEK Limited</t>
         </is>
       </c>
       <c r="F175" s="26" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G175" s="21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H175" s="16" t="inlineStr">
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="I175" s="22" t="n">
-        <v>3639279989.109741</v>
+        <v>3184144896</v>
       </c>
       <c r="J175" s="25" t="inlineStr">
         <is>
@@ -24407,21 +24407,21 @@
         </is>
       </c>
       <c r="K175" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L175" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M175" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, Weinstein-Stage2, LynchPEGY</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, KPIThreshold, Lyn</t>
         </is>
       </c>
       <c r="N175" s="24" t="n">
-        <v>0.3627257874731835</v>
+        <v>0.3733520627675464</v>
       </c>
       <c r="O175" s="24" t="n">
-        <v>0.3732663602</v>
+        <v>0.3747261584</v>
       </c>
     </row>
     <row r="176" ht="16" customHeight="1">
@@ -24435,31 +24435,31 @@
       </c>
       <c r="D176" s="18" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>IRE.MI</t>
         </is>
       </c>
       <c r="E176" s="19" t="inlineStr">
         <is>
-          <t>Roku, Inc.</t>
+          <t>Iren SpA</t>
         </is>
       </c>
       <c r="F176" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G176" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="H176" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I176" s="22" t="n">
-        <v>23008751616</v>
+        <v>3639279989.109741</v>
       </c>
       <c r="J176" s="25" t="inlineStr">
         <is>
@@ -24467,21 +24467,21 @@
         </is>
       </c>
       <c r="K176" s="22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L176" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M176" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, ConcentratedSegments, FastestSegment, Ly</t>
+          <t>FixedCost+DemandShock, Weinstein-Stage2, LynchPEGY</t>
         </is>
       </c>
       <c r="N176" s="24" t="n">
-        <v>0.3586058250989377</v>
+        <v>0.3627257874731835</v>
       </c>
       <c r="O176" s="24" t="n">
-        <v>0.372947284</v>
+        <v>0.3732663602</v>
       </c>
     </row>
     <row r="177" ht="16" customHeight="1">
@@ -24495,22 +24495,22 @@
       </c>
       <c r="D177" s="18" t="inlineStr">
         <is>
-          <t>2882.TW</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="E177" s="19" t="inlineStr">
         <is>
-          <t>Cathay Financial Holding Co., Ltd.</t>
+          <t>Roku, Inc.</t>
         </is>
       </c>
       <c r="F177" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G177" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H177" s="16" t="inlineStr">
@@ -24519,7 +24519,7 @@
         </is>
       </c>
       <c r="I177" s="22" t="n">
-        <v>51344554454.28955</v>
+        <v>23008751616</v>
       </c>
       <c r="J177" s="25" t="inlineStr">
         <is>
@@ -24527,21 +24527,21 @@
         </is>
       </c>
       <c r="K177" s="22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L177" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M177" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, Kullamagi-Breakout, AsleepAtWheel-Beats, ReratingCon</t>
+          <t>KPIThreshold, StrongCoverage, ConcentratedSegments, FastestSegment, Ly</t>
         </is>
       </c>
       <c r="N177" s="24" t="n">
-        <v>0.4240990477030801</v>
+        <v>0.3586058250989377</v>
       </c>
       <c r="O177" s="24" t="n">
-        <v>0.370475248</v>
+        <v>0.372947284</v>
       </c>
     </row>
     <row r="178" ht="16" customHeight="1">
@@ -24555,22 +24555,22 @@
       </c>
       <c r="D178" s="18" t="inlineStr">
         <is>
-          <t>JMHLY</t>
+          <t>2882.TW</t>
         </is>
       </c>
       <c r="E178" s="19" t="inlineStr">
         <is>
-          <t>Jardine Matheson Holdings Limited</t>
+          <t>Cathay Financial Holding Co., Ltd.</t>
         </is>
       </c>
       <c r="F178" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G178" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H178" s="16" t="inlineStr">
@@ -24579,7 +24579,7 @@
         </is>
       </c>
       <c r="I178" s="22" t="n">
-        <v>17159691264</v>
+        <v>51344554454.28955</v>
       </c>
       <c r="J178" s="25" t="inlineStr">
         <is>
@@ -24587,21 +24587,21 @@
         </is>
       </c>
       <c r="K178" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L178" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M178" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchEV-GY, Forensic-OverDepreciated, Forensic-OwnerEarn</t>
+          <t>Weinstein-Stage2, Kullamagi-Breakout, AsleepAtWheel-Beats, ReratingCon</t>
         </is>
       </c>
       <c r="N178" s="24" t="n">
-        <v>0.3598250205577918</v>
+        <v>0.4240990477030801</v>
       </c>
       <c r="O178" s="24" t="n">
-        <v>0.3702820862</v>
+        <v>0.370475248</v>
       </c>
     </row>
     <row r="179" ht="16" customHeight="1">
@@ -24615,31 +24615,31 @@
       </c>
       <c r="D179" s="18" t="inlineStr">
         <is>
-          <t>4002.SR</t>
+          <t>JMHLY</t>
         </is>
       </c>
       <c r="E179" s="19" t="inlineStr">
         <is>
-          <t>Mouwasat Medical Services Company</t>
+          <t>Jardine Matheson Holdings Limited</t>
         </is>
       </c>
       <c r="F179" s="26" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G179" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H179" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I179" s="22" t="n">
-        <v>3562060668.808075</v>
+        <v>17159691264</v>
       </c>
       <c r="J179" s="25" t="inlineStr">
         <is>
@@ -24647,21 +24647,21 @@
         </is>
       </c>
       <c r="K179" s="22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L179" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M179" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, MidCapGARP, CapitalRet</t>
+          <t>KPIThreshold, LynchEV-GY, OakDeleveraging, Forensic-OverDepreciated, F</t>
         </is>
       </c>
       <c r="N179" s="24" t="n">
-        <v>0.3592079714650162</v>
+        <v>0.3598250205577918</v>
       </c>
       <c r="O179" s="24" t="n">
-        <v>0.3696463558</v>
+        <v>0.3702820862</v>
       </c>
     </row>
     <row r="180" ht="16" customHeight="1">
@@ -24675,17 +24675,17 @@
       </c>
       <c r="D180" s="18" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>4002.SR</t>
         </is>
       </c>
       <c r="E180" s="19" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Mouwasat Medical Services Company</t>
         </is>
       </c>
       <c r="F180" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G180" s="21" t="inlineStr">
@@ -24695,11 +24695,11 @@
       </c>
       <c r="H180" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I180" s="22" t="n">
-        <v>129998356480</v>
+        <v>3562060668.808075</v>
       </c>
       <c r="J180" s="25" t="inlineStr">
         <is>
@@ -24707,21 +24707,21 @@
         </is>
       </c>
       <c r="K180" s="22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L180" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M180" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LargeCapQuality, Weinstein-Stage2, LowSBCQuality, LynchP</t>
+          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, MidCapGARP, CapitalRet</t>
         </is>
       </c>
       <c r="N180" s="24" t="n">
-        <v>0.3599840668402113</v>
+        <v>0.3592079714650162</v>
       </c>
       <c r="O180" s="24" t="n">
-        <v>0.368704175</v>
+        <v>0.3696463558</v>
       </c>
     </row>
     <row r="181" ht="16" customHeight="1">
@@ -24735,22 +24735,22 @@
       </c>
       <c r="D181" s="18" t="inlineStr">
         <is>
-          <t>000157.SZ</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="E181" s="19" t="inlineStr">
         <is>
-          <t>Zoomlion Heavy Industry Science and Technology Co., Ltd.</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="F181" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G181" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H181" s="16" t="inlineStr">
@@ -24759,7 +24759,7 @@
         </is>
       </c>
       <c r="I181" s="22" t="n">
-        <v>8334704957.35083</v>
+        <v>129998356480</v>
       </c>
       <c r="J181" s="25" t="inlineStr">
         <is>
@@ -24767,21 +24767,21 @@
         </is>
       </c>
       <c r="K181" s="22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L181" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M181" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, KPIThreshold, CapitalReturner, An</t>
+          <t>KPIThreshold, LargeCapQuality, Weinstein-Stage2, LowSBCQuality, LynchP</t>
         </is>
       </c>
       <c r="N181" s="24" t="n">
-        <v>0.3634270199786372</v>
+        <v>0.3599840668402113</v>
       </c>
       <c r="O181" s="24" t="n">
-        <v>0.3677732496</v>
+        <v>0.368704175</v>
       </c>
     </row>
     <row r="182" ht="16" customHeight="1">
@@ -24795,31 +24795,31 @@
       </c>
       <c r="D182" s="18" t="inlineStr">
         <is>
-          <t>NDGPF</t>
+          <t>000157.SZ</t>
         </is>
       </c>
       <c r="E182" s="19" t="inlineStr">
         <is>
-          <t>Nine Dragons Paper (Holdings) Limited</t>
+          <t>Zoomlion Heavy Industry Science and Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="F182" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G182" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H182" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I182" s="22" t="n">
-        <v>3941465344</v>
+        <v>8334704957.35083</v>
       </c>
       <c r="J182" s="25" t="inlineStr">
         <is>
@@ -24834,14 +24834,14 @@
       </c>
       <c r="M182" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchPEGY, LynchEV-GY, NegativeEV-Value, LeveredInflecti</t>
+          <t>NarrativeLag, FixedCost+DemandShock, KPIThreshold, CapitalReturner, An</t>
         </is>
       </c>
       <c r="N182" s="24" t="n">
-        <v>0.3644506367431516</v>
+        <v>0.3634270199786372</v>
       </c>
       <c r="O182" s="24" t="n">
-        <v>0.3677603272</v>
+        <v>0.3677732496</v>
       </c>
     </row>
     <row r="183" ht="16" customHeight="1">
@@ -24855,22 +24855,22 @@
       </c>
       <c r="D183" s="18" t="inlineStr">
         <is>
-          <t>ARIS</t>
+          <t>NDGPF</t>
         </is>
       </c>
       <c r="E183" s="19" t="inlineStr">
         <is>
-          <t>Aris Water Solutions Inc. Class A Common Stock</t>
+          <t>Nine Dragons Paper (Holdings) Limited</t>
         </is>
       </c>
       <c r="F183" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G183" s="21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H183" s="16" t="inlineStr">
@@ -24879,7 +24879,7 @@
         </is>
       </c>
       <c r="I183" s="22" t="n">
-        <v>4033655808</v>
+        <v>3941465344</v>
       </c>
       <c r="J183" s="25" t="inlineStr">
         <is>
@@ -24887,21 +24887,21 @@
         </is>
       </c>
       <c r="K183" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L183" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M183" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, ONeil-CANSLIM, AsleepAtWheel-Beats, AsleepUnrer</t>
+          <t>KPIThreshold, LynchPEGY, LynchEV-GY, NegativeEV-Value, LeveredInflecti</t>
         </is>
       </c>
       <c r="N183" s="24" t="n">
-        <v>0.4564184110948191</v>
+        <v>0.3644506367431516</v>
       </c>
       <c r="O183" s="24" t="n">
-        <v>0.3677268</v>
+        <v>0.3677603272</v>
       </c>
     </row>
     <row r="184" ht="16" customHeight="1">
@@ -24915,31 +24915,31 @@
       </c>
       <c r="D184" s="18" t="inlineStr">
         <is>
-          <t>REPYF</t>
+          <t>ARIS</t>
         </is>
       </c>
       <c r="E184" s="19" t="inlineStr">
         <is>
-          <t>Repsol S.A.</t>
+          <t>Aris Water Solutions Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="F184" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G184" s="21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="H184" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I184" s="22" t="n">
-        <v>35861041152</v>
+        <v>4033655808</v>
       </c>
       <c r="J184" s="25" t="inlineStr">
         <is>
@@ -24947,21 +24947,21 @@
         </is>
       </c>
       <c r="K184" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L184" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="L184" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="M184" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ONeil-CANSLIM, Weinstein-Stage2, LynchPEGY, LynchEV-GY</t>
+          <t>FixedCost+DemandShock, ONeil-CANSLIM, AsleepAtWheel-Beats, AsleepUnrer</t>
         </is>
       </c>
       <c r="N184" s="24" t="n">
-        <v>0.3982605156632564</v>
+        <v>0.4564184110948191</v>
       </c>
       <c r="O184" s="24" t="n">
-        <v>0.3655311932999999</v>
+        <v>0.3677268</v>
       </c>
     </row>
     <row r="185" ht="16" customHeight="1">
@@ -24975,31 +24975,31 @@
       </c>
       <c r="D185" s="18" t="inlineStr">
         <is>
-          <t>6993.HK</t>
+          <t>REPYF</t>
         </is>
       </c>
       <c r="E185" s="19" t="inlineStr">
         <is>
-          <t>Blue Moon Group Holdings Limited</t>
+          <t>Repsol S.A.</t>
         </is>
       </c>
       <c r="F185" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G185" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H185" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I185" s="22" t="n">
-        <v>2756393266.747559</v>
+        <v>35861041152</v>
       </c>
       <c r="J185" s="25" t="inlineStr">
         <is>
@@ -25007,21 +25007,21 @@
         </is>
       </c>
       <c r="K185" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L185" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M185" s="21" t="inlineStr">
         <is>
-          <t>BalanceSheetReturn, StrongCoverage, LynchEV-GY</t>
+          <t>KPIThreshold, ONeil-CANSLIM, Weinstein-Stage2, LynchPEGY, LynchEV-GY</t>
         </is>
       </c>
       <c r="N185" s="24" t="n">
-        <v>0.3574925837532002</v>
+        <v>0.3982605156632564</v>
       </c>
       <c r="O185" s="24" t="n">
-        <v>0.364889873</v>
+        <v>0.3655311932999999</v>
       </c>
     </row>
     <row r="186" ht="16" customHeight="1">
@@ -25035,22 +25035,22 @@
       </c>
       <c r="D186" s="18" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>6993.HK</t>
         </is>
       </c>
       <c r="E186" s="19" t="inlineStr">
         <is>
-          <t>L Brands, Inc.</t>
+          <t>Blue Moon Group Holdings Limited</t>
         </is>
       </c>
       <c r="F186" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G186" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H186" s="16" t="inlineStr">
@@ -25059,7 +25059,7 @@
         </is>
       </c>
       <c r="I186" s="22" t="n">
-        <v>6694867456</v>
+        <v>2756393266.747559</v>
       </c>
       <c r="J186" s="25" t="inlineStr">
         <is>
@@ -25067,21 +25067,21 @@
         </is>
       </c>
       <c r="K186" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L186" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M186" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, KPIThreshold, ROICInflect, Weinstein-Stage2, Ta</t>
+          <t>BalanceSheetReturn, StrongCoverage, LynchEV-GY</t>
         </is>
       </c>
       <c r="N186" s="24" t="n">
-        <v>0.3581243934303308</v>
+        <v>0.3574925837532002</v>
       </c>
       <c r="O186" s="24" t="n">
-        <v>0.3631812</v>
+        <v>0.364889873</v>
       </c>
     </row>
     <row r="187" ht="16" customHeight="1">
@@ -25095,12 +25095,12 @@
       </c>
       <c r="D187" s="18" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E187" s="19" t="inlineStr">
         <is>
-          <t>Reddit Inc. Class A Common Stock</t>
+          <t>L Brands, Inc.</t>
         </is>
       </c>
       <c r="F187" s="26" t="inlineStr">
@@ -25110,38 +25110,38 @@
       </c>
       <c r="G187" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H187" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I187" s="22" t="n">
-        <v>30354399232</v>
-      </c>
-      <c r="J187" s="26" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>6694867456</v>
+      </c>
+      <c r="J187" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K187" s="22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L187" s="22" t="n">
         <v>5</v>
       </c>
       <c r="M187" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ROICInflect, LargeCapQuality, StrongCoverage, LynchPEGY,</t>
+          <t>FixedCost+DemandShock, KPIThreshold, ROICInflect, Weinstein-Stage2, Ta</t>
         </is>
       </c>
       <c r="N187" s="24" t="n">
-        <v>0.3770777242280583</v>
+        <v>0.3581243934303308</v>
       </c>
       <c r="O187" s="24" t="n">
-        <v>0.3627174806</v>
+        <v>0.3631812</v>
       </c>
     </row>
     <row r="188" ht="16" customHeight="1">
@@ -25155,53 +25155,53 @@
       </c>
       <c r="D188" s="18" t="inlineStr">
         <is>
-          <t>AMBUJACEM.NS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="E188" s="19" t="inlineStr">
         <is>
-          <t>Ambuja Cements Limited</t>
+          <t>Reddit Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="F188" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G188" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H188" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I188" s="22" t="n">
-        <v>10175493318.0661</v>
-      </c>
-      <c r="J188" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>30354399232</v>
+      </c>
+      <c r="J188" s="26" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K188" s="22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L188" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M188" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, StrongCoverage, E</t>
+          <t>KPIThreshold, ROICInflect, LargeCapQuality, StrongCoverage, LynchPEGY,</t>
         </is>
       </c>
       <c r="N188" s="24" t="n">
-        <v>0.3545121970432137</v>
+        <v>0.3770777242280583</v>
       </c>
       <c r="O188" s="24" t="n">
-        <v>0.3625809204</v>
+        <v>0.3627174806</v>
       </c>
     </row>
     <row r="189" ht="16" customHeight="1">
@@ -25215,17 +25215,17 @@
       </c>
       <c r="D189" s="18" t="inlineStr">
         <is>
-          <t>STERV.HE</t>
+          <t>AMBUJACEM.NS</t>
         </is>
       </c>
       <c r="E189" s="19" t="inlineStr">
         <is>
-          <t>Stora Enso Oyj Class R</t>
+          <t>Ambuja Cements Limited</t>
         </is>
       </c>
       <c r="F189" s="26" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G189" s="21" t="inlineStr">
@@ -25235,11 +25235,11 @@
       </c>
       <c r="H189" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I189" s="22" t="n">
-        <v>9213913542.196289</v>
+        <v>10175493318.0661</v>
       </c>
       <c r="J189" s="25" t="inlineStr">
         <is>
@@ -25247,21 +25247,21 @@
         </is>
       </c>
       <c r="K189" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L189" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M189" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, KPIThreshold, BalanceSheetReturn, LynchEV-GY, A</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, StrongCoverage, E</t>
         </is>
       </c>
       <c r="N189" s="24" t="n">
-        <v>0.3510541838316492</v>
+        <v>0.3545121970432137</v>
       </c>
       <c r="O189" s="24" t="n">
-        <v>0.3624566928</v>
+        <v>0.3625809204</v>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1">
@@ -25275,22 +25275,22 @@
       </c>
       <c r="D190" s="18" t="inlineStr">
         <is>
-          <t>ZLIOY</t>
+          <t>STERV.HE</t>
         </is>
       </c>
       <c r="E190" s="19" t="inlineStr">
         <is>
-          <t>Zoomlion Heavy Industry Science and Technology Co., Ltd.</t>
+          <t>Stora Enso Oyj Class R</t>
         </is>
       </c>
       <c r="F190" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G190" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H190" s="16" t="inlineStr">
@@ -25299,7 +25299,7 @@
         </is>
       </c>
       <c r="I190" s="22" t="n">
-        <v>9167708160</v>
+        <v>9213913542.196289</v>
       </c>
       <c r="J190" s="25" t="inlineStr">
         <is>
@@ -25307,21 +25307,21 @@
         </is>
       </c>
       <c r="K190" s="22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L190" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M190" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, KPIThreshold, CapitalReturner, Fo</t>
+          <t>FixedCost+DemandShock, KPIThreshold, BalanceSheetReturn, LynchEV-GY, A</t>
         </is>
       </c>
       <c r="N190" s="24" t="n">
-        <v>0.3581123960570111</v>
+        <v>0.3510541838316492</v>
       </c>
       <c r="O190" s="24" t="n">
-        <v>0.3623952444</v>
+        <v>0.3624566928</v>
       </c>
     </row>
     <row r="191" ht="16" customHeight="1">
@@ -25335,22 +25335,22 @@
       </c>
       <c r="D191" s="18" t="inlineStr">
         <is>
-          <t>NESTE.HE</t>
+          <t>ZLIOY</t>
         </is>
       </c>
       <c r="E191" s="19" t="inlineStr">
         <is>
-          <t>Neste Oyj</t>
+          <t>Zoomlion Heavy Industry Science and Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="F191" s="26" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G191" s="21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H191" s="16" t="inlineStr">
@@ -25359,7 +25359,7 @@
         </is>
       </c>
       <c r="I191" s="22" t="n">
-        <v>29158572284.50196</v>
+        <v>9167708160</v>
       </c>
       <c r="J191" s="25" t="inlineStr">
         <is>
@@ -25367,21 +25367,21 @@
         </is>
       </c>
       <c r="K191" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="L191" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="L191" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="M191" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Weinstein-Stage2, LynchEV-GY, AsleepAtWheel-Beats</t>
+          <t>NarrativeLag, FixedCost+DemandShock, KPIThreshold, CapitalReturner, Fo</t>
         </is>
       </c>
       <c r="N191" s="24" t="n">
-        <v>0.4186590884267794</v>
+        <v>0.3581123960570111</v>
       </c>
       <c r="O191" s="24" t="n">
-        <v>0.3600613366</v>
+        <v>0.3623952444</v>
       </c>
     </row>
     <row r="192" ht="16" customHeight="1">
@@ -25395,7 +25395,7 @@
       </c>
       <c r="D192" s="18" t="inlineStr">
         <is>
-          <t>NTOIY</t>
+          <t>NESTE.HE</t>
         </is>
       </c>
       <c r="E192" s="19" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="F192" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G192" s="21" t="inlineStr">
@@ -25419,7 +25419,7 @@
         </is>
       </c>
       <c r="I192" s="22" t="n">
-        <v>29379131392</v>
+        <v>29158572284.50196</v>
       </c>
       <c r="J192" s="25" t="inlineStr">
         <is>
@@ -25430,18 +25430,18 @@
         <v>4</v>
       </c>
       <c r="L192" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M192" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ONeil-CANSLIM, Weinstein-Stage2, LynchEV-GY</t>
+          <t>KPIThreshold, Weinstein-Stage2, LynchEV-GY, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="N192" s="24" t="n">
-        <v>0.4212481477819056</v>
+        <v>0.4186590884267794</v>
       </c>
       <c r="O192" s="24" t="n">
-        <v>0.359977114</v>
+        <v>0.3600613366</v>
       </c>
     </row>
     <row r="193" ht="16" customHeight="1">
@@ -25455,22 +25455,22 @@
       </c>
       <c r="D193" s="18" t="inlineStr">
         <is>
-          <t>P9O.F</t>
+          <t>NTOIY</t>
         </is>
       </c>
       <c r="E193" s="19" t="inlineStr">
         <is>
-          <t>Powszechna Kasa Oszczednosci Bank Polski Spolka Akcyjna</t>
+          <t>Neste Oyj</t>
         </is>
       </c>
       <c r="F193" s="26" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G193" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H193" s="16" t="inlineStr">
@@ -25479,7 +25479,7 @@
         </is>
       </c>
       <c r="I193" s="22" t="n">
-        <v>39854029304.37305</v>
+        <v>29379131392</v>
       </c>
       <c r="J193" s="25" t="inlineStr">
         <is>
@@ -25487,21 +25487,21 @@
         </is>
       </c>
       <c r="K193" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L193" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M193" s="21" t="inlineStr">
         <is>
-          <t>FinancialsValue, Weinstein-Stage2, Kullamagi-Breakout</t>
+          <t>KPIThreshold, ONeil-CANSLIM, Weinstein-Stage2, LynchEV-GY</t>
         </is>
       </c>
       <c r="N193" s="24" t="n">
-        <v>0.4394818351474017</v>
+        <v>0.4212481477819056</v>
       </c>
       <c r="O193" s="24" t="n">
-        <v>0.3596461439999999</v>
+        <v>0.359977114</v>
       </c>
     </row>
     <row r="194" ht="16" customHeight="1">
@@ -25515,53 +25515,53 @@
       </c>
       <c r="D194" s="18" t="inlineStr">
         <is>
-          <t>FALABELLA.SN</t>
+          <t>P9O.F</t>
         </is>
       </c>
       <c r="E194" s="19" t="inlineStr">
         <is>
-          <t>Falabella S.A.</t>
+          <t>Powszechna Kasa Oszczednosci Bank Polski Spolka Akcyjna</t>
         </is>
       </c>
       <c r="F194" s="26" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G194" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H194" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I194" s="22" t="n">
-        <v>17261694936.60217</v>
-      </c>
-      <c r="J194" s="26" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>39854029304.37305</v>
+      </c>
+      <c r="J194" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K194" s="22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L194" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M194" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, MidCapGARP, Wei</t>
+          <t>FinancialsValue, Weinstein-Stage2, Kullamagi-Breakout</t>
         </is>
       </c>
       <c r="N194" s="24" t="n">
-        <v>0.3961187568078758</v>
+        <v>0.4394818351474017</v>
       </c>
       <c r="O194" s="24" t="n">
-        <v>0.3589705226</v>
+        <v>0.3596461439999999</v>
       </c>
     </row>
     <row r="195" ht="16" customHeight="1">
@@ -25575,53 +25575,53 @@
       </c>
       <c r="D195" s="18" t="inlineStr">
         <is>
-          <t>ZLIOF</t>
+          <t>FALABELLA.SN</t>
         </is>
       </c>
       <c r="E195" s="19" t="inlineStr">
         <is>
-          <t>Zoomlion Heavy Industry Science and Technology Co., Ltd.</t>
+          <t>Falabella S.A.</t>
         </is>
       </c>
       <c r="F195" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="G195" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H195" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I195" s="22" t="n">
-        <v>7827392512</v>
-      </c>
-      <c r="J195" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>17261694936.60217</v>
+      </c>
+      <c r="J195" s="26" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K195" s="22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L195" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M195" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, KPIThreshold, CapitalReturner, Fo</t>
+          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, MidCapGARP, Wei</t>
         </is>
       </c>
       <c r="N195" s="24" t="n">
-        <v>0.3546535533630403</v>
+        <v>0.3961187568078758</v>
       </c>
       <c r="O195" s="24" t="n">
-        <v>0.3588949872000001</v>
+        <v>0.3589705226</v>
       </c>
     </row>
     <row r="196" ht="16" customHeight="1">
@@ -25635,31 +25635,31 @@
       </c>
       <c r="D196" s="18" t="inlineStr">
         <is>
-          <t>4506.T</t>
+          <t>ZLIOF</t>
         </is>
       </c>
       <c r="E196" s="19" t="inlineStr">
         <is>
-          <t>Sumitomo Dainippon Pharma Co., Ltd.</t>
+          <t>Zoomlion Heavy Industry Science and Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="F196" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G196" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H196" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I196" s="22" t="n">
-        <v>4270613302.632294</v>
+        <v>7827392512</v>
       </c>
       <c r="J196" s="25" t="inlineStr">
         <is>
@@ -25667,21 +25667,21 @@
         </is>
       </c>
       <c r="K196" s="22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L196" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M196" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, KPIThreshold, MidCapGARP, LynchPEGY, LynchEV-GY, XR-Fore</t>
+          <t>NarrativeLag, FixedCost+DemandShock, KPIThreshold, CapitalReturner, Fo</t>
         </is>
       </c>
       <c r="N196" s="24" t="n">
-        <v>0.3571166372492592</v>
+        <v>0.3546535533630403</v>
       </c>
       <c r="O196" s="24" t="n">
-        <v>0.357723765</v>
+        <v>0.3588949872000001</v>
       </c>
     </row>
     <row r="197" ht="16" customHeight="1">
@@ -25695,31 +25695,31 @@
       </c>
       <c r="D197" s="18" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>4506.T</t>
         </is>
       </c>
       <c r="E197" s="19" t="inlineStr">
         <is>
-          <t>Twilio Inc.</t>
+          <t>Sumitomo Dainippon Pharma Co., Ltd.</t>
         </is>
       </c>
       <c r="F197" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H197" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I197" s="22" t="n">
-        <v>34915328000</v>
+        <v>4270613302.632294</v>
       </c>
       <c r="J197" s="25" t="inlineStr">
         <is>
@@ -25727,21 +25727,21 @@
         </is>
       </c>
       <c r="K197" s="22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L197" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M197" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Kullamagi-Breakout, TaxEfficient, StrongCoverage, Concen</t>
+          <t>NarrativeLag, KPIThreshold, MidCapGARP, LynchPEGY, LynchEV-GY, XR-Fore</t>
         </is>
       </c>
       <c r="N197" s="24" t="n">
-        <v>0.3663178461098828</v>
+        <v>0.3571166372492592</v>
       </c>
       <c r="O197" s="24" t="n">
-        <v>0.353802148</v>
+        <v>0.357723765</v>
       </c>
     </row>
     <row r="198" ht="16" customHeight="1">
@@ -25755,22 +25755,22 @@
       </c>
       <c r="D198" s="18" t="inlineStr">
         <is>
-          <t>CHBJF</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="E198" s="19" t="inlineStr">
         <is>
-          <t>China CITIC Bank Corporation Ltd Class H</t>
+          <t>Twilio Inc.</t>
         </is>
       </c>
       <c r="F198" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G198" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H198" s="16" t="inlineStr">
@@ -25779,7 +25779,7 @@
         </is>
       </c>
       <c r="I198" s="22" t="n">
-        <v>58427420672</v>
+        <v>34915328000</v>
       </c>
       <c r="J198" s="25" t="inlineStr">
         <is>
@@ -25787,21 +25787,21 @@
         </is>
       </c>
       <c r="K198" s="22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L198" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M198" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, Kullamagi-Breakout, LynchPEGY</t>
+          <t>KPIThreshold, Kullamagi-Breakout, TaxEfficient, StrongCoverage, Concen</t>
         </is>
       </c>
       <c r="N198" s="24" t="n">
-        <v>0.4079686276076965</v>
+        <v>0.3663178461098828</v>
       </c>
       <c r="O198" s="24" t="n">
-        <v>0.35330467</v>
+        <v>0.353802148</v>
       </c>
     </row>
     <row r="199" ht="16" customHeight="1">
@@ -25815,31 +25815,31 @@
       </c>
       <c r="D199" s="18" t="inlineStr">
         <is>
-          <t>JBT.F</t>
+          <t>CHBJF</t>
         </is>
       </c>
       <c r="E199" s="19" t="inlineStr">
         <is>
-          <t>John Bean Technologies Corporation</t>
+          <t>China CITIC Bank Corporation Ltd Class H</t>
         </is>
       </c>
       <c r="F199" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G199" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H199" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I199" s="22" t="n">
-        <v>5657003461.142578</v>
+        <v>58427420672</v>
       </c>
       <c r="J199" s="25" t="inlineStr">
         <is>
@@ -25847,21 +25847,21 @@
         </is>
       </c>
       <c r="K199" s="22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L199" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M199" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, BAB-Becoming, Lyn</t>
+          <t>Weinstein-Stage2, Kullamagi-Breakout, LynchPEGY</t>
         </is>
       </c>
       <c r="N199" s="24" t="n">
-        <v>0.3558277068233402</v>
+        <v>0.4079686276076965</v>
       </c>
       <c r="O199" s="24" t="n">
-        <v>0.34714558</v>
+        <v>0.35330467</v>
       </c>
     </row>
     <row r="200" ht="16" customHeight="1">
@@ -25875,12 +25875,12 @@
       </c>
       <c r="D200" s="18" t="inlineStr">
         <is>
-          <t>TYEKF</t>
+          <t>JBT.F</t>
         </is>
       </c>
       <c r="E200" s="19" t="inlineStr">
         <is>
-          <t>thyssenkrupp AG</t>
+          <t>John Bean Technologies Corporation</t>
         </is>
       </c>
       <c r="F200" s="26" t="inlineStr">
@@ -25899,7 +25899,7 @@
         </is>
       </c>
       <c r="I200" s="22" t="n">
-        <v>10922235904</v>
+        <v>5657003461.142578</v>
       </c>
       <c r="J200" s="25" t="inlineStr">
         <is>
@@ -25907,21 +25907,21 @@
         </is>
       </c>
       <c r="K200" s="22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L200" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M200" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Weinstein-Stage2, StrongCoverage, LynchEV-GY, HiddenAsse</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, BAB-Becoming, Lyn</t>
         </is>
       </c>
       <c r="N200" s="24" t="n">
-        <v>0.3761381242120362</v>
+        <v>0.3558277068233402</v>
       </c>
       <c r="O200" s="24" t="n">
-        <v>0.3470271644</v>
+        <v>0.34714558</v>
       </c>
     </row>
     <row r="201" ht="16" customHeight="1">
@@ -25935,12 +25935,12 @@
       </c>
       <c r="D201" s="18" t="inlineStr">
         <is>
-          <t>REPYY</t>
+          <t>TYEKF</t>
         </is>
       </c>
       <c r="E201" s="19" t="inlineStr">
         <is>
-          <t>Repsol S.A.</t>
+          <t>thyssenkrupp AG</t>
         </is>
       </c>
       <c r="F201" s="26" t="inlineStr">
@@ -25950,16 +25950,16 @@
       </c>
       <c r="G201" s="21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H201" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I201" s="22" t="n">
-        <v>36010684416</v>
+        <v>10922235904</v>
       </c>
       <c r="J201" s="25" t="inlineStr">
         <is>
@@ -25967,21 +25967,21 @@
         </is>
       </c>
       <c r="K201" s="22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L201" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M201" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ONeil-CANSLIM, Weinstein-Stage2, LynchPEGY, LynchEV-GY</t>
+          <t>KPIThreshold, Weinstein-Stage2, StrongCoverage, LynchEV-GY, HiddenAsse</t>
         </is>
       </c>
       <c r="N201" s="24" t="n">
-        <v>0.3758541077045203</v>
+        <v>0.3761381242120362</v>
       </c>
       <c r="O201" s="24" t="n">
-        <v>0.3449668768</v>
+        <v>0.3470271644</v>
       </c>
     </row>
     <row r="202" ht="16" customHeight="1">
@@ -25995,12 +25995,12 @@
       </c>
       <c r="D202" s="18" t="inlineStr">
         <is>
-          <t>CSPKY</t>
+          <t>REPYY</t>
         </is>
       </c>
       <c r="E202" s="19" t="inlineStr">
         <is>
-          <t>COSCO SHIPPING Ports Limited</t>
+          <t>Repsol S.A.</t>
         </is>
       </c>
       <c r="F202" s="26" t="inlineStr">
@@ -26010,16 +26010,16 @@
       </c>
       <c r="G202" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H202" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I202" s="22" t="n">
-        <v>2422076672</v>
+        <v>36010684416</v>
       </c>
       <c r="J202" s="25" t="inlineStr">
         <is>
@@ -26027,21 +26027,21 @@
         </is>
       </c>
       <c r="K202" s="22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L202" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M202" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, LynchPEGY, Forensic-PayoutConfirmed, Fo</t>
+          <t>KPIThreshold, ONeil-CANSLIM, Weinstein-Stage2, LynchPEGY, LynchEV-GY</t>
         </is>
       </c>
       <c r="N202" s="24" t="n">
-        <v>0.3506595668598756</v>
+        <v>0.3758541077045203</v>
       </c>
       <c r="O202" s="24" t="n">
-        <v>0.3436187472</v>
+        <v>0.3449668768</v>
       </c>
     </row>
     <row r="203" ht="16" customHeight="1">
@@ -26055,12 +26055,12 @@
       </c>
       <c r="D203" s="18" t="inlineStr">
         <is>
-          <t>STMEF</t>
+          <t>CSPKY</t>
         </is>
       </c>
       <c r="E203" s="19" t="inlineStr">
         <is>
-          <t>Stmicroelectronics N.V.</t>
+          <t>COSCO SHIPPING Ports Limited</t>
         </is>
       </c>
       <c r="F203" s="26" t="inlineStr">
@@ -26070,16 +26070,16 @@
       </c>
       <c r="G203" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H203" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I203" s="22" t="n">
-        <v>45978894336</v>
+        <v>2422076672</v>
       </c>
       <c r="J203" s="25" t="inlineStr">
         <is>
@@ -26087,21 +26087,21 @@
         </is>
       </c>
       <c r="K203" s="22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L203" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M203" s="21" t="inlineStr">
         <is>
-          <t>LindyMargin, StrongCoverage, Flyover-QuietQuality</t>
+          <t>NarrativeLag, CapitalReturner, LynchPEGY, Forensic-PayoutConfirmed, Fo</t>
         </is>
       </c>
       <c r="N203" s="24" t="n">
-        <v>0.4271592825942886</v>
+        <v>0.3506595668598756</v>
       </c>
       <c r="O203" s="24" t="n">
-        <v>0.3432069266000001</v>
+        <v>0.3436187472</v>
       </c>
     </row>
     <row r="204" ht="16" customHeight="1">
@@ -26115,12 +26115,12 @@
       </c>
       <c r="D204" s="18" t="inlineStr">
         <is>
-          <t>LYSFF</t>
+          <t>STMEF</t>
         </is>
       </c>
       <c r="E204" s="19" t="inlineStr">
         <is>
-          <t>Leroy Seafood Group ASA</t>
+          <t>Stmicroelectronics N.V.</t>
         </is>
       </c>
       <c r="F204" s="26" t="inlineStr">
@@ -26130,16 +26130,16 @@
       </c>
       <c r="G204" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H204" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I204" s="22" t="n">
-        <v>2660695808</v>
+        <v>45978894336</v>
       </c>
       <c r="J204" s="25" t="inlineStr">
         <is>
@@ -26147,21 +26147,21 @@
         </is>
       </c>
       <c r="K204" s="22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L204" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M204" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, Forensic-ExpensedGrowth, Forensic-Payou</t>
+          <t>LindyMargin, StrongCoverage, Flyover-QuietQuality</t>
         </is>
       </c>
       <c r="N204" s="24" t="n">
-        <v>0.3514764416447539</v>
+        <v>0.4271592825942886</v>
       </c>
       <c r="O204" s="24" t="n">
-        <v>0.3414455226</v>
+        <v>0.3432069266000001</v>
       </c>
     </row>
     <row r="205" ht="16" customHeight="1">
@@ -26175,12 +26175,12 @@
       </c>
       <c r="D205" s="18" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>LYSFF</t>
         </is>
       </c>
       <c r="E205" s="19" t="inlineStr">
         <is>
-          <t>Illumina, Inc.</t>
+          <t>Leroy Seafood Group ASA</t>
         </is>
       </c>
       <c r="F205" s="26" t="inlineStr">
@@ -26190,16 +26190,16 @@
       </c>
       <c r="G205" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H205" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I205" s="22" t="n">
-        <v>31173949440</v>
+        <v>2660695808</v>
       </c>
       <c r="J205" s="25" t="inlineStr">
         <is>
@@ -26214,14 +26214,14 @@
       </c>
       <c r="M205" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ROICInflect, LargeCapQuality, Kullamagi-Breakout, Strong</t>
+          <t>NarrativeLag, CapitalReturner, Forensic-ExpensedGrowth, Forensic-Payou</t>
         </is>
       </c>
       <c r="N205" s="24" t="n">
-        <v>0.3713904674941474</v>
+        <v>0.3514764416447539</v>
       </c>
       <c r="O205" s="24" t="n">
-        <v>0.3362889618</v>
+        <v>0.3414455226</v>
       </c>
     </row>
     <row r="206" ht="16" customHeight="1">
@@ -26235,31 +26235,31 @@
       </c>
       <c r="D206" s="18" t="inlineStr">
         <is>
-          <t>SRAIL.SW</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="E206" s="19" t="inlineStr">
         <is>
-          <t>Stadler Rail AG</t>
+          <t>Illumina, Inc.</t>
         </is>
       </c>
       <c r="F206" s="26" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G206" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H206" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I206" s="22" t="n">
-        <v>3688772771.590302</v>
+        <v>31173949440</v>
       </c>
       <c r="J206" s="25" t="inlineStr">
         <is>
@@ -26267,21 +26267,21 @@
         </is>
       </c>
       <c r="K206" s="22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L206" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M206" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, OwnerOperator, LynchPEGY, LynchEV-GY, CheapSale</t>
+          <t>KPIThreshold, ROICInflect, LargeCapQuality, Kullamagi-Breakout, Strong</t>
         </is>
       </c>
       <c r="N206" s="24" t="n">
-        <v>0.3694043486726419</v>
+        <v>0.3713904674941474</v>
       </c>
       <c r="O206" s="24" t="n">
-        <v>0.333221817</v>
+        <v>0.3362889618</v>
       </c>
     </row>
     <row r="207" ht="16" customHeight="1">
@@ -26295,22 +26295,22 @@
       </c>
       <c r="D207" s="18" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>SRAIL.SW</t>
         </is>
       </c>
       <c r="E207" s="19" t="inlineStr">
         <is>
-          <t>Kulicke And Soffa Industries, Inc.</t>
+          <t>Stadler Rail AG</t>
         </is>
       </c>
       <c r="F207" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G207" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H207" s="16" t="inlineStr">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="I207" s="22" t="n">
-        <v>4507106816</v>
+        <v>3688772771.590302</v>
       </c>
       <c r="J207" s="25" t="inlineStr">
         <is>
@@ -26327,21 +26327,21 @@
         </is>
       </c>
       <c r="K207" s="22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L207" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M207" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, DiversifiedSegments, GeographicGlobal, L</t>
+          <t>FixedCost+DemandShock, OwnerOperator, LynchPEGY, LynchEV-GY, CheapSale</t>
         </is>
       </c>
       <c r="N207" s="24" t="n">
-        <v>0.3782164069191616</v>
+        <v>0.3694043486726419</v>
       </c>
       <c r="O207" s="24" t="n">
-        <v>0.330940008</v>
+        <v>0.333221817</v>
       </c>
     </row>
     <row r="208" ht="16" customHeight="1">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="D208" s="18" t="inlineStr">
         <is>
-          <t>ROHCF</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="E208" s="19" t="inlineStr">
         <is>
-          <t>ROHM Co., Ltd.</t>
+          <t>Kulicke And Soffa Industries, Inc.</t>
         </is>
       </c>
       <c r="F208" s="26" t="inlineStr">
@@ -26379,7 +26379,7 @@
         </is>
       </c>
       <c r="I208" s="22" t="n">
-        <v>12038503424</v>
+        <v>4507106816</v>
       </c>
       <c r="J208" s="25" t="inlineStr">
         <is>
@@ -26387,21 +26387,21 @@
         </is>
       </c>
       <c r="K208" s="22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L208" s="22" t="n">
         <v>4</v>
       </c>
       <c r="M208" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage</t>
+          <t>KPIThreshold, StrongCoverage, DiversifiedSegments, GeographicGlobal, L</t>
         </is>
       </c>
       <c r="N208" s="24" t="n">
-        <v>0.4135177562163062</v>
+        <v>0.3782164069191616</v>
       </c>
       <c r="O208" s="24" t="n">
-        <v>0.3263248577</v>
+        <v>0.330940008</v>
       </c>
     </row>
     <row r="209" ht="16" customHeight="1">
@@ -26415,12 +26415,12 @@
       </c>
       <c r="D209" s="18" t="inlineStr">
         <is>
-          <t>AUOTY</t>
+          <t>ROHCF</t>
         </is>
       </c>
       <c r="E209" s="19" t="inlineStr">
         <is>
-          <t>AUO Corporation</t>
+          <t>ROHM Co., Ltd.</t>
         </is>
       </c>
       <c r="F209" s="26" t="inlineStr">
@@ -26439,7 +26439,7 @@
         </is>
       </c>
       <c r="I209" s="22" t="n">
-        <v>7275403776</v>
+        <v>12038503424</v>
       </c>
       <c r="J209" s="25" t="inlineStr">
         <is>
@@ -26447,21 +26447,21 @@
         </is>
       </c>
       <c r="K209" s="22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L209" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M209" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, BalanceSheetReturn, NetCashReturner, Kullamagi-Breakout,</t>
+          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage</t>
         </is>
       </c>
       <c r="N209" s="24" t="n">
-        <v>0.3556502115661384</v>
+        <v>0.4135177562163062</v>
       </c>
       <c r="O209" s="24" t="n">
-        <v>0.3156688956</v>
+        <v>0.3263248577</v>
       </c>
     </row>
     <row r="210" ht="16" customHeight="1">
@@ -26475,12 +26475,12 @@
       </c>
       <c r="D210" s="18" t="inlineStr">
         <is>
-          <t>ROHCY</t>
+          <t>AUOTY</t>
         </is>
       </c>
       <c r="E210" s="19" t="inlineStr">
         <is>
-          <t>ROHM Co., Ltd.</t>
+          <t>AUO Corporation</t>
         </is>
       </c>
       <c r="F210" s="26" t="inlineStr">
@@ -26499,7 +26499,7 @@
         </is>
       </c>
       <c r="I210" s="22" t="n">
-        <v>11627376640</v>
+        <v>7275403776</v>
       </c>
       <c r="J210" s="25" t="inlineStr">
         <is>
@@ -26507,21 +26507,21 @@
         </is>
       </c>
       <c r="K210" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L210" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="L210" s="22" t="n">
-        <v>4</v>
-      </c>
       <c r="M210" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage</t>
+          <t>KPIThreshold, BalanceSheetReturn, NetCashReturner, Kullamagi-Breakout,</t>
         </is>
       </c>
       <c r="N210" s="24" t="n">
-        <v>0.3854642684362932</v>
+        <v>0.3556502115661384</v>
       </c>
       <c r="O210" s="24" t="n">
-        <v>0.3029761515</v>
+        <v>0.3156688956</v>
       </c>
     </row>
     <row r="211" ht="16" customHeight="1">
@@ -26535,12 +26535,12 @@
       </c>
       <c r="D211" s="18" t="inlineStr">
         <is>
-          <t>VIAV</t>
+          <t>ROHCY</t>
         </is>
       </c>
       <c r="E211" s="19" t="inlineStr">
         <is>
-          <t>Viavi Solutions Inc.</t>
+          <t>ROHM Co., Ltd.</t>
         </is>
       </c>
       <c r="F211" s="26" t="inlineStr">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="I211" s="22" t="n">
-        <v>9561555968</v>
+        <v>11627376640</v>
       </c>
       <c r="J211" s="25" t="inlineStr">
         <is>
@@ -26567,21 +26567,21 @@
         </is>
       </c>
       <c r="K211" s="22" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L211" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M211" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LindyMargin, LindyFCF, NoDilution, CapitalLightPivot, Co</t>
+          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage</t>
         </is>
       </c>
       <c r="N211" s="24" t="n">
-        <v>0.3543843895665659</v>
+        <v>0.3854642684362932</v>
       </c>
       <c r="O211" s="24" t="n">
-        <v>0.2895140304</v>
+        <v>0.3029761515</v>
       </c>
     </row>
     <row r="212" ht="16" customHeight="1">
@@ -26595,22 +26595,22 @@
       </c>
       <c r="D212" s="18" t="inlineStr">
         <is>
-          <t>300058.SZ</t>
+          <t>VIAV</t>
         </is>
       </c>
       <c r="E212" s="19" t="inlineStr">
         <is>
-          <t>BlueFocus Intelligent Communications Group Co., Ltd.</t>
+          <t>Viavi Solutions Inc.</t>
         </is>
       </c>
       <c r="F212" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G212" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H212" s="16" t="inlineStr">
@@ -26619,7 +26619,7 @@
         </is>
       </c>
       <c r="I212" s="22" t="n">
-        <v>6978258494.540283</v>
+        <v>9561555968</v>
       </c>
       <c r="J212" s="25" t="inlineStr">
         <is>
@@ -26627,21 +26627,21 @@
         </is>
       </c>
       <c r="K212" s="22" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L212" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M212" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, BAB-Becoming, LigerLaggingInflect</t>
+          <t>KPIThreshold, LindyMargin, LindyFCF, NoDilution, CapitalLightPivot, Co</t>
         </is>
       </c>
       <c r="N212" s="24" t="n">
-        <v>0.3642144155933209</v>
+        <v>0.3543843895665659</v>
       </c>
       <c r="O212" s="24" t="n">
-        <v>0.2862394308</v>
+        <v>0.2895140304</v>
       </c>
     </row>
     <row r="213" ht="16" customHeight="1">
@@ -26655,22 +26655,22 @@
       </c>
       <c r="D213" s="18" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>300058.SZ</t>
         </is>
       </c>
       <c r="E213" s="19" t="inlineStr">
         <is>
-          <t>LifeStance Health Group Inc. Common Stock</t>
+          <t>BlueFocus Intelligent Communications Group Co., Ltd.</t>
         </is>
       </c>
       <c r="F213" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G213" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H213" s="16" t="inlineStr">
@@ -26679,7 +26679,7 @@
         </is>
       </c>
       <c r="I213" s="22" t="n">
-        <v>4956539392</v>
+        <v>6978258494.540283</v>
       </c>
       <c r="J213" s="25" t="inlineStr">
         <is>
@@ -26687,21 +26687,21 @@
         </is>
       </c>
       <c r="K213" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L213" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M213" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Weinstein-Stage2, Kullamagi-Breakout, LynchEV-GY, Asleep</t>
+          <t>KPIThreshold, StrongCoverage, BAB-Becoming, LigerLaggingInflect</t>
         </is>
       </c>
       <c r="N213" s="24" t="n">
-        <v>0.3857802555289219</v>
+        <v>0.3642144155933209</v>
       </c>
       <c r="O213" s="24" t="n">
-        <v>0.2771147229</v>
+        <v>0.2862394308</v>
       </c>
     </row>
     <row r="214" ht="16" customHeight="1">
@@ -26715,31 +26715,31 @@
       </c>
       <c r="D214" s="18" t="inlineStr">
         <is>
-          <t>605289.SS</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="E214" s="19" t="inlineStr">
         <is>
-          <t>Shanghai Luoman Lighting Technologies Inc.</t>
+          <t>LifeStance Health Group Inc. Common Stock</t>
         </is>
       </c>
       <c r="F214" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G214" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H214" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I214" s="22" t="n">
-        <v>2203383810.571838</v>
+        <v>4956539392</v>
       </c>
       <c r="J214" s="25" t="inlineStr">
         <is>
@@ -26747,21 +26747,21 @@
         </is>
       </c>
       <c r="K214" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L214" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M214" s="21" t="inlineStr">
         <is>
-          <t>RegimeCyclical, KPIThreshold, OwnerOperator, TenBaggerPath, TenBaggerP</t>
+          <t>KPIThreshold, Weinstein-Stage2, Kullamagi-Breakout, LynchEV-GY, Asleep</t>
         </is>
       </c>
       <c r="N214" s="24" t="n">
-        <v>0.3608547301929121</v>
+        <v>0.3857802555289219</v>
       </c>
       <c r="O214" s="24" t="n">
-        <v>0.273952194</v>
+        <v>0.2771147229</v>
       </c>
     </row>
     <row r="215" ht="16" customHeight="1">
@@ -26775,31 +26775,31 @@
       </c>
       <c r="D215" s="18" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>605289.SS</t>
         </is>
       </c>
       <c r="E215" s="19" t="inlineStr">
         <is>
-          <t>Nanya Technology Corporation</t>
+          <t>Shanghai Luoman Lighting Technologies Inc.</t>
         </is>
       </c>
       <c r="F215" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G215" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H215" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I215" s="22" t="n">
-        <v>48388455383.396</v>
+        <v>2203383810.571838</v>
       </c>
       <c r="J215" s="25" t="inlineStr">
         <is>
@@ -26810,18 +26810,18 @@
         <v>4</v>
       </c>
       <c r="L215" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M215" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, MidCapGARP, LynchEV-GY, AsleepAtWheel-Beats</t>
+          <t>RegimeCyclical, KPIThreshold, OwnerOperator, TenBaggerPath, TenBaggerP</t>
         </is>
       </c>
       <c r="N215" s="24" t="n">
-        <v>0.5000369663619509</v>
+        <v>0.3608547301929121</v>
       </c>
       <c r="O215" s="24" t="n">
-        <v>0.2702974278</v>
+        <v>0.273952194</v>
       </c>
     </row>
     <row r="216" ht="16" customHeight="1">
@@ -26835,12 +26835,12 @@
       </c>
       <c r="D216" s="18" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="E216" s="19" t="inlineStr">
         <is>
-          <t>Nan Ya Printed Circuit Board Corporation</t>
+          <t>Nanya Technology Corporation</t>
         </is>
       </c>
       <c r="F216" s="26" t="inlineStr">
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="I216" s="22" t="n">
-        <v>22105121921.95679</v>
+        <v>48388455383.396</v>
       </c>
       <c r="J216" s="25" t="inlineStr">
         <is>
@@ -26870,18 +26870,18 @@
         <v>4</v>
       </c>
       <c r="L216" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M216" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, XR-ForensicFloorGrowth, AsleepAtWheel-Be</t>
+          <t>KPIThreshold, MidCapGARP, LynchEV-GY, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="N216" s="24" t="n">
-        <v>0.4799905507601829</v>
+        <v>0.5000369663619509</v>
       </c>
       <c r="O216" s="24" t="n">
-        <v>0.257349768</v>
+        <v>0.2702974278</v>
       </c>
     </row>
     <row r="217" ht="16" customHeight="1">
@@ -26895,17 +26895,17 @@
       </c>
       <c r="D217" s="18" t="inlineStr">
         <is>
-          <t>002281.SZ</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="E217" s="19" t="inlineStr">
         <is>
-          <t>Accelink Technologies Co., Ltd.</t>
+          <t>Nan Ya Printed Circuit Board Corporation</t>
         </is>
       </c>
       <c r="F217" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G217" s="21" t="inlineStr">
@@ -26919,7 +26919,7 @@
         </is>
       </c>
       <c r="I217" s="22" t="n">
-        <v>21702351509.64355</v>
+        <v>22105121921.95679</v>
       </c>
       <c r="J217" s="25" t="inlineStr">
         <is>
@@ -26927,21 +26927,21 @@
         </is>
       </c>
       <c r="K217" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L217" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="L217" s="22" t="n">
-        <v>4</v>
-      </c>
       <c r="M217" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, StrongCoverage, BAB-Becoming</t>
+          <t>KPIThreshold, StrongCoverage, XR-ForensicFloorGrowth, AsleepAtWheel-Be</t>
         </is>
       </c>
       <c r="N217" s="24" t="n">
-        <v>0.3843302829211299</v>
+        <v>0.4799905507601829</v>
       </c>
       <c r="O217" s="24" t="n">
-        <v>0.2476969</v>
+        <v>0.257349768</v>
       </c>
     </row>
     <row r="218" ht="16" customHeight="1">
@@ -26955,22 +26955,22 @@
       </c>
       <c r="D218" s="18" t="inlineStr">
         <is>
-          <t>TSUSF</t>
+          <t>002281.SZ</t>
         </is>
       </c>
       <c r="E218" s="19" t="inlineStr">
         <is>
-          <t>Tsuruha Holdings Inc.</t>
+          <t>Accelink Technologies Co., Ltd.</t>
         </is>
       </c>
       <c r="F218" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G218" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H218" s="16" t="inlineStr">
@@ -26979,7 +26979,7 @@
         </is>
       </c>
       <c r="I218" s="22" t="n">
-        <v>7815836672</v>
+        <v>21702351509.64355</v>
       </c>
       <c r="J218" s="25" t="inlineStr">
         <is>
@@ -26987,21 +26987,21 @@
         </is>
       </c>
       <c r="K218" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L218" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="L218" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="M218" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchEV-GY, ExceptionalEVSG, TenBaggerPath</t>
+          <t>KPIThreshold, StrongCoverage, BAB-Becoming</t>
         </is>
       </c>
       <c r="N218" s="24" t="n">
-        <v>0.5803731904418854</v>
+        <v>0.3843302829211299</v>
       </c>
       <c r="O218" s="24" t="n">
-        <v>0.239856232</v>
+        <v>0.2476969</v>
       </c>
     </row>
     <row r="219" ht="16" customHeight="1">
@@ -27015,12 +27015,12 @@
       </c>
       <c r="D219" s="18" t="inlineStr">
         <is>
-          <t>TIAOF</t>
+          <t>TSUSF</t>
         </is>
       </c>
       <c r="E219" s="19" t="inlineStr">
         <is>
-          <t>Telecom Italia S.p.A.</t>
+          <t>Tsuruha Holdings Inc.</t>
         </is>
       </c>
       <c r="F219" s="26" t="inlineStr">
@@ -27030,16 +27030,16 @@
       </c>
       <c r="G219" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H219" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I219" s="22" t="n">
-        <v>18559361024</v>
+        <v>7815836672</v>
       </c>
       <c r="J219" s="25" t="inlineStr">
         <is>
@@ -27047,25 +27047,85 @@
         </is>
       </c>
       <c r="K219" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L219" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M219" s="21" t="inlineStr">
         <is>
+          <t>Weinstein-Stage2, LynchEV-GY, ExceptionalEVSG, TenBaggerPath</t>
+        </is>
+      </c>
+      <c r="N219" s="24" t="n">
+        <v>0.5803731904418854</v>
+      </c>
+      <c r="O219" s="24" t="n">
+        <v>0.239856232</v>
+      </c>
+    </row>
+    <row r="220" ht="16" customHeight="1">
+      <c r="B220" s="16" t="n">
+        <v>217</v>
+      </c>
+      <c r="C220" s="17" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="D220" s="18" t="inlineStr">
+        <is>
+          <t>TIAOF</t>
+        </is>
+      </c>
+      <c r="E220" s="19" t="inlineStr">
+        <is>
+          <t>Telecom Italia S.p.A.</t>
+        </is>
+      </c>
+      <c r="F220" s="26" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G220" s="21" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="H220" s="16" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="I220" s="22" t="n">
+        <v>18559361024</v>
+      </c>
+      <c r="J220" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="K220" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L220" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M220" s="21" t="inlineStr">
+        <is>
           <t>KPIThreshold, Weinstein-Stage2, Kullamagi-Breakout</t>
         </is>
       </c>
-      <c r="N219" s="24" t="n">
+      <c r="N220" s="24" t="n">
         <v>0.3606072781109206</v>
       </c>
-      <c r="O219" s="24" t="n">
+      <c r="O220" s="24" t="n">
         <v>0.1493827233</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:O219"/>
+  <autoFilter ref="B3:O220"/>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
@@ -36866,14 +36926,14 @@
         </is>
       </c>
       <c r="K165" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L165" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M165" s="21" t="inlineStr">
         <is>
-          <t>OwnerOperator, Weinstein-Stage2, LynchPEGY, LynchEV-GY, Forensic-Payou</t>
+          <t>OwnerOperator, Weinstein-Stage2, LynchPEGY, LynchEV-GY, OakDeleveragin</t>
         </is>
       </c>
       <c r="N165" s="24" t="n">
@@ -37106,14 +37166,14 @@
         </is>
       </c>
       <c r="K169" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L169" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M169" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, KPIThreshold, OakDeepValue, XR-AssetOwnerCat</t>
+          <t>NarrativeLag, DeadOption, KPIThreshold, OakDeleveraging, OakDeepValue,</t>
         </is>
       </c>
       <c r="N169" s="24" t="n">
@@ -37226,7 +37286,7 @@
         </is>
       </c>
       <c r="K171" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L171" s="22" t="n">
         <v>2</v>
@@ -37522,14 +37582,14 @@
         </is>
       </c>
       <c r="K176" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L176" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M176" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, LynchEV-GY, Forensic-OwnerEarnings, Forensic-Payout</t>
+          <t>CapitalDiscipline, LynchEV-GY, OakDeleveraging, Forensic-OwnerEarnings</t>
         </is>
       </c>
       <c r="N176" s="24" t="n">
@@ -39134,14 +39194,14 @@
         </is>
       </c>
       <c r="K203" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L203" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M203" s="21" t="inlineStr">
         <is>
-          <t>QuietCompounder, OwnerOperator, BAB-Becoming, LynchPEGY, LynchEV-GY, C</t>
+          <t>QuietCompounder, OwnerOperator, BAB-Becoming, LynchPEGY, LynchEV-GY, O</t>
         </is>
       </c>
       <c r="N203" s="24" t="n">
@@ -42010,14 +42070,14 @@
         </is>
       </c>
       <c r="K251" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L251" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M251" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, Forensic-PayoutConfirmed, Forensic-CannibalDiscount</t>
+          <t>CapitalDiscipline, OakDeleveraging, Forensic-PayoutConfirmed, Forensic</t>
         </is>
       </c>
       <c r="N251" s="24" t="n">
@@ -44582,14 +44642,14 @@
         </is>
       </c>
       <c r="K294" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L294" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M294" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, OwnerOperator, BAB-Becoming, Forensic-UnderstatedE,</t>
+          <t>CapitalDiscipline, OwnerOperator, BAB-Becoming, OakDeleveraging, Foren</t>
         </is>
       </c>
       <c r="N294" s="24" t="n">
@@ -46498,14 +46558,14 @@
         </is>
       </c>
       <c r="K326" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L326" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M326" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, LynchEV-GY, Forensic-PayoutConfirmed, For</t>
+          <t>Weinstein-Stage2, LynchPEGY, LynchEV-GY, OakDeleveraging, Forensic-Pay</t>
         </is>
       </c>
       <c r="N326" s="24" t="n">
@@ -46794,7 +46854,7 @@
         </is>
       </c>
       <c r="K331" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L331" s="22" t="n">
         <v>1</v>
@@ -47154,14 +47214,14 @@
         </is>
       </c>
       <c r="K337" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L337" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M337" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, BAB-Becoming, Forensic-OwnerEarnings, Forensic-PayoutCon</t>
+          <t>NarrativeLag, BAB-Becoming, OakDeleveraging, Forensic-OwnerEarnings, F</t>
         </is>
       </c>
       <c r="N337" s="24" t="n">
@@ -48170,14 +48230,14 @@
         </is>
       </c>
       <c r="K354" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L354" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M354" s="21" t="inlineStr">
         <is>
-          <t>BAB-Becoming, Forensic-PayoutConfirmed, Forensic-CannibalDiscount, XR-</t>
+          <t>BAB-Becoming, OakDeleveraging, Forensic-PayoutConfirmed, Forensic-Cann</t>
         </is>
       </c>
       <c r="N354" s="24" t="n">
@@ -48646,14 +48706,14 @@
         </is>
       </c>
       <c r="K362" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L362" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M362" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, Forensic-UnderstatedE, NegativeEV-Value, AnalystAwak</t>
+          <t>Weinstein-Stage2, OakDeleveraging, Forensic-UnderstatedE, NegativeEV-V</t>
         </is>
       </c>
       <c r="N362" s="24" t="n">
@@ -48946,14 +49006,14 @@
         </is>
       </c>
       <c r="K367" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L367" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M367" s="21" t="inlineStr">
         <is>
-          <t>LynchEV-GY, Forensic-UnderstatedE, Forensic-SelfFunded, ExceptionalEVS</t>
+          <t>LynchEV-GY, OakDeleveraging, Forensic-UnderstatedE, Forensic-SelfFunde</t>
         </is>
       </c>
       <c r="N367" s="24" t="n">
@@ -49246,14 +49306,14 @@
         </is>
       </c>
       <c r="K372" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L372" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M372" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, LargeCapQuality, MidCapGARP, LynchPEGY, XR-ForensicFloor</t>
+          <t>NarrativeLag, LargeCapQuality, MidCapGARP, LynchPEGY, OakDeleveraging,</t>
         </is>
       </c>
       <c r="N372" s="24" t="n">
@@ -49366,14 +49426,14 @@
         </is>
       </c>
       <c r="K374" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L374" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M374" s="21" t="inlineStr">
         <is>
-          <t>BAB-Becoming, Forensic-PayoutConfirmed, Forensic-CannibalDiscount, XR-</t>
+          <t>BAB-Becoming, OakDeleveraging, Forensic-PayoutConfirmed, Forensic-Cann</t>
         </is>
       </c>
       <c r="N374" s="24" t="n">
@@ -52842,14 +52902,14 @@
         </is>
       </c>
       <c r="K432" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L432" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M432" s="21" t="inlineStr">
         <is>
-          <t>MidCapGARP, LynchEV-GY, Forensic-OverDepreciated, Forensic-PayoutConfi</t>
+          <t>MidCapGARP, LynchEV-GY, OakDeleveraging, Forensic-OverDepreciated, For</t>
         </is>
       </c>
       <c r="N432" s="24" t="n">
@@ -55294,14 +55354,14 @@
         </is>
       </c>
       <c r="K473" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L473" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M473" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, BAB-Becoming, LynchEV-GY, Forensic-UnderstatedE, Forensi</t>
+          <t>NarrativeLag, BAB-Becoming, LynchEV-GY, OakDeleveraging, Forensic-Unde</t>
         </is>
       </c>
       <c r="N473" s="24" t="n">

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 4,228 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (218) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (218) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3792) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 4,227 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (218) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (218) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (3791) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>3,792</t>
+          <t>3,791</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="K44" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L44" s="22" t="n">
         <v>3</v>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="K96" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L96" s="22" t="n">
         <v>4</v>
@@ -10948,12 +10948,12 @@
       </c>
       <c r="D170" s="18" t="inlineStr">
         <is>
-          <t>PIFMF</t>
+          <t>UMICF</t>
         </is>
       </c>
       <c r="E170" s="19" t="inlineStr">
         <is>
-          <t>PT Indofood Sukses Makmur Tbk</t>
+          <t>Umicore SA</t>
         </is>
       </c>
       <c r="F170" s="26" t="inlineStr">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="G170" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H170" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I170" s="22" t="n">
-        <v>3599974656</v>
+        <v>6209218048</v>
       </c>
       <c r="J170" s="25" t="inlineStr">
         <is>
@@ -10980,21 +10980,21 @@
         </is>
       </c>
       <c r="K170" s="22" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L170" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M170" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, MidCapGARP, LynchEV-GY</t>
+          <t>FixedCost+DemandShock, KPIThreshold, MidCapGARP, BAB-Becoming, LynchPE</t>
         </is>
       </c>
       <c r="N170" s="24" t="n">
-        <v>0.425402653358671</v>
+        <v>0.4333506010109346</v>
       </c>
       <c r="O170" s="24" t="n">
-        <v>0.44183961</v>
+        <v>0.441537726</v>
       </c>
     </row>
     <row r="171" ht="16" customHeight="1">
@@ -11008,22 +11008,22 @@
       </c>
       <c r="D171" s="18" t="inlineStr">
         <is>
-          <t>UMICF</t>
+          <t>603659.SS</t>
         </is>
       </c>
       <c r="E171" s="19" t="inlineStr">
         <is>
-          <t>Umicore SA</t>
+          <t>Shanghai Putailai New Energy Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="F171" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G171" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H171" s="16" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="I171" s="22" t="n">
-        <v>6209218048</v>
+        <v>6775944979.991455</v>
       </c>
       <c r="J171" s="25" t="inlineStr">
         <is>
@@ -11040,21 +11040,21 @@
         </is>
       </c>
       <c r="K171" s="22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L171" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M171" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, KPIThreshold, MidCapGARP, BAB-Becoming, LynchPE</t>
+          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, KPIThreshold, MidCapG</t>
         </is>
       </c>
       <c r="N171" s="24" t="n">
-        <v>0.4333506010109346</v>
+        <v>0.4185875724253831</v>
       </c>
       <c r="O171" s="24" t="n">
-        <v>0.441537726</v>
+        <v>0.4413756964</v>
       </c>
     </row>
     <row r="172" ht="16" customHeight="1">
@@ -11068,31 +11068,31 @@
       </c>
       <c r="D172" s="18" t="inlineStr">
         <is>
-          <t>603659.SS</t>
+          <t>IHS</t>
         </is>
       </c>
       <c r="E172" s="19" t="inlineStr">
         <is>
-          <t>Shanghai Putailai New Energy Technology Co., Ltd.</t>
+          <t>IHS Holding Limited Ordinary Shares</t>
         </is>
       </c>
       <c r="F172" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G172" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H172" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I172" s="22" t="n">
-        <v>6775944979.991455</v>
+        <v>2865746176</v>
       </c>
       <c r="J172" s="25" t="inlineStr">
         <is>
@@ -11100,21 +11100,21 @@
         </is>
       </c>
       <c r="K172" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L172" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M172" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, KPIThreshold, MidCapG</t>
+          <t>KPIThreshold, QuietCompounder, MidCapGARP, LynchEV-GY, Forensic-Unders</t>
         </is>
       </c>
       <c r="N172" s="24" t="n">
-        <v>0.4185875724253831</v>
+        <v>0.4081869342601544</v>
       </c>
       <c r="O172" s="24" t="n">
-        <v>0.4413756964</v>
+        <v>0.4408415999999999</v>
       </c>
     </row>
     <row r="173" ht="16" customHeight="1">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="D173" s="18" t="inlineStr">
         <is>
-          <t>IHS</t>
+          <t>PIFMF</t>
         </is>
       </c>
       <c r="E173" s="19" t="inlineStr">
         <is>
-          <t>IHS Holding Limited Ordinary Shares</t>
+          <t>PT Indofood Sukses Makmur Tbk</t>
         </is>
       </c>
       <c r="F173" s="26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G173" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H173" s="16" t="inlineStr">
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="I173" s="22" t="n">
-        <v>2865746176</v>
+        <v>3599974656</v>
       </c>
       <c r="J173" s="25" t="inlineStr">
         <is>
@@ -11160,21 +11160,21 @@
         </is>
       </c>
       <c r="K173" s="22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L173" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M173" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, QuietCompounder, MidCapGARP, LynchEV-GY, Forensic-Unders</t>
+          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, MidCapGARP, LynchEV-GY</t>
         </is>
       </c>
       <c r="N173" s="24" t="n">
-        <v>0.4081869342601544</v>
+        <v>0.425402653358671</v>
       </c>
       <c r="O173" s="24" t="n">
-        <v>0.4408415999999999</v>
+        <v>0.4405160376</v>
       </c>
     </row>
     <row r="174" ht="16" customHeight="1">
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="K202" s="22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L202" s="22" t="n">
         <v>4</v>
@@ -19103,53 +19103,53 @@
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>PIFMY</t>
+          <t>VNA.DE</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>PT Indofood Sukses Makmur Tbk</t>
+          <t>Vonovia SE</t>
         </is>
       </c>
       <c r="F86" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G86" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H86" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I86" s="22" t="n">
-        <v>3487585536</v>
-      </c>
-      <c r="J86" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>17725510292.5708</v>
+      </c>
+      <c r="J86" s="26" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K86" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L86" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="L86" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="M86" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, LynchEV-GY, LigerLaggingInflect, NegativeEV-</t>
+          <t>LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-BeatsNoRerate, Analyst</t>
         </is>
       </c>
       <c r="N86" s="24" t="n">
-        <v>0.3979056090610184</v>
+        <v>0.4370623405061705</v>
       </c>
       <c r="O86" s="24" t="n">
-        <v>0.409080105</v>
+        <v>0.4090182828</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
@@ -19163,22 +19163,22 @@
       </c>
       <c r="D87" s="18" t="inlineStr">
         <is>
-          <t>VNA.DE</t>
+          <t>NJDCY</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>Vonovia SE</t>
+          <t>Nidec Corp.</t>
         </is>
       </c>
       <c r="F87" s="26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G87" s="21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H87" s="16" t="inlineStr">
@@ -19187,29 +19187,29 @@
         </is>
       </c>
       <c r="I87" s="22" t="n">
-        <v>17725510292.5708</v>
-      </c>
-      <c r="J87" s="26" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>17872109568</v>
+      </c>
+      <c r="J87" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K87" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L87" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="L87" s="22" t="n">
-        <v>5</v>
-      </c>
       <c r="M87" s="21" t="inlineStr">
         <is>
-          <t>LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-BeatsNoRerate, Analyst</t>
+          <t>NarrativeLag, FixedCost+DemandShock, BAB-Becoming, LynchPEGY, XR-Foren</t>
         </is>
       </c>
       <c r="N87" s="24" t="n">
-        <v>0.4370623405061705</v>
+        <v>0.3921379635500283</v>
       </c>
       <c r="O87" s="24" t="n">
-        <v>0.4090182828</v>
+        <v>0.4088271616</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="D88" s="18" t="inlineStr">
         <is>
-          <t>NJDCY</t>
+          <t>NNDNF</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
@@ -19247,7 +19247,7 @@
         </is>
       </c>
       <c r="I88" s="22" t="n">
-        <v>17872109568</v>
+        <v>19198672896</v>
       </c>
       <c r="J88" s="25" t="inlineStr">
         <is>
@@ -19255,21 +19255,21 @@
         </is>
       </c>
       <c r="K88" s="22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L88" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M88" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, BAB-Becoming, LynchPEGY, XR-Foren</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, BAB-Becoming, Lyn</t>
         </is>
       </c>
       <c r="N88" s="24" t="n">
-        <v>0.3921379635500283</v>
+        <v>0.391851000844459</v>
       </c>
       <c r="O88" s="24" t="n">
-        <v>0.4088271616</v>
+        <v>0.4085282943999999</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -19283,12 +19283,12 @@
       </c>
       <c r="D89" s="18" t="inlineStr">
         <is>
-          <t>NNDNF</t>
+          <t>KSANF</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>Nidec Corp.</t>
+          <t>Kansai Paint Co., Ltd.</t>
         </is>
       </c>
       <c r="F89" s="26" t="inlineStr">
@@ -19298,16 +19298,16 @@
       </c>
       <c r="G89" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H89" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I89" s="22" t="n">
-        <v>19198672896</v>
+        <v>3107836928</v>
       </c>
       <c r="J89" s="25" t="inlineStr">
         <is>
@@ -19315,21 +19315,21 @@
         </is>
       </c>
       <c r="K89" s="22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L89" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M89" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, BAB-Becoming, Lyn</t>
+          <t>BalanceSheetReturn, CashAdjPE-NegOrCheap, Forensic-PayoutConfirmed, Ne</t>
         </is>
       </c>
       <c r="N89" s="24" t="n">
-        <v>0.391851000844459</v>
+        <v>0.3888518122768227</v>
       </c>
       <c r="O89" s="24" t="n">
-        <v>0.4085282943999999</v>
+        <v>0.4082715022</v>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
@@ -19343,17 +19343,17 @@
       </c>
       <c r="D90" s="18" t="inlineStr">
         <is>
-          <t>KSANF</t>
+          <t>EQX.TO</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>Kansai Paint Co., Ltd.</t>
+          <t>Equinox Gold Corp.</t>
         </is>
       </c>
       <c r="F90" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G90" s="21" t="inlineStr">
@@ -19367,7 +19367,7 @@
         </is>
       </c>
       <c r="I90" s="22" t="n">
-        <v>3107836928</v>
+        <v>14354527646.84619</v>
       </c>
       <c r="J90" s="25" t="inlineStr">
         <is>
@@ -19375,21 +19375,21 @@
         </is>
       </c>
       <c r="K90" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L90" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="L90" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="M90" s="21" t="inlineStr">
         <is>
-          <t>BalanceSheetReturn, CashAdjPE-NegOrCheap, Forensic-PayoutConfirmed, Ne</t>
+          <t>FixedCost+DemandShock, RegimeCyclical, KPIThreshold, LynchPEGY, LynchE</t>
         </is>
       </c>
       <c r="N90" s="24" t="n">
-        <v>0.3888518122768227</v>
+        <v>0.3891677996930489</v>
       </c>
       <c r="O90" s="24" t="n">
-        <v>0.4082715022</v>
+        <v>0.4082525656</v>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
@@ -19403,22 +19403,22 @@
       </c>
       <c r="D91" s="18" t="inlineStr">
         <is>
-          <t>EQX.TO</t>
+          <t>PIFMY</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>Equinox Gold Corp.</t>
+          <t>PT Indofood Sukses Makmur Tbk</t>
         </is>
       </c>
       <c r="F91" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G91" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H91" s="16" t="inlineStr">
@@ -19427,7 +19427,7 @@
         </is>
       </c>
       <c r="I91" s="22" t="n">
-        <v>14354527646.84619</v>
+        <v>3487585536</v>
       </c>
       <c r="J91" s="25" t="inlineStr">
         <is>
@@ -19435,21 +19435,21 @@
         </is>
       </c>
       <c r="K91" s="22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M91" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, RegimeCyclical, KPIThreshold, LynchPEGY, LynchE</t>
+          <t>NarrativeLag, MidCapGARP, LynchEV-GY, LigerLaggingInflect</t>
         </is>
       </c>
       <c r="N91" s="24" t="n">
-        <v>0.3891677996930489</v>
+        <v>0.3979056090610184</v>
       </c>
       <c r="O91" s="24" t="n">
-        <v>0.4082525656</v>
+        <v>0.4078546668</v>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
@@ -27167,14 +27167,14 @@
         </is>
       </c>
       <c r="K220" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L220" s="22" t="n">
         <v>3</v>
       </c>
       <c r="M220" s="21" t="inlineStr">
         <is>
-          <t>LynchEV-GY, ExceptionalEVSG, TenBaggerPath</t>
+          <t>Weinstein-Stage2, LynchEV-GY, ExceptionalEVSG, TenBaggerPath</t>
         </is>
       </c>
       <c r="N220" s="24" t="n">
@@ -27598,7 +27598,7 @@
         </is>
       </c>
       <c r="K7" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" s="22" t="n">
         <v>2</v>
@@ -28018,14 +28018,14 @@
         </is>
       </c>
       <c r="K14" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L14" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M14" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, NetCashReturner, StrongCoverage, LigerL</t>
+          <t>NarrativeLag, CapitalReturner, NetCashReturner, StrongCoverage, LynchE</t>
         </is>
       </c>
       <c r="N14" s="24" t="n">
@@ -31750,12 +31750,12 @@
       </c>
       <c r="D77" s="18" t="inlineStr">
         <is>
-          <t>AYYLF</t>
+          <t>CIHKY</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>Ayala Corporation</t>
+          <t>China Merchants Bank Co., Ltd.</t>
         </is>
       </c>
       <c r="F77" s="26" t="inlineStr">
@@ -31765,16 +31765,16 @@
       </c>
       <c r="G77" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H77" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mega Cap</t>
         </is>
       </c>
       <c r="I77" s="22" t="n">
-        <v>5110343680</v>
+        <v>166955368448</v>
       </c>
       <c r="J77" s="25" t="inlineStr">
         <is>
@@ -31782,21 +31782,21 @@
         </is>
       </c>
       <c r="K77" s="22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L77" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M77" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, NetCashReturner, LynchEV-GY, XR-CyclicalTrou</t>
+          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY</t>
         </is>
       </c>
       <c r="N77" s="24" t="n">
-        <v>0.375730911793973</v>
+        <v>0.3789959204316813</v>
       </c>
       <c r="O77" s="24" t="n">
-        <v>0.5162614800000001</v>
+        <v>0.5152824</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
@@ -31810,12 +31810,12 @@
       </c>
       <c r="D78" s="18" t="inlineStr">
         <is>
-          <t>CIHKY</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>China Merchants Bank Co., Ltd.</t>
+          <t>Korn Ferry</t>
         </is>
       </c>
       <c r="F78" s="26" t="inlineStr">
@@ -31825,16 +31825,16 @@
       </c>
       <c r="G78" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H78" s="16" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I78" s="22" t="n">
-        <v>166955368448</v>
+        <v>4233221120</v>
       </c>
       <c r="J78" s="25" t="inlineStr">
         <is>
@@ -31842,21 +31842,21 @@
         </is>
       </c>
       <c r="K78" s="22" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="L78" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="21" t="inlineStr">
         <is>
-          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY</t>
+          <t>FixedCost+DemandShock, CapitalDiscipline, DurableReinvest, CheapPerROI</t>
         </is>
       </c>
       <c r="N78" s="24" t="n">
-        <v>0.3789959204316813</v>
+        <v>0.4791088848212037</v>
       </c>
       <c r="O78" s="24" t="n">
-        <v>0.5152824</v>
+        <v>0.5151522376000001</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
@@ -31870,12 +31870,12 @@
       </c>
       <c r="D79" s="18" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>GNW</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>Korn Ferry</t>
+          <t>Genworth Financial, Inc.</t>
         </is>
       </c>
       <c r="F79" s="26" t="inlineStr">
@@ -31885,7 +31885,7 @@
       </c>
       <c r="G79" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H79" s="16" t="inlineStr">
@@ -31894,7 +31894,7 @@
         </is>
       </c>
       <c r="I79" s="22" t="n">
-        <v>4233221120</v>
+        <v>3963657216</v>
       </c>
       <c r="J79" s="25" t="inlineStr">
         <is>
@@ -31902,21 +31902,21 @@
         </is>
       </c>
       <c r="K79" s="22" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L79" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M79" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, CapitalDiscipline, DurableReinvest, CheapPerROI</t>
+          <t>Weinstein-Stage2, Forensic-PayoutConfirmed, Forensic-BookCompounder</t>
         </is>
       </c>
       <c r="N79" s="24" t="n">
-        <v>0.4791088848212037</v>
+        <v>0.3886650993162909</v>
       </c>
       <c r="O79" s="24" t="n">
-        <v>0.5151522376000001</v>
+        <v>0.5148748440000001</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="D80" s="18" t="inlineStr">
         <is>
-          <t>GNW</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>Genworth Financial, Inc.</t>
+          <t>Maplebear Inc.</t>
         </is>
       </c>
       <c r="F80" s="26" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="G80" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H80" s="16" t="inlineStr">
@@ -31954,7 +31954,7 @@
         </is>
       </c>
       <c r="I80" s="22" t="n">
-        <v>3963657216</v>
+        <v>11280998400</v>
       </c>
       <c r="J80" s="25" t="inlineStr">
         <is>
@@ -31962,21 +31962,21 @@
         </is>
       </c>
       <c r="K80" s="22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L80" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, Forensic-PayoutConfirmed, Forensic-BookCompounder</t>
+          <t>CapitalDiscipline, LargeCapQuality, CapitalReturner, Weinstein-Stage2,</t>
         </is>
       </c>
       <c r="N80" s="24" t="n">
-        <v>0.3886650993162909</v>
+        <v>0.4606116694859642</v>
       </c>
       <c r="O80" s="24" t="n">
-        <v>0.5148748440000001</v>
+        <v>0.51417472</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="D81" s="18" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>SWRBF</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>Maplebear Inc.</t>
+          <t>Swire Pacific Limited</t>
         </is>
       </c>
       <c r="F81" s="26" t="inlineStr">
@@ -32005,16 +32005,16 @@
       </c>
       <c r="G81" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H81" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I81" s="22" t="n">
-        <v>11280998400</v>
+        <v>10886654976</v>
       </c>
       <c r="J81" s="25" t="inlineStr">
         <is>
@@ -32022,21 +32022,21 @@
         </is>
       </c>
       <c r="K81" s="22" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L81" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, LargeCapQuality, CapitalReturner, Weinstein-Stage2,</t>
+          <t>FixedCost+DemandShock, CapitalReturner, Forensic-OverDepreciated, Fore</t>
         </is>
       </c>
       <c r="N81" s="24" t="n">
-        <v>0.4606116694859642</v>
+        <v>0.4823864540425946</v>
       </c>
       <c r="O81" s="24" t="n">
-        <v>0.51417472</v>
+        <v>0.5140304999999999</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
@@ -32050,12 +32050,12 @@
       </c>
       <c r="D82" s="18" t="inlineStr">
         <is>
-          <t>SWRBF</t>
+          <t>HRSHF</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>Swire Pacific Limited</t>
+          <t>Haier Smart Home Co., Ltd. Class H</t>
         </is>
       </c>
       <c r="F82" s="26" t="inlineStr">
@@ -32065,7 +32065,7 @@
       </c>
       <c r="G82" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H82" s="16" t="inlineStr">
@@ -32074,7 +32074,7 @@
         </is>
       </c>
       <c r="I82" s="22" t="n">
-        <v>10886654976</v>
+        <v>23722874880</v>
       </c>
       <c r="J82" s="25" t="inlineStr">
         <is>
@@ -32082,21 +32082,21 @@
         </is>
       </c>
       <c r="K82" s="22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L82" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M82" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, CapitalReturner, Forensic-OverDepreciated, Fore</t>
+          <t>CapitalReturner, BalanceSheetReturn, StrongCoverage, LigerLaggingInfle</t>
         </is>
       </c>
       <c r="N82" s="24" t="n">
-        <v>0.4823864540425946</v>
+        <v>0.4487960654074911</v>
       </c>
       <c r="O82" s="24" t="n">
-        <v>0.5140304999999999</v>
+        <v>0.5137284</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
@@ -32110,31 +32110,31 @@
       </c>
       <c r="D83" s="18" t="inlineStr">
         <is>
-          <t>HRSHF</t>
+          <t>600095.SS</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>Haier Smart Home Co., Ltd. Class H</t>
+          <t>Xiangcai Co., Ltd.</t>
         </is>
       </c>
       <c r="F83" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G83" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H83" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I83" s="22" t="n">
-        <v>23722874880</v>
+        <v>3626018767.532593</v>
       </c>
       <c r="J83" s="25" t="inlineStr">
         <is>
@@ -32142,21 +32142,21 @@
         </is>
       </c>
       <c r="K83" s="22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M83" s="21" t="inlineStr">
         <is>
-          <t>CapitalReturner, BalanceSheetReturn, StrongCoverage, LigerLaggingInfle</t>
+          <t>NarrativeLag, BalanceSheetReturn, NetCashReturner, StrongCoverage, Lyn</t>
         </is>
       </c>
       <c r="N83" s="24" t="n">
-        <v>0.4487960654074911</v>
+        <v>0.4409834804508652</v>
       </c>
       <c r="O83" s="24" t="n">
-        <v>0.5137284</v>
+        <v>0.5122606664000001</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -32170,22 +32170,22 @@
       </c>
       <c r="D84" s="18" t="inlineStr">
         <is>
-          <t>600095.SS</t>
+          <t>EVD.DE</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>Xiangcai Co., Ltd.</t>
+          <t>CTS Eventim AG &amp; Co. KGaA</t>
         </is>
       </c>
       <c r="F84" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G84" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H84" s="16" t="inlineStr">
@@ -32194,29 +32194,29 @@
         </is>
       </c>
       <c r="I84" s="22" t="n">
-        <v>3626018767.532593</v>
-      </c>
-      <c r="J84" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>6297144095.853516</v>
+      </c>
+      <c r="J84" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="K84" s="22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M84" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, BalanceSheetReturn, NetCashReturner, StrongCoverage, Lyn</t>
+          <t>NarrativeLag, DeadOption, MidCapGARP, StrongCoverage, BAB-Becoming, Ly</t>
         </is>
       </c>
       <c r="N84" s="24" t="n">
-        <v>0.4409834804508652</v>
+        <v>0.4524262018429997</v>
       </c>
       <c r="O84" s="24" t="n">
-        <v>0.5122606664000001</v>
+        <v>0.5121311468</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -32230,22 +32230,22 @@
       </c>
       <c r="D85" s="18" t="inlineStr">
         <is>
-          <t>EVD.DE</t>
+          <t>PAYC</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>CTS Eventim AG &amp; Co. KGaA</t>
+          <t>Paycom Software, Inc.</t>
         </is>
       </c>
       <c r="F85" s="26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G85" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H85" s="16" t="inlineStr">
@@ -32254,29 +32254,29 @@
         </is>
       </c>
       <c r="I85" s="22" t="n">
-        <v>6297144095.853516</v>
-      </c>
-      <c r="J85" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>9866628096</v>
+      </c>
+      <c r="J85" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K85" s="22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L85" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M85" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, MidCapGARP, StrongCoverage, BAB-Becoming, Ly</t>
+          <t>NarrativeLag, CapitalDiscipline, LindyMargin, LindyFCF, QuietCompounde</t>
         </is>
       </c>
       <c r="N85" s="24" t="n">
-        <v>0.4524262018429997</v>
+        <v>0.4527245679569818</v>
       </c>
       <c r="O85" s="24" t="n">
-        <v>0.5121311468</v>
+        <v>0.5120041832000001</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
@@ -32290,17 +32290,17 @@
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>PAYC</t>
+          <t>900926.SS</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>Paycom Software, Inc.</t>
+          <t>Shanghai Baosight Software Co.,Ltd.</t>
         </is>
       </c>
       <c r="F86" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G86" s="21" t="inlineStr">
@@ -32310,11 +32310,11 @@
       </c>
       <c r="H86" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I86" s="22" t="n">
-        <v>9866628096</v>
+        <v>2412070912</v>
       </c>
       <c r="J86" s="25" t="inlineStr">
         <is>
@@ -32322,21 +32322,21 @@
         </is>
       </c>
       <c r="K86" s="22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L86" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M86" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, LindyMargin, LindyFCF, QuietCompounde</t>
+          <t>NarrativeLag, DeadOption, BalanceSheetReturn, StrongCoverage, LynchPEG</t>
         </is>
       </c>
       <c r="N86" s="24" t="n">
-        <v>0.4527245679569818</v>
+        <v>0.4680241826245717</v>
       </c>
       <c r="O86" s="24" t="n">
-        <v>0.5120041832000001</v>
+        <v>0.51147745</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
@@ -32350,31 +32350,31 @@
       </c>
       <c r="D87" s="18" t="inlineStr">
         <is>
-          <t>900926.SS</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>Shanghai Baosight Software Co.,Ltd.</t>
+          <t>Millrose Properties, Inc.</t>
         </is>
       </c>
       <c r="F87" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G87" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H87" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I87" s="22" t="n">
-        <v>2412070912</v>
+        <v>4929963008</v>
       </c>
       <c r="J87" s="25" t="inlineStr">
         <is>
@@ -32382,21 +32382,21 @@
         </is>
       </c>
       <c r="K87" s="22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M87" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, BalanceSheetReturn, StrongCoverage, LynchPEG</t>
+          <t>LynchPEGY, InsiderConviction-SEC</t>
         </is>
       </c>
       <c r="N87" s="24" t="n">
-        <v>0.4680241826245717</v>
+        <v>0.4569553886753627</v>
       </c>
       <c r="O87" s="24" t="n">
-        <v>0.51147745</v>
+        <v>0.5107847999999999</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
@@ -32410,31 +32410,31 @@
       </c>
       <c r="D88" s="18" t="inlineStr">
         <is>
-          <t>MRP</t>
+          <t>NWG.L</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>Millrose Properties, Inc.</t>
+          <t>NatWest Group plc</t>
         </is>
       </c>
       <c r="F88" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G88" s="21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H88" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I88" s="22" t="n">
-        <v>4929963008</v>
+        <v>73410600587.56494</v>
       </c>
       <c r="J88" s="25" t="inlineStr">
         <is>
@@ -32442,21 +32442,21 @@
         </is>
       </c>
       <c r="K88" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M88" s="21" t="inlineStr">
         <is>
-          <t>LynchPEGY, InsiderConviction-SEC</t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
         </is>
       </c>
       <c r="N88" s="24" t="n">
-        <v>0.4569553886753627</v>
+        <v>0.3209231417148051</v>
       </c>
       <c r="O88" s="24" t="n">
-        <v>0.5107847999999999</v>
+        <v>0.51053298</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="D89" s="18" t="inlineStr">
         <is>
-          <t>NWG.L</t>
+          <t>AYYLF</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>NatWest Group plc</t>
+          <t>Ayala Corporation</t>
         </is>
       </c>
       <c r="F89" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G89" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H89" s="16" t="inlineStr">
@@ -32494,7 +32494,7 @@
         </is>
       </c>
       <c r="I89" s="22" t="n">
-        <v>73410600587.56494</v>
+        <v>5110343680</v>
       </c>
       <c r="J89" s="25" t="inlineStr">
         <is>
@@ -32502,21 +32502,21 @@
         </is>
       </c>
       <c r="K89" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M89" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
+          <t>NarrativeLag, MidCapGARP, NetCashReturner, LynchEV-GY, XR-CyclicalTrou</t>
         </is>
       </c>
       <c r="N89" s="24" t="n">
-        <v>0.3209231417148051</v>
+        <v>0.375730911793973</v>
       </c>
       <c r="O89" s="24" t="n">
-        <v>0.51053298</v>
+        <v>0.510475791</v>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
@@ -39494,7 +39494,7 @@
         </is>
       </c>
       <c r="K206" s="22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L206" s="22" t="n">
         <v>2</v>
@@ -39942,22 +39942,22 @@
       </c>
       <c r="D214" s="18" t="inlineStr">
         <is>
-          <t>PHTCF</t>
+          <t>NAVINFLUOR.NS</t>
         </is>
       </c>
       <c r="E214" s="19" t="inlineStr">
         <is>
-          <t>PLDT Inc.</t>
+          <t>Navin Fluorine International Limited</t>
         </is>
       </c>
       <c r="F214" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G214" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H214" s="16" t="inlineStr">
@@ -39966,7 +39966,7 @@
         </is>
       </c>
       <c r="I214" s="22" t="n">
-        <v>4861255168</v>
+        <v>4581028753.371248</v>
       </c>
       <c r="J214" s="25" t="inlineStr">
         <is>
@@ -39974,21 +39974,21 @@
         </is>
       </c>
       <c r="K214" s="22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L214" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M214" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, NetCashReturner, LynchEV-GY, LigerLaggi</t>
+          <t>FixedCost+DemandShock, ONeil-CANSLIM, Weinstein-Stage2, StrongCoverage</t>
         </is>
       </c>
       <c r="N214" s="24" t="n">
-        <v>0.3425930168343006</v>
+        <v>0.4640265859605835</v>
       </c>
       <c r="O214" s="24" t="n">
-        <v>0.4572524250000001</v>
+        <v>0.45710304</v>
       </c>
     </row>
     <row r="215" ht="16" customHeight="1">
@@ -40002,22 +40002,22 @@
       </c>
       <c r="D215" s="18" t="inlineStr">
         <is>
-          <t>NAVINFLUOR.NS</t>
+          <t>3698.HK</t>
         </is>
       </c>
       <c r="E215" s="19" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Limited</t>
+          <t>Huishang Bank Corporation Limited</t>
         </is>
       </c>
       <c r="F215" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G215" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H215" s="16" t="inlineStr">
@@ -40026,7 +40026,7 @@
         </is>
       </c>
       <c r="I215" s="22" t="n">
-        <v>4581028753.371248</v>
+        <v>8613885759.288021</v>
       </c>
       <c r="J215" s="25" t="inlineStr">
         <is>
@@ -40034,21 +40034,21 @@
         </is>
       </c>
       <c r="K215" s="22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L215" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M215" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, ONeil-CANSLIM, Weinstein-Stage2, StrongCoverage</t>
+          <t>Weinstein-Stage2, LynchPEGY</t>
         </is>
       </c>
       <c r="N215" s="24" t="n">
-        <v>0.4640265859605835</v>
+        <v>0.4471291465149196</v>
       </c>
       <c r="O215" s="24" t="n">
-        <v>0.45710304</v>
+        <v>0.45709545</v>
       </c>
     </row>
     <row r="216" ht="16" customHeight="1">
@@ -40062,22 +40062,22 @@
       </c>
       <c r="D216" s="18" t="inlineStr">
         <is>
-          <t>3698.HK</t>
+          <t>KONMY</t>
         </is>
       </c>
       <c r="E216" s="19" t="inlineStr">
         <is>
-          <t>Huishang Bank Corporation Limited</t>
+          <t>Konami Holdings Corporation</t>
         </is>
       </c>
       <c r="F216" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G216" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H216" s="16" t="inlineStr">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="I216" s="22" t="n">
-        <v>8613885759.288021</v>
+        <v>17790433280</v>
       </c>
       <c r="J216" s="25" t="inlineStr">
         <is>
@@ -40094,21 +40094,21 @@
         </is>
       </c>
       <c r="K216" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L216" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="L216" s="22" t="n">
-        <v>4</v>
-      </c>
       <c r="M216" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY</t>
+          <t xml:space="preserve">NarrativeLag, LargeCapQuality, StrongCoverage, LynchPEGY, LynchEV-GY, </t>
         </is>
       </c>
       <c r="N216" s="24" t="n">
-        <v>0.4471291465149196</v>
+        <v>0.4323731223551612</v>
       </c>
       <c r="O216" s="24" t="n">
-        <v>0.45709545</v>
+        <v>0.4570013183999999</v>
       </c>
     </row>
     <row r="217" ht="16" customHeight="1">
@@ -40122,12 +40122,12 @@
       </c>
       <c r="D217" s="18" t="inlineStr">
         <is>
-          <t>KONMY</t>
+          <t>DBD</t>
         </is>
       </c>
       <c r="E217" s="19" t="inlineStr">
         <is>
-          <t>Konami Holdings Corporation</t>
+          <t>Diebold Nixdorf, Incorporated</t>
         </is>
       </c>
       <c r="F217" s="26" t="inlineStr">
@@ -40137,7 +40137,7 @@
       </c>
       <c r="G217" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H217" s="16" t="inlineStr">
@@ -40146,7 +40146,7 @@
         </is>
       </c>
       <c r="I217" s="22" t="n">
-        <v>17790433280</v>
+        <v>2227575296</v>
       </c>
       <c r="J217" s="25" t="inlineStr">
         <is>
@@ -40154,21 +40154,21 @@
         </is>
       </c>
       <c r="K217" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L217" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M217" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, LargeCapQuality, StrongCoverage, LynchPEGY, LynchEV-GY, </t>
+          <t>CapitalDiscipline, KPIThreshold, CapitalReturner, LowSBCQuality, Geogr</t>
         </is>
       </c>
       <c r="N217" s="24" t="n">
-        <v>0.4323731223551612</v>
+        <v>0.3903658198976695</v>
       </c>
       <c r="O217" s="24" t="n">
-        <v>0.4570013183999999</v>
+        <v>0.4567277</v>
       </c>
     </row>
     <row r="218" ht="16" customHeight="1">
@@ -40182,12 +40182,12 @@
       </c>
       <c r="D218" s="18" t="inlineStr">
         <is>
-          <t>DBD</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="E218" s="19" t="inlineStr">
         <is>
-          <t>Diebold Nixdorf, Incorporated</t>
+          <t>Dillard’S, Inc.</t>
         </is>
       </c>
       <c r="F218" s="26" t="inlineStr">
@@ -40197,7 +40197,7 @@
       </c>
       <c r="G218" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H218" s="16" t="inlineStr">
@@ -40206,7 +40206,7 @@
         </is>
       </c>
       <c r="I218" s="22" t="n">
-        <v>2227575296</v>
+        <v>10161546240</v>
       </c>
       <c r="J218" s="25" t="inlineStr">
         <is>
@@ -40214,21 +40214,21 @@
         </is>
       </c>
       <c r="K218" s="22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L218" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M218" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, KPIThreshold, CapitalReturner, LowSBCQuality, Geogr</t>
+          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, CapitalReturner</t>
         </is>
       </c>
       <c r="N218" s="24" t="n">
-        <v>0.3903658198976695</v>
+        <v>0.39016453913511</v>
       </c>
       <c r="O218" s="24" t="n">
-        <v>0.4567277</v>
+        <v>0.4564924</v>
       </c>
     </row>
     <row r="219" ht="16" customHeight="1">
@@ -40242,22 +40242,22 @@
       </c>
       <c r="D219" s="18" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>RITPF</t>
         </is>
       </c>
       <c r="E219" s="19" t="inlineStr">
         <is>
-          <t>Dillard’S, Inc.</t>
+          <t>RIT Capital Partners plc</t>
         </is>
       </c>
       <c r="F219" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G219" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H219" s="16" t="inlineStr">
@@ -40266,7 +40266,7 @@
         </is>
       </c>
       <c r="I219" s="22" t="n">
-        <v>10161546240</v>
+        <v>4206580480</v>
       </c>
       <c r="J219" s="25" t="inlineStr">
         <is>
@@ -40274,21 +40274,21 @@
         </is>
       </c>
       <c r="K219" s="22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L219" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M219" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, CapitalReturner</t>
+          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY</t>
         </is>
       </c>
       <c r="N219" s="24" t="n">
-        <v>0.39016453913511</v>
+        <v>0.4174950525510613</v>
       </c>
       <c r="O219" s="24" t="n">
-        <v>0.4564924</v>
+        <v>0.4562307932000001</v>
       </c>
     </row>
     <row r="220" ht="16" customHeight="1">
@@ -40302,22 +40302,22 @@
       </c>
       <c r="D220" s="18" t="inlineStr">
         <is>
-          <t>RITPF</t>
+          <t>PHTCF</t>
         </is>
       </c>
       <c r="E220" s="19" t="inlineStr">
         <is>
-          <t>RIT Capital Partners plc</t>
+          <t>PLDT Inc.</t>
         </is>
       </c>
       <c r="F220" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G220" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H220" s="16" t="inlineStr">
@@ -40326,7 +40326,7 @@
         </is>
       </c>
       <c r="I220" s="22" t="n">
-        <v>4206580480</v>
+        <v>4861255168</v>
       </c>
       <c r="J220" s="25" t="inlineStr">
         <is>
@@ -40334,21 +40334,21 @@
         </is>
       </c>
       <c r="K220" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L220" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M220" s="21" t="inlineStr">
         <is>
-          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY</t>
+          <t>NarrativeLag, CapitalReturner, NetCashReturner, LynchEV-GY, LigerLaggi</t>
         </is>
       </c>
       <c r="N220" s="24" t="n">
-        <v>0.4174950525510613</v>
+        <v>0.3425930168343006</v>
       </c>
       <c r="O220" s="24" t="n">
-        <v>0.4562307932000001</v>
+        <v>0.4558514814</v>
       </c>
     </row>
     <row r="221" ht="16" customHeight="1">
@@ -47754,7 +47754,7 @@
         </is>
       </c>
       <c r="K344" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L344" s="22" t="n">
         <v>1</v>
@@ -50830,31 +50830,31 @@
       </c>
       <c r="D396" s="18" t="inlineStr">
         <is>
-          <t>UVRBF</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="E396" s="19" t="inlineStr">
         <is>
-          <t>Universal Robina Corporation</t>
+          <t>West Pharmaceutical Services, Inc.</t>
         </is>
       </c>
       <c r="F396" s="26" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G396" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H396" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I396" s="22" t="n">
-        <v>2129043200</v>
+        <v>24366200832</v>
       </c>
       <c r="J396" s="25" t="inlineStr">
         <is>
@@ -50862,21 +50862,21 @@
         </is>
       </c>
       <c r="K396" s="22" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L396" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M396" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, LynchEV-GY, LigerLaggingInflect</t>
+          <t>LindyMargin, LindyFCF, NoDilution, BuybackCompounder, LargeCapQuality,</t>
         </is>
       </c>
       <c r="N396" s="24" t="n">
-        <v>0.3732668102239384</v>
+        <v>0.3807445036921761</v>
       </c>
       <c r="O396" s="24" t="n">
-        <v>0.4232844</v>
+        <v>0.422991848</v>
       </c>
     </row>
     <row r="397" ht="16" customHeight="1">
@@ -50890,31 +50890,31 @@
       </c>
       <c r="D397" s="18" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>PAAS.TO</t>
         </is>
       </c>
       <c r="E397" s="19" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services, Inc.</t>
+          <t>PAN AMERICAN SILVER CORP</t>
         </is>
       </c>
       <c r="F397" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G397" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H397" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I397" s="22" t="n">
-        <v>24366200832</v>
+        <v>20718569823.74561</v>
       </c>
       <c r="J397" s="25" t="inlineStr">
         <is>
@@ -50922,21 +50922,21 @@
         </is>
       </c>
       <c r="K397" s="22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L397" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M397" s="21" t="inlineStr">
         <is>
-          <t>LindyMargin, LindyFCF, NoDilution, BuybackCompounder, LargeCapQuality,</t>
+          <t>FixedCost+DemandShock, RegimeCyclical, LargeCapQuality, MidCapGARP, St</t>
         </is>
       </c>
       <c r="N397" s="24" t="n">
-        <v>0.3807445036921761</v>
+        <v>0.4101897986043997</v>
       </c>
       <c r="O397" s="24" t="n">
-        <v>0.422991848</v>
+        <v>0.4225874622</v>
       </c>
     </row>
     <row r="398" ht="16" customHeight="1">
@@ -50950,22 +50950,22 @@
       </c>
       <c r="D398" s="18" t="inlineStr">
         <is>
-          <t>PAAS.TO</t>
+          <t>LKQ</t>
         </is>
       </c>
       <c r="E398" s="19" t="inlineStr">
         <is>
-          <t>PAN AMERICAN SILVER CORP</t>
+          <t>LKQ Corporation</t>
         </is>
       </c>
       <c r="F398" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G398" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H398" s="16" t="inlineStr">
@@ -50974,7 +50974,7 @@
         </is>
       </c>
       <c r="I398" s="22" t="n">
-        <v>20718569823.74561</v>
+        <v>6099880448</v>
       </c>
       <c r="J398" s="25" t="inlineStr">
         <is>
@@ -50982,21 +50982,21 @@
         </is>
       </c>
       <c r="K398" s="22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L398" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M398" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, RegimeCyclical, LargeCapQuality, MidCapGARP, St</t>
+          <t>NarrativeLag, LindyFCF, NoDilution, CapitalReturner, LowSBCQuality, Ge</t>
         </is>
       </c>
       <c r="N398" s="24" t="n">
-        <v>0.4101897986043997</v>
+        <v>0.3668171847414376</v>
       </c>
       <c r="O398" s="24" t="n">
-        <v>0.4225874622</v>
+        <v>0.4225728</v>
       </c>
     </row>
     <row r="399" ht="16" customHeight="1">
@@ -51010,22 +51010,22 @@
       </c>
       <c r="D399" s="18" t="inlineStr">
         <is>
-          <t>LKQ</t>
+          <t>B8O.F</t>
         </is>
       </c>
       <c r="E399" s="19" t="inlineStr">
         <is>
-          <t>LKQ Corporation</t>
+          <t>Yangzijiang Shipbuilding Holdings, Ltd.</t>
         </is>
       </c>
       <c r="F399" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G399" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H399" s="16" t="inlineStr">
@@ -51034,7 +51034,7 @@
         </is>
       </c>
       <c r="I399" s="22" t="n">
-        <v>6099880448</v>
+        <v>15013914247.77686</v>
       </c>
       <c r="J399" s="25" t="inlineStr">
         <is>
@@ -51042,21 +51042,21 @@
         </is>
       </c>
       <c r="K399" s="22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L399" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M399" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, LindyFCF, NoDilution, CapitalReturner, LowSBCQuality, Ge</t>
+          <t>CapitalDiscipline, OwnerOperator, LargeCapQuality, MidCapGARP, Weinste</t>
         </is>
       </c>
       <c r="N399" s="24" t="n">
-        <v>0.3668171847414376</v>
+        <v>0.4551581311869413</v>
       </c>
       <c r="O399" s="24" t="n">
-        <v>0.4225728</v>
+        <v>0.422511232</v>
       </c>
     </row>
     <row r="400" ht="16" customHeight="1">
@@ -51070,17 +51070,17 @@
       </c>
       <c r="D400" s="18" t="inlineStr">
         <is>
-          <t>B8O.F</t>
+          <t>AYI</t>
         </is>
       </c>
       <c r="E400" s="19" t="inlineStr">
         <is>
-          <t>Yangzijiang Shipbuilding Holdings, Ltd.</t>
+          <t>Acuity Brands, Inc.</t>
         </is>
       </c>
       <c r="F400" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G400" s="21" t="inlineStr">
@@ -51094,7 +51094,7 @@
         </is>
       </c>
       <c r="I400" s="22" t="n">
-        <v>15013914247.77686</v>
+        <v>9548241920</v>
       </c>
       <c r="J400" s="25" t="inlineStr">
         <is>
@@ -51102,21 +51102,21 @@
         </is>
       </c>
       <c r="K400" s="22" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L400" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M400" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, OwnerOperator, LargeCapQuality, MidCapGARP, Weinste</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CashReinvest, LindyMargin, LindyF</t>
         </is>
       </c>
       <c r="N400" s="24" t="n">
-        <v>0.4551581311869413</v>
+        <v>0.3666860393161141</v>
       </c>
       <c r="O400" s="24" t="n">
-        <v>0.422511232</v>
+        <v>0.42242176</v>
       </c>
     </row>
     <row r="401" ht="16" customHeight="1">
@@ -51130,12 +51130,12 @@
       </c>
       <c r="D401" s="18" t="inlineStr">
         <is>
-          <t>AYI</t>
+          <t>TWODY</t>
         </is>
       </c>
       <c r="E401" s="19" t="inlineStr">
         <is>
-          <t>Acuity Brands, Inc.</t>
+          <t>Taylor Wimpey plc</t>
         </is>
       </c>
       <c r="F401" s="26" t="inlineStr">
@@ -51154,7 +51154,7 @@
         </is>
       </c>
       <c r="I401" s="22" t="n">
-        <v>9548241920</v>
+        <v>3639735552</v>
       </c>
       <c r="J401" s="25" t="inlineStr">
         <is>
@@ -51162,21 +51162,21 @@
         </is>
       </c>
       <c r="K401" s="22" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L401" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M401" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CashReinvest, LindyMargin, LindyF</t>
+          <t>NarrativeLag, CapitalReturner, Cundill-DeepValue, StrongCoverage, Lync</t>
         </is>
       </c>
       <c r="N401" s="24" t="n">
-        <v>0.3666860393161141</v>
+        <v>0.3901809834895145</v>
       </c>
       <c r="O401" s="24" t="n">
-        <v>0.42242176</v>
+        <v>0.4223788563999999</v>
       </c>
     </row>
     <row r="402" ht="16" customHeight="1">
@@ -51190,12 +51190,12 @@
       </c>
       <c r="D402" s="18" t="inlineStr">
         <is>
-          <t>TWODY</t>
+          <t>HDALF</t>
         </is>
       </c>
       <c r="E402" s="19" t="inlineStr">
         <is>
-          <t>Taylor Wimpey plc</t>
+          <t>Haidilao International Holding Ltd.</t>
         </is>
       </c>
       <c r="F402" s="26" t="inlineStr">
@@ -51205,16 +51205,16 @@
       </c>
       <c r="G402" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H402" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I402" s="22" t="n">
-        <v>3639735552</v>
+        <v>7323992576</v>
       </c>
       <c r="J402" s="25" t="inlineStr">
         <is>
@@ -51222,21 +51222,21 @@
         </is>
       </c>
       <c r="K402" s="22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L402" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M402" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, Cundill-DeepValue, StrongCoverage, Lync</t>
+          <t>CapitalDiscipline, QuietCompounder, OwnerOperator, CapitalReturner, Ba</t>
         </is>
       </c>
       <c r="N402" s="24" t="n">
-        <v>0.3901809834895145</v>
+        <v>0.4129622445692864</v>
       </c>
       <c r="O402" s="24" t="n">
-        <v>0.4223788563999999</v>
+        <v>0.4222869091999999</v>
       </c>
     </row>
     <row r="403" ht="16" customHeight="1">
@@ -51250,22 +51250,22 @@
       </c>
       <c r="D403" s="18" t="inlineStr">
         <is>
-          <t>HDALF</t>
+          <t>003490.KS</t>
         </is>
       </c>
       <c r="E403" s="19" t="inlineStr">
         <is>
-          <t>Haidilao International Holding Ltd.</t>
+          <t>Korean Air Lines Co., Ltd.</t>
         </is>
       </c>
       <c r="F403" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G403" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H403" s="16" t="inlineStr">
@@ -51274,7 +51274,7 @@
         </is>
       </c>
       <c r="I403" s="22" t="n">
-        <v>7323992576</v>
+        <v>6972414965.038239</v>
       </c>
       <c r="J403" s="25" t="inlineStr">
         <is>
@@ -51282,21 +51282,21 @@
         </is>
       </c>
       <c r="K403" s="22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L403" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M403" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, QuietCompounder, OwnerOperator, CapitalReturner, Ba</t>
+          <t>FixedCost+DemandShock, BalanceSheetReturn, Weinstein-Stage2, XR-Latent</t>
         </is>
       </c>
       <c r="N403" s="24" t="n">
-        <v>0.4129622445692864</v>
+        <v>0.4140500311836295</v>
       </c>
       <c r="O403" s="24" t="n">
-        <v>0.4222869091999999</v>
+        <v>0.4216142085</v>
       </c>
     </row>
     <row r="404" ht="16" customHeight="1">
@@ -51310,22 +51310,22 @@
       </c>
       <c r="D404" s="18" t="inlineStr">
         <is>
-          <t>003490.KS</t>
+          <t>SHMZF</t>
         </is>
       </c>
       <c r="E404" s="19" t="inlineStr">
         <is>
-          <t>Korean Air Lines Co., Ltd.</t>
+          <t>Shimadzu Corporation</t>
         </is>
       </c>
       <c r="F404" s="26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G404" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H404" s="16" t="inlineStr">
@@ -51334,7 +51334,7 @@
         </is>
       </c>
       <c r="I404" s="22" t="n">
-        <v>6972414965.038239</v>
+        <v>6749641728</v>
       </c>
       <c r="J404" s="25" t="inlineStr">
         <is>
@@ -51342,21 +51342,21 @@
         </is>
       </c>
       <c r="K404" s="22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L404" s="22" t="n">
         <v>1</v>
       </c>
       <c r="M404" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, BalanceSheetReturn, Weinstein-Stage2, XR-Latent</t>
+          <t>MidCapGARP, StrongCoverage, LynchPEGY, Bottleneck-Chokepoint</t>
         </is>
       </c>
       <c r="N404" s="24" t="n">
-        <v>0.4140500311836295</v>
+        <v>0.4136022447447241</v>
       </c>
       <c r="O404" s="24" t="n">
-        <v>0.4216142085</v>
+        <v>0.4214896166000001</v>
       </c>
     </row>
     <row r="405" ht="16" customHeight="1">
@@ -51370,12 +51370,12 @@
       </c>
       <c r="D405" s="18" t="inlineStr">
         <is>
-          <t>SHMZF</t>
+          <t>BZZUF</t>
         </is>
       </c>
       <c r="E405" s="19" t="inlineStr">
         <is>
-          <t>Shimadzu Corporation</t>
+          <t>Buzzi Unicem S.p.A.</t>
         </is>
       </c>
       <c r="F405" s="26" t="inlineStr">
@@ -51385,16 +51385,16 @@
       </c>
       <c r="G405" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H405" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I405" s="22" t="n">
-        <v>6749641728</v>
+        <v>8472559104</v>
       </c>
       <c r="J405" s="25" t="inlineStr">
         <is>
@@ -51402,21 +51402,21 @@
         </is>
       </c>
       <c r="K405" s="22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L405" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M405" s="21" t="inlineStr">
         <is>
-          <t>MidCapGARP, StrongCoverage, LynchPEGY, Bottleneck-Chokepoint</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, OwnerOperator,</t>
         </is>
       </c>
       <c r="N405" s="24" t="n">
-        <v>0.4136022447447241</v>
+        <v>0.395675285290647</v>
       </c>
       <c r="O405" s="24" t="n">
-        <v>0.4214896166000001</v>
+        <v>0.4214182072</v>
       </c>
     </row>
     <row r="406" ht="16" customHeight="1">
@@ -51430,12 +51430,12 @@
       </c>
       <c r="D406" s="18" t="inlineStr">
         <is>
-          <t>BZZUF</t>
+          <t>FRCOY</t>
         </is>
       </c>
       <c r="E406" s="19" t="inlineStr">
         <is>
-          <t>Buzzi Unicem S.p.A.</t>
+          <t>Fast Retailing Co., Ltd.</t>
         </is>
       </c>
       <c r="F406" s="26" t="inlineStr">
@@ -51445,16 +51445,16 @@
       </c>
       <c r="G406" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H406" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="I406" s="22" t="n">
-        <v>8472559104</v>
+        <v>132621017088</v>
       </c>
       <c r="J406" s="25" t="inlineStr">
         <is>
@@ -51462,21 +51462,21 @@
         </is>
       </c>
       <c r="K406" s="22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L406" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M406" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, OwnerOperator,</t>
+          <t>LargeCapQuality, StrongCoverage, Bottleneck-Chokepoint</t>
         </is>
       </c>
       <c r="N406" s="24" t="n">
-        <v>0.395675285290647</v>
+        <v>0.4170385434067795</v>
       </c>
       <c r="O406" s="24" t="n">
-        <v>0.4214182072</v>
+        <v>0.421355</v>
       </c>
     </row>
     <row r="407" ht="16" customHeight="1">
@@ -51490,22 +51490,22 @@
       </c>
       <c r="D407" s="18" t="inlineStr">
         <is>
-          <t>FRCOY</t>
+          <t>GGBR4.SA</t>
         </is>
       </c>
       <c r="E407" s="19" t="inlineStr">
         <is>
-          <t>Fast Retailing Co., Ltd.</t>
+          <t>Gerdau S.A.</t>
         </is>
       </c>
       <c r="F407" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G407" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H407" s="16" t="inlineStr">
@@ -51514,7 +51514,7 @@
         </is>
       </c>
       <c r="I407" s="22" t="n">
-        <v>132621017088</v>
+        <v>9842497539.897947</v>
       </c>
       <c r="J407" s="25" t="inlineStr">
         <is>
@@ -51522,21 +51522,21 @@
         </is>
       </c>
       <c r="K407" s="22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L407" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M407" s="21" t="inlineStr">
         <is>
-          <t>LargeCapQuality, StrongCoverage, Bottleneck-Chokepoint</t>
+          <t>Weinstein-Stage2, BAB-Becoming, LynchPEGY, Forensic-PayoutConfirmed, F</t>
         </is>
       </c>
       <c r="N407" s="24" t="n">
-        <v>0.4170385434067795</v>
+        <v>0.3918790758786376</v>
       </c>
       <c r="O407" s="24" t="n">
-        <v>0.421355</v>
+        <v>0.4210889270000001</v>
       </c>
     </row>
     <row r="408" ht="16" customHeight="1">
@@ -51550,22 +51550,22 @@
       </c>
       <c r="D408" s="18" t="inlineStr">
         <is>
-          <t>GGBR4.SA</t>
+          <t>0285.HK</t>
         </is>
       </c>
       <c r="E408" s="19" t="inlineStr">
         <is>
-          <t>Gerdau S.A.</t>
+          <t>BYD Electronic (International) Company Limited</t>
         </is>
       </c>
       <c r="F408" s="26" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G408" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H408" s="16" t="inlineStr">
@@ -51574,7 +51574,7 @@
         </is>
       </c>
       <c r="I408" s="22" t="n">
-        <v>9842497539.897947</v>
+        <v>6838612255.101865</v>
       </c>
       <c r="J408" s="25" t="inlineStr">
         <is>
@@ -51582,21 +51582,21 @@
         </is>
       </c>
       <c r="K408" s="22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L408" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M408" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, BAB-Becoming, LynchPEGY, Forensic-PayoutConfirmed, F</t>
+          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, StrongCoverage, Temple</t>
         </is>
       </c>
       <c r="N408" s="24" t="n">
-        <v>0.3918790758786376</v>
+        <v>0.3813040132620671</v>
       </c>
       <c r="O408" s="24" t="n">
-        <v>0.4210889270000001</v>
+        <v>0.420894225</v>
       </c>
     </row>
     <row r="409" ht="16" customHeight="1">
@@ -51610,31 +51610,31 @@
       </c>
       <c r="D409" s="18" t="inlineStr">
         <is>
-          <t>0285.HK</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="E409" s="19" t="inlineStr">
         <is>
-          <t>BYD Electronic (International) Company Limited</t>
+          <t>The Marzetti Company Common Stock</t>
         </is>
       </c>
       <c r="F409" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G409" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H409" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="I409" s="22" t="n">
-        <v>6838612255.101865</v>
+        <v>2839628544</v>
       </c>
       <c r="J409" s="25" t="inlineStr">
         <is>
@@ -51642,21 +51642,21 @@
         </is>
       </c>
       <c r="K409" s="22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L409" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M409" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, StrongCoverage, Temple</t>
+          <t xml:space="preserve">NarrativeLag, CapitalDiscipline, CashReinvest, LindyMargin, LindyFCF, </t>
         </is>
       </c>
       <c r="N409" s="24" t="n">
-        <v>0.3813040132620671</v>
+        <v>0.3779559453679549</v>
       </c>
       <c r="O409" s="24" t="n">
-        <v>0.420894225</v>
+        <v>0.4206418560000001</v>
       </c>
     </row>
     <row r="410" ht="16" customHeight="1">
@@ -51670,12 +51670,12 @@
       </c>
       <c r="D410" s="18" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="E410" s="19" t="inlineStr">
         <is>
-          <t>The Marzetti Company Common Stock</t>
+          <t>Pjt Partners Inc.</t>
         </is>
       </c>
       <c r="F410" s="26" t="inlineStr">
@@ -51685,7 +51685,7 @@
       </c>
       <c r="G410" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H410" s="16" t="inlineStr">
@@ -51694,29 +51694,29 @@
         </is>
       </c>
       <c r="I410" s="22" t="n">
-        <v>2839628544</v>
-      </c>
-      <c r="J410" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>6952289792</v>
+      </c>
+      <c r="J410" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="K410" s="22" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L410" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M410" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, CapitalDiscipline, CashReinvest, LindyMargin, LindyFCF, </t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
         </is>
       </c>
       <c r="N410" s="24" t="n">
-        <v>0.3779559453679549</v>
+        <v>0.3319382175059425</v>
       </c>
       <c r="O410" s="24" t="n">
-        <v>0.4206418560000001</v>
+        <v>0.42063232</v>
       </c>
     </row>
     <row r="411" ht="16" customHeight="1">
@@ -51730,22 +51730,22 @@
       </c>
       <c r="D411" s="18" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>SCT.L</t>
         </is>
       </c>
       <c r="E411" s="19" t="inlineStr">
         <is>
-          <t>Pjt Partners Inc.</t>
+          <t>Softcat plc</t>
         </is>
       </c>
       <c r="F411" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G411" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H411" s="16" t="inlineStr">
@@ -51754,29 +51754,29 @@
         </is>
       </c>
       <c r="I411" s="22" t="n">
-        <v>6952289792</v>
-      </c>
-      <c r="J411" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>4874979959.599915</v>
+      </c>
+      <c r="J411" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K411" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L411" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M411" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
+          <t>NarrativeLag, CapitalDiscipline, Weinstein-Stage2, Kullamagi-Breakout,</t>
         </is>
       </c>
       <c r="N411" s="24" t="n">
-        <v>0.3319382175059425</v>
+        <v>0.4154131964770285</v>
       </c>
       <c r="O411" s="24" t="n">
-        <v>0.42063232</v>
+        <v>0.420606</v>
       </c>
     </row>
     <row r="412" ht="16" customHeight="1">
@@ -51790,22 +51790,22 @@
       </c>
       <c r="D412" s="18" t="inlineStr">
         <is>
-          <t>SCT.L</t>
+          <t>UVRBF</t>
         </is>
       </c>
       <c r="E412" s="19" t="inlineStr">
         <is>
-          <t>Softcat plc</t>
+          <t>Universal Robina Corporation</t>
         </is>
       </c>
       <c r="F412" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="G412" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H412" s="16" t="inlineStr">
@@ -51814,7 +51814,7 @@
         </is>
       </c>
       <c r="I412" s="22" t="n">
-        <v>4874979959.599915</v>
+        <v>2129043200</v>
       </c>
       <c r="J412" s="25" t="inlineStr">
         <is>
@@ -51822,21 +51822,21 @@
         </is>
       </c>
       <c r="K412" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L412" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M412" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, Weinstein-Stage2, Kullamagi-Breakout,</t>
+          <t>CapitalDiscipline, LynchEV-GY, LigerLaggingInflect</t>
         </is>
       </c>
       <c r="N412" s="24" t="n">
-        <v>0.4154131964770285</v>
+        <v>0.3732668102239384</v>
       </c>
       <c r="O412" s="24" t="n">
-        <v>0.420606</v>
+        <v>0.420462504</v>
       </c>
     </row>
     <row r="413" ht="16" customHeight="1">
@@ -55114,7 +55114,7 @@
         </is>
       </c>
       <c r="K467" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L467" s="22" t="n">
         <v>3</v>
@@ -56074,14 +56074,14 @@
         </is>
       </c>
       <c r="K483" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L483" s="22" t="n">
         <v>2</v>
       </c>
       <c r="M483" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, MidCapGARP, BAB-Becoming, BAB-Multibagger, X</t>
+          <t>NarrativeLag, DeadOption, BAB-Becoming, BAB-Multibagger, XR-ForcedSell</t>
         </is>
       </c>
       <c r="N483" s="24" t="n">
